--- a/EXCEL FILEOVI/ZAVRSNI EXCEL - SIM RESULTS .xlsx
+++ b/EXCEL FILEOVI/ZAVRSNI EXCEL - SIM RESULTS .xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/523341E057C2D1B5/Documents/2526 - LJETNI SEMESTAR/ZAVRŠNI RAD 2026/EXCEL FILEOVI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1006" documentId="8_{749E225B-507B-4645-922D-F24EE2B83FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A3EDFA0-2542-4003-BCEB-CABAA8F999F7}"/>
+  <xr:revisionPtr revIDLastSave="1402" documentId="8_{749E225B-507B-4645-922D-F24EE2B83FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F6582BD-CA3B-40DA-954D-316EB031F865}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5A5A50C3-7C6B-466F-847F-D23E3D13151B}"/>
   </bookViews>
   <sheets>
-    <sheet name="SZE parameters" sheetId="1" r:id="rId1"/>
-    <sheet name="SZC parameters" sheetId="2" r:id="rId2"/>
+    <sheet name="SZE SIM RESULTS" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,28 +36,124 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="34">
   <si>
-    <t>PRORACUN</t>
+    <t>Harmonik</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>HD value</t>
+  </si>
+  <si>
+    <t>HD [V]</t>
+  </si>
+  <si>
+    <t>HD [dB]</t>
+  </si>
+  <si>
+    <t>SZE / Re = 250 / Rt = 2200</t>
+  </si>
+  <si>
+    <t>THD [%]</t>
+  </si>
+  <si>
+    <t>SZE / Re = 500 / Rt = 2200</t>
+  </si>
+  <si>
+    <t>SZE / Re = 1000 / Rt = 2200</t>
+  </si>
+  <si>
+    <t>SZE / Re = 2000 / Rt = 2200</t>
+  </si>
+  <si>
+    <t>SZE / Re = 3000 / Rt = 2200</t>
+  </si>
+  <si>
+    <t>korisnost [%]</t>
+  </si>
+  <si>
+    <t>Output Power [W]</t>
+  </si>
+  <si>
+    <t>Input Power [W]</t>
+  </si>
+  <si>
+    <t>SZE / Re = 250 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 500 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 1000 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 2000 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 3000 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 3000 / Rt = 1100</t>
+  </si>
+  <si>
+    <t>SZE / Re = 2000 / Rt = 1100</t>
+  </si>
+  <si>
+    <t>SZE / Re = 1000 / Rt = 1100</t>
+  </si>
+  <si>
+    <t>SZE / Re = 500 / Rt = 1100</t>
+  </si>
+  <si>
+    <t>SZE / Re = 250 / Rt = 1100</t>
+  </si>
+  <si>
+    <t>SZE / Re = 250 / Rt = 3300</t>
+  </si>
+  <si>
+    <t>SZE / Re = 500 / Rt = 3300</t>
+  </si>
+  <si>
+    <t>SZE / Re = 1000 / Rt = 3300</t>
+  </si>
+  <si>
+    <t>SZE / Re = 2000 / Rt = 3300</t>
+  </si>
+  <si>
+    <t>SZE / Re = 3000 / Rt = 3300</t>
+  </si>
+  <si>
+    <t>SZE / Re = 3000 / Rt = 4400</t>
+  </si>
+  <si>
+    <t>SZE / Re = 2000 / Rt = 4400</t>
+  </si>
+  <si>
+    <t>SZE / Re = 1000 / Rt = 4400</t>
+  </si>
+  <si>
+    <t>SZE / Re = 500 / Rt = 4400</t>
+  </si>
+  <si>
+    <t>SZE / Re = 250 / Rt = 4400</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -81,9 +176,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79FF54C5-DE8F-4674-B282-5F9819316D0D}">
-  <dimension ref="A1:A90"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -452,86 +550,3790 @@
     <col min="33" max="35" width="8.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="2" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="3" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="5" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="8" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="10" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="12" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="14" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="15" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="1" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+    </row>
+    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" t="s">
+        <v>4</v>
+      </c>
+      <c r="W2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>9.7472340000000006</v>
+      </c>
+      <c r="C3" s="2">
+        <f>10^(B3/20)</f>
+        <v>3.0715790727751315</v>
+      </c>
+      <c r="D3" s="2">
+        <f>C3^2</f>
+        <v>9.4345980003101371</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>8.9462379999999992</v>
+      </c>
+      <c r="H3" s="2">
+        <f>10^(G3/20)</f>
+        <v>2.8009922036538724</v>
+      </c>
+      <c r="I3" s="2">
+        <f>H3^2</f>
+        <v>7.8455573249297759</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
+        <v>6.601788</v>
+      </c>
+      <c r="M3" s="2">
+        <f>10^(L3/20)</f>
+        <v>2.1384022366665874</v>
+      </c>
+      <c r="N3" s="2">
+        <f>M3^2</f>
+        <v>4.5727641257806635</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>2.6878380000000002</v>
+      </c>
+      <c r="R3" s="2">
+        <f>10^(Q3/20)</f>
+        <v>1.362673781611937</v>
+      </c>
+      <c r="S3" s="2">
+        <f>R3^2</f>
+        <v>1.8568798350925768</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2">
+        <v>-0.24507419999999999</v>
+      </c>
+      <c r="W3" s="2">
+        <f>10^(V3/20)</f>
+        <v>0.97217912163703113</v>
+      </c>
+      <c r="X3" s="2">
+        <f>W3^2</f>
+        <v>0.94513224454694933</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>5.8321823999999998</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" ref="C4:C10" si="0">10^(B4/20)</f>
+        <v>1.9570824389506696</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D12" si="1">C4^2</f>
+        <v>3.8301716728491013</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1.93266</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" ref="H4:H10" si="2">10^(G4/20)</f>
+        <v>1.2492029466970178</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" ref="I4:I10" si="3">H4^2</f>
+        <v>1.5605080020365123</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4" s="2">
+        <v>-5.7993300000000003</v>
+      </c>
+      <c r="M4" s="2">
+        <f t="shared" ref="M4:M10" si="4">10^(L4/20)</f>
+        <v>0.51290094590092872</v>
+      </c>
+      <c r="N4" s="2">
+        <f t="shared" ref="N4:N12" si="5">M4^2</f>
+        <v>0.26306738030606741</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>-20.03003</v>
+      </c>
+      <c r="R4" s="2">
+        <f t="shared" ref="R4:R10" si="6">10^(Q4/20)</f>
+        <v>9.9654863817176587E-2</v>
+      </c>
+      <c r="S4" s="2">
+        <f t="shared" ref="S4:S10" si="7">R4^2</f>
+        <v>9.9310918824200116E-3</v>
+      </c>
+      <c r="U4">
+        <v>2</v>
+      </c>
+      <c r="V4" s="2">
+        <v>-37.879820000000002</v>
+      </c>
+      <c r="W4" s="2">
+        <f t="shared" ref="W4:W10" si="8">10^(V4/20)</f>
+        <v>1.2764652610661897E-2</v>
+      </c>
+      <c r="X4" s="2">
+        <f t="shared" ref="X4:X12" si="9">W4^2</f>
+        <v>1.629363562708776E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>-2.5565099999999998</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.74503126815571452</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="1"/>
+        <v>0.55507159052971222</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>-26.298290000000001</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="2"/>
+        <v>4.8426769647804124E-2</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="3"/>
+        <v>2.3451520185214826E-3</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2">
+        <v>-14.659330000000001</v>
+      </c>
+      <c r="M5" s="2">
+        <f t="shared" si="4"/>
+        <v>0.18494112707747365</v>
+      </c>
+      <c r="N5" s="2">
+        <f t="shared" si="5"/>
+        <v>3.4203220484686256E-2</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>-22.202839999999998</v>
+      </c>
+      <c r="R5" s="2">
+        <f t="shared" si="6"/>
+        <v>7.759933508619081E-2</v>
+      </c>
+      <c r="S5" s="2">
+        <f t="shared" si="7"/>
+        <v>6.021656805818924E-3</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2">
+        <v>-34.638710000000003</v>
+      </c>
+      <c r="W5" s="2">
+        <f t="shared" si="8"/>
+        <v>1.8538069243291141E-2</v>
+      </c>
+      <c r="X5" s="2">
+        <f t="shared" si="9"/>
+        <v>3.43660011269057E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>-25.062999999999999</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>5.5827733927191446E-2</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="1"/>
+        <v>3.1167358754452829E-3</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2">
+        <v>-11.9879</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>0.25153880884721458</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="3"/>
+        <v>6.3271772356275555E-2</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6" s="2">
+        <v>-30.51709</v>
+      </c>
+      <c r="M6" s="2">
+        <f t="shared" si="4"/>
+        <v>2.979514477441499E-2</v>
+      </c>
+      <c r="N6" s="2">
+        <f t="shared" si="5"/>
+        <v>8.8775065212834891E-4</v>
+      </c>
+      <c r="P6">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>-28.17287</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" si="6"/>
+        <v>3.9026221038674994E-2</v>
+      </c>
+      <c r="S6" s="2">
+        <f t="shared" si="7"/>
+        <v>1.5230459285595188E-3</v>
+      </c>
+      <c r="U6">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2">
+        <v>-42.636589999999998</v>
+      </c>
+      <c r="W6" s="2">
+        <f t="shared" si="8"/>
+        <v>7.3819398138351153E-3</v>
+      </c>
+      <c r="X6" s="2">
+        <f t="shared" si="9"/>
+        <v>5.4493035415084014E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>-11.007</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.28161124979805008</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="1"/>
+        <v>7.9304896012819759E-2</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2">
+        <v>-28.661259999999999</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="2"/>
+        <v>3.6892407750616203E-2</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="3"/>
+        <v>1.3610497496377265E-3</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7" s="2">
+        <v>-23.499700000000001</v>
+      </c>
+      <c r="M7" s="2">
+        <f t="shared" si="4"/>
+        <v>6.6836700174838559E-2</v>
+      </c>
+      <c r="N7" s="2">
+        <f t="shared" si="5"/>
+        <v>4.4671444902612649E-3</v>
+      </c>
+      <c r="P7">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>-33.332484000000001</v>
+      </c>
+      <c r="R7" s="2">
+        <f t="shared" si="6"/>
+        <v>2.1546453676641462E-2</v>
+      </c>
+      <c r="S7" s="2">
+        <f t="shared" si="7"/>
+        <v>4.6424966603965639E-4</v>
+      </c>
+      <c r="U7">
+        <v>5</v>
+      </c>
+      <c r="V7" s="2">
+        <v>-37.548200000000001</v>
+      </c>
+      <c r="W7" s="2">
+        <f t="shared" si="8"/>
+        <v>1.3261419091999134E-2</v>
+      </c>
+      <c r="X7" s="2">
+        <f t="shared" si="9"/>
+        <v>1.7586523633363914E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>-17.115110000000001</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.13939413460466141</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9430724762182463E-2</v>
+      </c>
+      <c r="F8">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2">
+        <v>-20.3627</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>9.5910244914821211E-2</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="3"/>
+        <v>9.1987750796209879E-3</v>
+      </c>
+      <c r="K8">
+        <v>6</v>
+      </c>
+      <c r="L8" s="2">
+        <v>-30.574729999999999</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="4"/>
+        <v>2.9598077294880985E-2</v>
+      </c>
+      <c r="N8" s="2">
+        <f t="shared" si="5"/>
+        <v>8.7604617955374926E-4</v>
+      </c>
+      <c r="P8">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>-49.12724</v>
+      </c>
+      <c r="R8" s="2">
+        <f t="shared" si="6"/>
+        <v>3.4965359673634028E-3</v>
+      </c>
+      <c r="S8" s="2">
+        <f t="shared" si="7"/>
+        <v>1.2225763771065926E-5</v>
+      </c>
+      <c r="U8">
+        <v>6</v>
+      </c>
+      <c r="V8" s="2">
+        <v>-50.121259999999999</v>
+      </c>
+      <c r="W8" s="2">
+        <f t="shared" si="8"/>
+        <v>3.1184371818623381E-3</v>
+      </c>
+      <c r="X8" s="2">
+        <f t="shared" si="9"/>
+        <v>9.7246504572215207E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>-26.020900000000001</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="0"/>
+        <v>4.9998272591817702E-2</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4998272621657093E-3</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9" s="2">
+        <v>-36.463700000000003</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>1.5025017966763249E-2</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="3"/>
+        <v>2.2575116490155845E-4</v>
+      </c>
+      <c r="K9">
+        <v>7</v>
+      </c>
+      <c r="L9" s="2">
+        <v>-31.937999999999999</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="4"/>
+        <v>2.5298804558879277E-2</v>
+      </c>
+      <c r="N9" s="2">
+        <f t="shared" si="5"/>
+        <v>6.4002951210837087E-4</v>
+      </c>
+      <c r="P9">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>-46.446350000000002</v>
+      </c>
+      <c r="R9" s="2">
+        <f t="shared" si="6"/>
+        <v>4.760828093251528E-3</v>
+      </c>
+      <c r="S9" s="2">
+        <f t="shared" si="7"/>
+        <v>2.266548413349298E-5</v>
+      </c>
+      <c r="U9">
+        <v>7</v>
+      </c>
+      <c r="V9" s="2">
+        <v>-41.249771000000003</v>
+      </c>
+      <c r="W9" s="2">
+        <f t="shared" si="8"/>
+        <v>8.659871544634358E-3</v>
+      </c>
+      <c r="X9" s="2">
+        <f t="shared" si="9"/>
+        <v>7.4993375169567862E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>-20.358229999999999</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="0"/>
+        <v>9.595961569281436E-2</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="1"/>
+        <v>9.2082478439126231E-3</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2">
+        <v>-24.412800000000001</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>6.0167227540845261E-2</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="3"/>
+        <v>3.6200952699518485E-3</v>
+      </c>
+      <c r="K10">
+        <v>8</v>
+      </c>
+      <c r="L10" s="2">
+        <v>-33.131920000000001</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="4"/>
+        <v>2.2049766764618117E-2</v>
+      </c>
+      <c r="N10" s="2">
+        <f t="shared" si="5"/>
+        <v>4.8619221437405771E-4</v>
+      </c>
+      <c r="P10">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>-37.78837</v>
+      </c>
+      <c r="R10" s="2">
+        <f t="shared" si="6"/>
+        <v>1.2899756128931869E-2</v>
+      </c>
+      <c r="S10" s="2">
+        <f t="shared" si="7"/>
+        <v>1.6640370818591532E-4</v>
+      </c>
+      <c r="U10">
+        <v>8</v>
+      </c>
+      <c r="V10" s="2">
+        <v>-68.736670000000004</v>
+      </c>
+      <c r="W10" s="2">
+        <f t="shared" si="8"/>
+        <v>3.657349803682403E-4</v>
+      </c>
+      <c r="X10" s="2">
+        <f t="shared" si="9"/>
+        <v>1.3376207586495713E-7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2">
+        <f>SQRT(SUM(D4:D10)/D3)</f>
+        <v>0.69053678997098566</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <f>SQRT(SUM(I4:I10)/I3)</f>
+        <v>0.45727795766436541</v>
+      </c>
+      <c r="K11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2">
+        <f>SQRT(SUM(N4:N10)/N3)</f>
+        <v>0.25810436021943967</v>
+      </c>
+      <c r="P11" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>SQRT(SUM(S4:S10)/S3)</f>
+        <v>9.8842283997892091E-2</v>
+      </c>
+      <c r="U11" t="s">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2">
+        <f>SQRT(SUM(X4:X10)/X3)</f>
+        <v>2.9487535496158849E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2">
+        <f>B11*100</f>
+        <v>69.053678997098572</v>
+      </c>
+      <c r="F12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2">
+        <f>G11*100</f>
+        <v>45.727795766436543</v>
+      </c>
+      <c r="K12" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" s="2">
+        <f>L11*100</f>
+        <v>25.810436021943968</v>
+      </c>
+      <c r="P12" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="2">
+        <f>Q11*100</f>
+        <v>9.88422839978921</v>
+      </c>
+      <c r="U12" t="s">
+        <v>6</v>
+      </c>
+      <c r="V12" s="2">
+        <f>V11*100</f>
+        <v>2.9487535496158848</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="17" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="K17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="P17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="U17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+    </row>
+    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" t="s">
+        <v>2</v>
+      </c>
+      <c r="K18" t="s">
+        <v>0</v>
+      </c>
+      <c r="L18" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" t="s">
+        <v>2</v>
+      </c>
+      <c r="P18" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" t="s">
+        <v>2</v>
+      </c>
+      <c r="U18" t="s">
+        <v>0</v>
+      </c>
+      <c r="V18" t="s">
+        <v>4</v>
+      </c>
+      <c r="W18" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2">
+        <v>6.7682770000000003</v>
+      </c>
+      <c r="C19" s="2">
+        <f>10^(B19/20)</f>
+        <v>2.1797859551571217</v>
+      </c>
+      <c r="D19" s="2">
+        <f>C19^2</f>
+        <v>4.7514668103002453</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>4.9325409999999996</v>
+      </c>
+      <c r="H19" s="2">
+        <f>10^(G19/20)</f>
+        <v>1.7645218882746261</v>
+      </c>
+      <c r="I19" s="2">
+        <f>H19^2</f>
+        <v>3.1135374942002518</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1.7835570000000001</v>
+      </c>
+      <c r="M19" s="2">
+        <f>10^(L19/20)</f>
+        <v>1.2279419885753484</v>
+      </c>
+      <c r="N19" s="2">
+        <f>M19^2</f>
+        <v>1.5078415273063812</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>-2.7031450000000001</v>
+      </c>
+      <c r="R19" s="2">
+        <f>10^(Q19/20)</f>
+        <v>0.73255923896036046</v>
+      </c>
+      <c r="S19" s="2">
+        <f>R19^2</f>
+        <v>0.53664303858618245</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2">
+        <v>-5.8865530000000001</v>
+      </c>
+      <c r="W19" s="2">
+        <f>10^(V19/20)</f>
+        <v>0.50777621031291997</v>
+      </c>
+      <c r="X19" s="2">
+        <f>W19^2</f>
+        <v>0.25783667975975072</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1.5660780000000001</v>
+      </c>
+      <c r="C20" s="2">
+        <f t="shared" ref="C20:C26" si="10">10^(B20/20)</f>
+        <v>1.1975782502725438</v>
+      </c>
+      <c r="D20" s="2">
+        <f t="shared" ref="D20:D26" si="11">C20^2</f>
+        <v>1.4341936655258476</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2">
+        <v>-3.9363000000000001</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" ref="H20:H26" si="12">10^(G20/20)</f>
+        <v>0.63560162665626685</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" ref="I20:I26" si="13">H20^2</f>
+        <v>0.40398942780809244</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20" s="2">
+        <v>-13.43887</v>
+      </c>
+      <c r="M20" s="2">
+        <f t="shared" ref="M20:M26" si="14">10^(L20/20)</f>
+        <v>0.2128415926493088</v>
+      </c>
+      <c r="N20" s="2">
+        <f t="shared" ref="N20:N26" si="15">M20^2</f>
+        <v>4.5301543561494302E-2</v>
+      </c>
+      <c r="P20">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>-30.990259999999999</v>
+      </c>
+      <c r="R20" s="2">
+        <f t="shared" ref="R20:R26" si="16">10^(Q20/20)</f>
+        <v>2.8215451228061027E-2</v>
+      </c>
+      <c r="S20" s="2">
+        <f t="shared" ref="S20:S26" si="17">R20^2</f>
+        <v>7.9611168800309054E-4</v>
+      </c>
+      <c r="U20">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2">
+        <v>-65.969729999999998</v>
+      </c>
+      <c r="W20" s="2">
+        <f t="shared" ref="W20:W26" si="18">10^(V20/20)</f>
+        <v>5.0293689935005737E-4</v>
+      </c>
+      <c r="X20" s="2">
+        <f t="shared" ref="X20:X26" si="19">W20^2</f>
+        <v>2.5294552472784976E-7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2">
+        <v>-11.415800000000001</v>
+      </c>
+      <c r="C21" s="2">
+        <f t="shared" si="10"/>
+        <v>0.26866432388032097</v>
+      </c>
+      <c r="D21" s="2">
+        <f t="shared" si="11"/>
+        <v>7.2180518926069998E-2</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2">
+        <v>-22.321069999999999</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="12"/>
+        <v>7.6550230017373253E-2</v>
+      </c>
+      <c r="I21" s="2">
+        <f t="shared" si="13"/>
+        <v>5.8599377157127529E-3</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21" s="2">
+        <v>-19.567900000000002</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" si="14"/>
+        <v>0.10510055272648611</v>
+      </c>
+      <c r="N21" s="2">
+        <f t="shared" si="15"/>
+        <v>1.1046126183412887E-2</v>
+      </c>
+      <c r="P21">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>-32.109788000000002</v>
+      </c>
+      <c r="R21" s="2">
+        <f t="shared" si="16"/>
+        <v>2.4803364755235858E-2</v>
+      </c>
+      <c r="S21" s="2">
+        <f t="shared" si="17"/>
+        <v>6.1520690318127638E-4</v>
+      </c>
+      <c r="U21">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2">
+        <v>-50.223329999999997</v>
+      </c>
+      <c r="W21" s="2">
+        <f t="shared" si="18"/>
+        <v>3.0820061429196353E-3</v>
+      </c>
+      <c r="X21" s="2">
+        <f t="shared" si="19"/>
+        <v>9.4987618649943669E-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" s="2">
+        <v>-15.617190000000001</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" si="10"/>
+        <v>0.16563057135745332</v>
+      </c>
+      <c r="D22" s="2">
+        <f t="shared" si="11"/>
+        <v>2.7433486168196436E-2</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2">
+        <v>-18.847539999999999</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="12"/>
+        <v>0.11418866616446387</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="13"/>
+        <v>1.3039051480419376E-2</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22" s="2">
+        <v>-34.189619999999998</v>
+      </c>
+      <c r="M22" s="2">
+        <f t="shared" si="14"/>
+        <v>1.952176138156932E-2</v>
+      </c>
+      <c r="N22" s="2">
+        <f t="shared" si="15"/>
+        <v>3.810991674389313E-4</v>
+      </c>
+      <c r="P22">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>-36.027729999999998</v>
+      </c>
+      <c r="R22" s="2">
+        <f t="shared" si="16"/>
+        <v>1.5798414349361647E-2</v>
+      </c>
+      <c r="S22" s="2">
+        <f t="shared" si="17"/>
+        <v>2.49589895954116E-4</v>
+      </c>
+      <c r="U22">
+        <v>4</v>
+      </c>
+      <c r="V22" s="2">
+        <v>-61.591799999999999</v>
+      </c>
+      <c r="W22" s="2">
+        <f t="shared" si="18"/>
+        <v>8.3254937668637862E-4</v>
+      </c>
+      <c r="X22" s="2">
+        <f t="shared" si="19"/>
+        <v>6.9313846462087754E-7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23" s="2">
+        <v>-17.219830000000002</v>
+      </c>
+      <c r="C23" s="2">
+        <f t="shared" si="10"/>
+        <v>0.13772364238646667</v>
+      </c>
+      <c r="D23" s="2">
+        <f t="shared" si="11"/>
+        <v>1.8967801672195358E-2</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2">
+        <v>-27.135739999999998</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="12"/>
+        <v>4.3975724177045733E-2</v>
+      </c>
+      <c r="I23" s="2">
+        <f t="shared" si="13"/>
+        <v>1.9338643168956046E-3</v>
+      </c>
+      <c r="K23">
+        <v>5</v>
+      </c>
+      <c r="L23" s="2">
+        <v>-33.874360000000003</v>
+      </c>
+      <c r="M23" s="2">
+        <f t="shared" si="14"/>
+        <v>2.0243332102641398E-2</v>
+      </c>
+      <c r="N23" s="2">
+        <f t="shared" si="15"/>
+        <v>4.097924946178318E-4</v>
+      </c>
+      <c r="P23">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>-38.085560000000001</v>
+      </c>
+      <c r="R23" s="2">
+        <f t="shared" si="16"/>
+        <v>1.246585296288831E-2</v>
+      </c>
+      <c r="S23" s="2">
+        <f t="shared" si="17"/>
+        <v>1.5539749009235127E-4</v>
+      </c>
+      <c r="U23">
+        <v>5</v>
+      </c>
+      <c r="V23" s="2">
+        <v>-52.544119999999999</v>
+      </c>
+      <c r="W23" s="2">
+        <f t="shared" si="18"/>
+        <v>2.35935884707182E-3</v>
+      </c>
+      <c r="X23" s="2">
+        <f t="shared" si="19"/>
+        <v>5.5665741692560674E-6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24" s="2">
+        <v>-31.648599999999998</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" si="10"/>
+        <v>2.6155919977842376E-2</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="11"/>
+        <v>6.8413214988729393E-4</v>
+      </c>
+      <c r="F24">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2">
+        <v>-27.937919999999998</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="12"/>
+        <v>4.0096272421387906E-2</v>
+      </c>
+      <c r="I24" s="2">
+        <f t="shared" si="13"/>
+        <v>1.6077110620901524E-3</v>
+      </c>
+      <c r="K24">
+        <v>6</v>
+      </c>
+      <c r="L24" s="2">
+        <v>-32.442239999999998</v>
+      </c>
+      <c r="M24" s="2">
+        <f t="shared" si="14"/>
+        <v>2.3871955707789751E-2</v>
+      </c>
+      <c r="N24" s="2">
+        <f t="shared" si="15"/>
+        <v>5.6987026931467569E-4</v>
+      </c>
+      <c r="P24">
+        <v>6</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>-46.484569999999998</v>
+      </c>
+      <c r="R24" s="2">
+        <f t="shared" si="16"/>
+        <v>4.7399253288239298E-3</v>
+      </c>
+      <c r="S24" s="2">
+        <f t="shared" si="17"/>
+        <v>2.246689212282664E-5</v>
+      </c>
+      <c r="U24">
+        <v>6</v>
+      </c>
+      <c r="V24" s="2">
+        <v>-59.123550000000002</v>
+      </c>
+      <c r="W24" s="2">
+        <f>10^(V24/20)</f>
+        <v>1.1061715894533477E-3</v>
+      </c>
+      <c r="X24" s="2">
+        <f t="shared" si="19"/>
+        <v>1.2236155853137456E-6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2">
+        <v>-22.412500000000001</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="10"/>
+        <v>7.5748667929495014E-2</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="11"/>
+        <v>5.7378606930929069E-3</v>
+      </c>
+      <c r="F25">
+        <v>7</v>
+      </c>
+      <c r="G25" s="2">
+        <v>-30.596316000000002</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" si="12"/>
+        <v>2.9524612067430886E-2</v>
+      </c>
+      <c r="I25" s="2">
+        <f t="shared" si="13"/>
+        <v>8.7170271773228552E-4</v>
+      </c>
+      <c r="K25">
+        <v>7</v>
+      </c>
+      <c r="L25" s="2">
+        <v>-43.529693000000002</v>
+      </c>
+      <c r="M25" s="2">
+        <f t="shared" si="14"/>
+        <v>6.6606306266898362E-3</v>
+      </c>
+      <c r="N25" s="2">
+        <f t="shared" si="15"/>
+        <v>4.4364000345198639E-5</v>
+      </c>
+      <c r="P25">
+        <v>7</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>-49.811889999999998</v>
+      </c>
+      <c r="R25" s="2">
+        <f t="shared" si="16"/>
+        <v>3.2315099687674985E-3</v>
+      </c>
+      <c r="S25" s="2">
+        <f t="shared" si="17"/>
+        <v>1.044265667824372E-5</v>
+      </c>
+      <c r="U25">
+        <v>7</v>
+      </c>
+      <c r="V25" s="2">
+        <v>-54.15334</v>
+      </c>
+      <c r="W25" s="2">
+        <f>10^(V25/20)</f>
+        <v>1.9603472148566931E-3</v>
+      </c>
+      <c r="X25" s="2">
+        <f t="shared" si="19"/>
+        <v>3.8429612027963939E-6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>8</v>
+      </c>
+      <c r="B26" s="2">
+        <v>-39.467100000000002</v>
+      </c>
+      <c r="C26" s="2">
+        <f t="shared" si="10"/>
+        <v>1.0632735242956418E-2</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="11"/>
+        <v>1.1305505874680748E-4</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2">
+        <v>-35.761539999999997</v>
+      </c>
+      <c r="H26" s="2">
+        <f t="shared" si="12"/>
+        <v>1.6290071856043555E-2</v>
+      </c>
+      <c r="I26" s="2">
+        <f t="shared" si="13"/>
+        <v>2.6536644107506233E-4</v>
+      </c>
+      <c r="K26">
+        <v>8</v>
+      </c>
+      <c r="L26" s="2">
+        <v>-43.648229999999998</v>
+      </c>
+      <c r="M26" s="2">
+        <f t="shared" si="14"/>
+        <v>6.5703499262493798E-3</v>
+      </c>
+      <c r="N26" s="2">
+        <f t="shared" si="15"/>
+        <v>4.3169498153365231E-5</v>
+      </c>
+      <c r="P26">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>-54.7545</v>
+      </c>
+      <c r="R26" s="2">
+        <f t="shared" si="16"/>
+        <v>1.8292581556982267E-3</v>
+      </c>
+      <c r="S26" s="2">
+        <f t="shared" si="17"/>
+        <v>3.3461854001884778E-6</v>
+      </c>
+      <c r="U26">
+        <v>8</v>
+      </c>
+      <c r="V26" s="2">
+        <v>-58.685600000000001</v>
+      </c>
+      <c r="W26" s="2">
+        <f t="shared" si="18"/>
+        <v>1.1633757315162722E-3</v>
+      </c>
+      <c r="X26" s="2">
+        <f t="shared" si="19"/>
+        <v>1.3534430926810213E-6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2">
+        <f>SQRT(SUM(D20:D26)/D19)</f>
+        <v>0.57286521798157586</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <f>SQRT(SUM(I20:I26)/I19)</f>
+        <v>0.37057410684906278</v>
+      </c>
+      <c r="K27" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2">
+        <f>SQRT(SUM(N20:N26)/N19)</f>
+        <v>0.19578116585594971</v>
+      </c>
+      <c r="P27" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="2">
+        <f>SQRT(SUM(S20:S26)/S19)</f>
+        <v>5.8754832421509827E-2</v>
+      </c>
+      <c r="U27" t="s">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2">
+        <f>SQRT(SUM(X20:X26)/X19)</f>
+        <v>9.3273060292258965E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2">
+        <f>B27*100</f>
+        <v>57.286521798157587</v>
+      </c>
+      <c r="F28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" s="2">
+        <f>G27*100</f>
+        <v>37.05741068490628</v>
+      </c>
+      <c r="K28" t="s">
+        <v>6</v>
+      </c>
+      <c r="L28" s="2">
+        <f>L27*100</f>
+        <v>19.578116585594969</v>
+      </c>
+      <c r="P28" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q28" s="2">
+        <f>Q27*100</f>
+        <v>5.8754832421509828</v>
+      </c>
+      <c r="U28" t="s">
+        <v>6</v>
+      </c>
+      <c r="V28" s="2">
+        <f>V27*100</f>
+        <v>0.93273060292258969</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="33" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="K33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="P33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="U33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+    </row>
+    <row r="34" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2</v>
+      </c>
+      <c r="F34" t="s">
+        <v>0</v>
+      </c>
+      <c r="G34" t="s">
+        <v>4</v>
+      </c>
+      <c r="H34" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" t="s">
+        <v>2</v>
+      </c>
+      <c r="K34" t="s">
+        <v>0</v>
+      </c>
+      <c r="L34" t="s">
+        <v>4</v>
+      </c>
+      <c r="M34" t="s">
+        <v>3</v>
+      </c>
+      <c r="N34" t="s">
+        <v>2</v>
+      </c>
+      <c r="P34" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>4</v>
+      </c>
+      <c r="R34" t="s">
+        <v>3</v>
+      </c>
+      <c r="S34" t="s">
+        <v>2</v>
+      </c>
+      <c r="U34" t="s">
+        <v>0</v>
+      </c>
+      <c r="V34" t="s">
+        <v>4</v>
+      </c>
+      <c r="W34" t="s">
+        <v>3</v>
+      </c>
+      <c r="X34" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2">
+        <v>8.7264093000000003</v>
+      </c>
+      <c r="C35" s="2">
+        <f>10^(B35/20)</f>
+        <v>2.7309922330078882</v>
+      </c>
+      <c r="D35" s="2">
+        <f>C35^2</f>
+        <v>7.4583185767494111</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2">
+        <v>4.9325400000000004</v>
+      </c>
+      <c r="H35" s="2">
+        <f>10^(G35/20)</f>
+        <v>1.7645216851265479</v>
+      </c>
+      <c r="I35" s="2">
+        <f>H35^2</f>
+        <v>3.1135367772818325</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35" s="2">
+        <v>1.7835570000000001</v>
+      </c>
+      <c r="M35" s="2">
+        <f>10^(L35/20)</f>
+        <v>1.2279419885753484</v>
+      </c>
+      <c r="N35" s="2">
+        <f>M35^2</f>
+        <v>1.5078415273063812</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>0.51427613999999999</v>
+      </c>
+      <c r="R35" s="2">
+        <f>10^(Q35/20)</f>
+        <v>1.0609961475695531</v>
+      </c>
+      <c r="S35" s="2">
+        <f>R35^2</f>
+        <v>1.1257128251574329</v>
+      </c>
+      <c r="U35">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2">
+        <v>-2.5384099999999998</v>
+      </c>
+      <c r="W35" s="2">
+        <f>10^(V35/20)</f>
+        <v>0.74658541247913746</v>
+      </c>
+      <c r="X35" s="2">
+        <f>W35^2</f>
+        <v>0.55738977812664381</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2">
+        <v>4.2524160000000002</v>
+      </c>
+      <c r="C36" s="2">
+        <f t="shared" ref="C36:C42" si="20">10^(B36/20)</f>
+        <v>1.6316266867970712</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" ref="D36:D42" si="21">C36^2</f>
+        <v>2.6622056450683882</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2">
+        <v>-3.9363100000000002</v>
+      </c>
+      <c r="H36" s="2">
+        <f>10^(G36/20)</f>
+        <v>0.63560089489327276</v>
+      </c>
+      <c r="I36" s="2">
+        <f t="shared" ref="I36:I42" si="22">H36^2</f>
+        <v>0.40398849758912919</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36" s="2">
+        <v>-13.438800000000001</v>
+      </c>
+      <c r="M36" s="2">
+        <f>10^(L36/20)</f>
+        <v>0.21284330795679507</v>
+      </c>
+      <c r="N36" s="2">
+        <f t="shared" ref="N36:N42" si="23">M36^2</f>
+        <v>4.5302273741991105E-2</v>
+      </c>
+      <c r="P36">
+        <v>2</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>-24.62462</v>
+      </c>
+      <c r="R36" s="2">
+        <f t="shared" ref="R36:R42" si="24">10^(Q36/20)</f>
+        <v>5.8717695170362363E-2</v>
+      </c>
+      <c r="S36" s="2">
+        <f t="shared" ref="S36:S42" si="25">R36^2</f>
+        <v>3.4477677261195955E-3</v>
+      </c>
+      <c r="U36">
+        <v>2</v>
+      </c>
+      <c r="V36" s="2">
+        <v>-47.950449999999996</v>
+      </c>
+      <c r="W36" s="2">
+        <f t="shared" ref="W36:W42" si="26">10^(V36/20)</f>
+        <v>4.0038472459549114E-3</v>
+      </c>
+      <c r="X36" s="2">
+        <f t="shared" ref="X36:X42" si="27">W36^2</f>
+        <v>1.6030792768940728E-5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37" s="2">
+        <v>-5.9124749999999997</v>
+      </c>
+      <c r="C37" s="2">
+        <f t="shared" si="20"/>
+        <v>0.50626307188618402</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="21"/>
+        <v>0.25630229795563553</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" s="2">
+        <v>-22.321000000000002</v>
+      </c>
+      <c r="H37" s="2">
+        <f>10^(G37/20)</f>
+        <v>7.655084694182393E-2</v>
+      </c>
+      <c r="I37" s="2">
+        <f t="shared" si="22"/>
+        <v>5.8600321675105543E-3</v>
+      </c>
+      <c r="K37">
+        <v>3</v>
+      </c>
+      <c r="L37" s="2">
+        <v>-19.567900000000002</v>
+      </c>
+      <c r="M37" s="2">
+        <f>10^(L37/20)</f>
+        <v>0.10510055272648611</v>
+      </c>
+      <c r="N37" s="2">
+        <f t="shared" si="23"/>
+        <v>1.1046126183412887E-2</v>
+      </c>
+      <c r="P37">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>-26.244759999999999</v>
+      </c>
+      <c r="R37" s="2">
+        <f t="shared" si="24"/>
+        <v>4.8726139024904185E-2</v>
+      </c>
+      <c r="S37" s="2">
+        <f t="shared" si="25"/>
+        <v>2.3742366242742903E-3</v>
+      </c>
+      <c r="U37">
+        <v>3</v>
+      </c>
+      <c r="V37" s="2">
+        <v>-41.345280000000002</v>
+      </c>
+      <c r="W37" s="2">
+        <f t="shared" si="26"/>
+        <v>8.5651702526749647E-3</v>
+      </c>
+      <c r="X37" s="2">
+        <f t="shared" si="27"/>
+        <v>7.3362141457308113E-5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>4</v>
+      </c>
+      <c r="B38" s="2">
+        <v>-17.163319999999999</v>
+      </c>
+      <c r="C38" s="2">
+        <f t="shared" si="20"/>
+        <v>0.13862258716932108</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="21"/>
+        <v>1.9216221673516019E-2</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38" s="2">
+        <v>-18.847548</v>
+      </c>
+      <c r="H38" s="2">
+        <f>10^(G38/20)</f>
+        <v>0.11418856099286408</v>
+      </c>
+      <c r="I38" s="2">
+        <f t="shared" si="22"/>
+        <v>1.303902746162104E-2</v>
+      </c>
+      <c r="K38">
+        <v>4</v>
+      </c>
+      <c r="L38" s="2">
+        <v>-34.189619999999998</v>
+      </c>
+      <c r="M38" s="2">
+        <f>10^(L38/20)</f>
+        <v>1.952176138156932E-2</v>
+      </c>
+      <c r="N38" s="2">
+        <f t="shared" si="23"/>
+        <v>3.810991674389313E-4</v>
+      </c>
+      <c r="P38">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>-31.102039999999999</v>
+      </c>
+      <c r="R38" s="2">
+        <f t="shared" si="24"/>
+        <v>2.7854668867971395E-2</v>
+      </c>
+      <c r="S38" s="2">
+        <f t="shared" si="25"/>
+        <v>7.7588257774433489E-4</v>
+      </c>
+      <c r="U38">
+        <v>4</v>
+      </c>
+      <c r="V38" s="2">
+        <v>-55.475811999999998</v>
+      </c>
+      <c r="W38" s="2">
+        <f t="shared" si="26"/>
+        <v>1.6834855770393963E-3</v>
+      </c>
+      <c r="X38" s="2">
+        <f t="shared" si="27"/>
+        <v>2.8341236880996692E-6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>5</v>
+      </c>
+      <c r="B39" s="2">
+        <v>-12.8383</v>
+      </c>
+      <c r="C39" s="2">
+        <f t="shared" si="20"/>
+        <v>0.22807884236201659</v>
+      </c>
+      <c r="D39" s="2">
+        <f t="shared" si="21"/>
+        <v>5.2019958333197613E-2</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39" s="2">
+        <v>-27.135739999999998</v>
+      </c>
+      <c r="H39" s="2">
+        <f>10^(G39/20)</f>
+        <v>4.3975724177045733E-2</v>
+      </c>
+      <c r="I39" s="2">
+        <f t="shared" si="22"/>
+        <v>1.9338643168956046E-3</v>
+      </c>
+      <c r="K39">
+        <v>5</v>
+      </c>
+      <c r="L39" s="2">
+        <v>-33.874360000000003</v>
+      </c>
+      <c r="M39" s="2">
+        <f>10^(L39/20)</f>
+        <v>2.0243332102641398E-2</v>
+      </c>
+      <c r="N39" s="2">
+        <f t="shared" si="23"/>
+        <v>4.097924946178318E-4</v>
+      </c>
+      <c r="P39">
+        <v>5</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>-34.502673000000001</v>
+      </c>
+      <c r="R39" s="2">
+        <f t="shared" si="24"/>
+        <v>1.8830695035671519E-2</v>
+      </c>
+      <c r="S39" s="2">
+        <f t="shared" si="25"/>
+        <v>3.5459507552646402E-4</v>
+      </c>
+      <c r="U39">
+        <v>5</v>
+      </c>
+      <c r="V39" s="2">
+        <v>-43.596539999999997</v>
+      </c>
+      <c r="W39" s="2">
+        <f t="shared" si="26"/>
+        <v>6.6095668583314778E-3</v>
+      </c>
+      <c r="X39" s="2">
+        <f t="shared" si="27"/>
+        <v>4.3686374054753841E-5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>6</v>
+      </c>
+      <c r="B40" s="2">
+        <v>-26.64396</v>
+      </c>
+      <c r="C40" s="2">
+        <f t="shared" si="20"/>
+        <v>4.6537387568645443E-2</v>
+      </c>
+      <c r="D40" s="2">
+        <f t="shared" si="21"/>
+        <v>2.1657284417143153E-3</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40" s="2">
+        <v>-27.937923999999999</v>
+      </c>
+      <c r="H40" s="2">
+        <f>10^(G40/20)</f>
+        <v>4.0096253956376324E-2</v>
+      </c>
+      <c r="I40" s="2">
+        <f t="shared" si="22"/>
+        <v>1.6077095813342239E-3</v>
+      </c>
+      <c r="K40">
+        <v>6</v>
+      </c>
+      <c r="L40" s="2">
+        <v>-32.442239999999998</v>
+      </c>
+      <c r="M40" s="2">
+        <f>10^(L40/20)</f>
+        <v>2.3871955707789751E-2</v>
+      </c>
+      <c r="N40" s="2">
+        <f t="shared" si="23"/>
+        <v>5.6987026931467569E-4</v>
+      </c>
+      <c r="P40">
+        <v>6</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>-50.60031</v>
+      </c>
+      <c r="R40" s="2">
+        <f t="shared" si="24"/>
+        <v>2.9511038996851966E-3</v>
+      </c>
+      <c r="S40" s="2">
+        <f t="shared" si="25"/>
+        <v>8.709014226737175E-6</v>
+      </c>
+      <c r="U40">
+        <v>6</v>
+      </c>
+      <c r="V40" s="2">
+        <v>-67.411060000000006</v>
+      </c>
+      <c r="W40" s="2">
+        <f t="shared" si="26"/>
+        <v>4.2603668816662614E-4</v>
+      </c>
+      <c r="X40" s="2">
+        <f t="shared" si="27"/>
+        <v>1.8150725966398703E-7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>7</v>
+      </c>
+      <c r="B41" s="2">
+        <v>-21.305900000000001</v>
+      </c>
+      <c r="C41" s="2">
+        <f t="shared" si="20"/>
+        <v>8.6040910991310754E-2</v>
+      </c>
+      <c r="D41" s="2">
+        <f t="shared" si="21"/>
+        <v>7.40303836421466E-3</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41" s="2">
+        <v>-30.596299999999999</v>
+      </c>
+      <c r="H41" s="2">
+        <f>10^(G41/20)</f>
+        <v>2.9524666453826294E-2</v>
+      </c>
+      <c r="I41" s="2">
+        <f t="shared" si="22"/>
+        <v>8.717059292096957E-4</v>
+      </c>
+      <c r="K41">
+        <v>7</v>
+      </c>
+      <c r="L41" s="2">
+        <v>-43.529690000000002</v>
+      </c>
+      <c r="M41" s="2">
+        <f>10^(L41/20)</f>
+        <v>6.6606329271905506E-3</v>
+      </c>
+      <c r="N41" s="2">
+        <f t="shared" si="23"/>
+        <v>4.436403099077496E-5</v>
+      </c>
+      <c r="P41">
+        <v>7</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>-64.501450000000006</v>
+      </c>
+      <c r="R41" s="2">
+        <f t="shared" si="24"/>
+        <v>5.9556271352755323E-4</v>
+      </c>
+      <c r="S41" s="2">
+        <f t="shared" si="25"/>
+        <v>3.5469494574430246E-7</v>
+      </c>
+      <c r="U41">
+        <v>7</v>
+      </c>
+      <c r="V41" s="2">
+        <v>-45.820599999999999</v>
+      </c>
+      <c r="W41" s="2">
+        <f t="shared" si="26"/>
+        <v>5.1164649103207123E-3</v>
+      </c>
+      <c r="X41" s="2">
+        <f t="shared" si="27"/>
+        <v>2.6178213178543136E-5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>8</v>
+      </c>
+      <c r="B42" s="2">
+        <v>-24.253699999999998</v>
+      </c>
+      <c r="C42" s="2">
+        <f t="shared" si="20"/>
+        <v>6.1279469933498504E-2</v>
+      </c>
+      <c r="D42" s="2">
+        <f t="shared" si="21"/>
+        <v>3.7551734353305473E-3</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="G42" s="2">
+        <v>-35.761546000000003</v>
+      </c>
+      <c r="H42" s="2">
+        <f>10^(G42/20)</f>
+        <v>1.6290060603264447E-2</v>
+      </c>
+      <c r="I42" s="2">
+        <f t="shared" si="22"/>
+        <v>2.6536607445802845E-4</v>
+      </c>
+      <c r="K42">
+        <v>8</v>
+      </c>
+      <c r="L42" s="2">
+        <v>-43.648229999999998</v>
+      </c>
+      <c r="M42" s="2">
+        <f>10^(L42/20)</f>
+        <v>6.5703499262493798E-3</v>
+      </c>
+      <c r="N42" s="2">
+        <f t="shared" si="23"/>
+        <v>4.3169498153365231E-5</v>
+      </c>
+      <c r="P42">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>-42.891917999999997</v>
+      </c>
+      <c r="R42" s="2">
+        <f t="shared" si="24"/>
+        <v>7.1681007360048805E-3</v>
+      </c>
+      <c r="S42" s="2">
+        <f t="shared" si="25"/>
+        <v>5.1381668161513708E-5</v>
+      </c>
+      <c r="U42">
+        <v>8</v>
+      </c>
+      <c r="V42" s="2">
+        <v>-67.42407</v>
+      </c>
+      <c r="W42" s="2">
+        <f t="shared" si="26"/>
+        <v>4.2539903461908822E-4</v>
+      </c>
+      <c r="X42" s="2">
+        <f t="shared" si="27"/>
+        <v>1.8096433865485222E-7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" s="2">
+        <f>SQRT(SUM(D36:D42)/D35)</f>
+        <v>0.63454455632488627</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <f>SQRT(SUM(I36:I42)/I35)</f>
+        <v>0.37057377751390241</v>
+      </c>
+      <c r="K43" t="s">
+        <v>1</v>
+      </c>
+      <c r="L43" s="2">
+        <f>SQRT(SUM(N36:N42)/N35)</f>
+        <v>0.19578240263032307</v>
+      </c>
+      <c r="P43" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="2">
+        <f>SQRT(SUM(S36:S42)/S35)</f>
+        <v>7.892886612997603E-2</v>
+      </c>
+      <c r="U43" t="s">
+        <v>1</v>
+      </c>
+      <c r="V43" s="2">
+        <f>SQRT(SUM(X36:X42)/X35)</f>
+        <v>1.7072057335423756E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="2">
+        <f>B43*100</f>
+        <v>63.454455632488624</v>
+      </c>
+      <c r="F44" t="s">
+        <v>6</v>
+      </c>
+      <c r="G44" s="2">
+        <f>G43*100</f>
+        <v>37.057377751390241</v>
+      </c>
+      <c r="K44" t="s">
+        <v>6</v>
+      </c>
+      <c r="L44" s="2">
+        <f>L43*100</f>
+        <v>19.578240263032306</v>
+      </c>
+      <c r="P44" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q44" s="2">
+        <f>Q43*100</f>
+        <v>7.8928866129976027</v>
+      </c>
+      <c r="U44" t="s">
+        <v>6</v>
+      </c>
+      <c r="V44" s="2">
+        <f>V43*100</f>
+        <v>1.7072057335423756</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="49" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="K49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="P49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="U49" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1"/>
+      <c r="X49" s="1"/>
+    </row>
+    <row r="50" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2</v>
+      </c>
+      <c r="F50" t="s">
+        <v>0</v>
+      </c>
+      <c r="G50" t="s">
+        <v>4</v>
+      </c>
+      <c r="H50" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" t="s">
+        <v>2</v>
+      </c>
+      <c r="K50" t="s">
+        <v>0</v>
+      </c>
+      <c r="L50" t="s">
+        <v>4</v>
+      </c>
+      <c r="M50" t="s">
+        <v>3</v>
+      </c>
+      <c r="N50" t="s">
+        <v>2</v>
+      </c>
+      <c r="P50" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>4</v>
+      </c>
+      <c r="R50" t="s">
+        <v>3</v>
+      </c>
+      <c r="S50" t="s">
+        <v>2</v>
+      </c>
+      <c r="U50" t="s">
+        <v>0</v>
+      </c>
+      <c r="V50" t="s">
+        <v>4</v>
+      </c>
+      <c r="W50" t="s">
+        <v>3</v>
+      </c>
+      <c r="X50" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51" s="2">
+        <v>10.066017</v>
+      </c>
+      <c r="C51" s="2">
+        <f>10^(B51/20)</f>
+        <v>3.1864040837436325</v>
+      </c>
+      <c r="D51" s="2">
+        <f>C51^2</f>
+        <v>10.153170984898098</v>
+      </c>
+      <c r="F51">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2">
+        <f>10^(G51/20)</f>
+        <v>1</v>
+      </c>
+      <c r="I51" s="2">
+        <f>H51^2</f>
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2">
+        <v>4.7132839999999998</v>
+      </c>
+      <c r="M51" s="2">
+        <f>10^(L51/20)</f>
+        <v>1.7205377268786246</v>
+      </c>
+      <c r="N51" s="2">
+        <f>M51^2</f>
+        <v>2.9602500696126648</v>
+      </c>
+      <c r="P51">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>3.5412034000000001</v>
+      </c>
+      <c r="R51" s="2">
+        <f>10^(Q51/20)</f>
+        <v>1.5033502356433173</v>
+      </c>
+      <c r="S51" s="2">
+        <f>R51^2</f>
+        <v>2.2600619310088175</v>
+      </c>
+      <c r="U51">
+        <v>1</v>
+      </c>
+      <c r="V51" s="2">
+        <v>0.66674623</v>
+      </c>
+      <c r="W51" s="2">
+        <f>10^(V51/20)</f>
+        <v>1.0797850531861271</v>
+      </c>
+      <c r="X51" s="2">
+        <f>W51^2</f>
+        <v>1.1659357610841672</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>2</v>
+      </c>
+      <c r="B52" s="2">
+        <v>6.3832149999999999</v>
+      </c>
+      <c r="C52" s="2">
+        <f t="shared" ref="C52:C58" si="28">10^(B52/20)</f>
+        <v>2.0852625805163836</v>
+      </c>
+      <c r="D52" s="2">
+        <f t="shared" ref="D52:D58" si="29">C52^2</f>
+        <v>4.3483200297018474</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2">
+        <f t="shared" ref="H52:H58" si="30">10^(G52/20)</f>
+        <v>1</v>
+      </c>
+      <c r="I52" s="2">
+        <f t="shared" ref="I52:I58" si="31">H52^2</f>
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>2</v>
+      </c>
+      <c r="L52" s="2">
+        <v>-8.9661418000000008</v>
+      </c>
+      <c r="M52" s="2">
+        <f t="shared" ref="M52:M58" si="32">10^(L52/20)</f>
+        <v>0.3561991756148925</v>
+      </c>
+      <c r="N52" s="2">
+        <f t="shared" ref="N52:N58" si="33">M52^2</f>
+        <v>0.12687785270872903</v>
+      </c>
+      <c r="P52">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>-18.148479999999999</v>
+      </c>
+      <c r="R52" s="2">
+        <f t="shared" ref="R52:R58" si="34">10^(Q52/20)</f>
+        <v>0.12375877444696284</v>
+      </c>
+      <c r="S52" s="2">
+        <f t="shared" ref="S52:S58" si="35">R52^2</f>
+        <v>1.5316234252614223E-2</v>
+      </c>
+      <c r="U52">
+        <v>2</v>
+      </c>
+      <c r="V52" s="2">
+        <v>-34.361789999999999</v>
+      </c>
+      <c r="W52" s="2">
+        <f t="shared" ref="W52:W58" si="36">10^(V52/20)</f>
+        <v>1.9138614731915041E-2</v>
+      </c>
+      <c r="X52" s="2">
+        <f t="shared" ref="X52:X58" si="37">W52^2</f>
+        <v>3.662865738566754E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53" s="2">
+        <v>-1.3378989999999999</v>
+      </c>
+      <c r="C53" s="2">
+        <f t="shared" si="28"/>
+        <v>0.8572451762442691</v>
+      </c>
+      <c r="D53" s="2">
+        <f t="shared" si="29"/>
+        <v>0.73486929219406805</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="I53" s="2">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>3</v>
+      </c>
+      <c r="L53" s="2">
+        <v>-16.372800000000002</v>
+      </c>
+      <c r="M53" s="2">
+        <f t="shared" si="32"/>
+        <v>0.15183084183278672</v>
+      </c>
+      <c r="N53" s="2">
+        <f t="shared" si="33"/>
+        <v>2.3052604531652698E-2</v>
+      </c>
+      <c r="P53">
+        <v>3</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>-20.612100000000002</v>
+      </c>
+      <c r="R53" s="2">
+        <f t="shared" si="34"/>
+        <v>9.3195512297420985E-2</v>
+      </c>
+      <c r="S53" s="2">
+        <f t="shared" si="35"/>
+        <v>8.6854035123787466E-3</v>
+      </c>
+      <c r="U53">
+        <v>3</v>
+      </c>
+      <c r="V53" s="2">
+        <v>-32.015265999999997</v>
+      </c>
+      <c r="W53" s="2">
+        <f t="shared" si="36"/>
+        <v>2.5074755097236185E-2</v>
+      </c>
+      <c r="X53" s="2">
+        <f t="shared" si="37"/>
+        <v>6.2874334318637208E-4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54" s="2">
+        <v>-34.740749999999998</v>
+      </c>
+      <c r="C54" s="2">
+        <f t="shared" si="28"/>
+        <v>1.8321562144563951E-2</v>
+      </c>
+      <c r="D54" s="2">
+        <f t="shared" si="29"/>
+        <v>3.3567963941711878E-4</v>
+      </c>
+      <c r="F54">
+        <v>4</v>
+      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="I54" s="2">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>4</v>
+      </c>
+      <c r="L54" s="2">
+        <v>-50.403146999999997</v>
+      </c>
+      <c r="M54" s="2">
+        <f t="shared" si="32"/>
+        <v>3.0188577545561608E-3</v>
+      </c>
+      <c r="N54" s="2">
+        <f t="shared" si="33"/>
+        <v>9.1135021422438646E-6</v>
+      </c>
+      <c r="P54">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>-27.214974999999999</v>
+      </c>
+      <c r="R54" s="2">
+        <f t="shared" si="34"/>
+        <v>4.3576390087146852E-2</v>
+      </c>
+      <c r="S54" s="2">
+        <f t="shared" si="35"/>
+        <v>1.8989017730271904E-3</v>
+      </c>
+      <c r="U54">
+        <v>4</v>
+      </c>
+      <c r="V54" s="2">
+        <v>-39.060518000000002</v>
+      </c>
+      <c r="W54" s="2">
+        <f t="shared" si="36"/>
+        <v>1.114228082441481E-2</v>
+      </c>
+      <c r="X54" s="2">
+        <f t="shared" si="37"/>
+        <v>1.2415042197012197E-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>5</v>
+      </c>
+      <c r="B55" s="2">
+        <v>-10.686389999999999</v>
+      </c>
+      <c r="C55" s="2">
+        <f t="shared" si="28"/>
+        <v>0.29220019404117403</v>
+      </c>
+      <c r="D55" s="2">
+        <f t="shared" si="29"/>
+        <v>8.5380953397699758E-2</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="I55" s="2">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>5</v>
+      </c>
+      <c r="L55" s="2">
+        <v>-27.170342000000002</v>
+      </c>
+      <c r="M55" s="2">
+        <f t="shared" si="32"/>
+        <v>4.3800886457996166E-2</v>
+      </c>
+      <c r="N55" s="2">
+        <f t="shared" si="33"/>
+        <v>1.9185176545062719E-3</v>
+      </c>
+      <c r="P55">
+        <v>5</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>-33.5154</v>
+      </c>
+      <c r="R55" s="2">
+        <f t="shared" si="34"/>
+        <v>2.1097451637106794E-2</v>
+      </c>
+      <c r="S55" s="2">
+        <f t="shared" si="35"/>
+        <v>4.4510246558006014E-4</v>
+      </c>
+      <c r="U55">
+        <v>5</v>
+      </c>
+      <c r="V55" s="2">
+        <v>-35.405248999999998</v>
+      </c>
+      <c r="W55" s="2">
+        <f t="shared" si="36"/>
+        <v>1.6972176910005642E-2</v>
+      </c>
+      <c r="X55" s="2">
+        <f t="shared" si="37"/>
+        <v>2.8805478906452866E-4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>6</v>
+      </c>
+      <c r="B56" s="2">
+        <v>-14.70834</v>
+      </c>
+      <c r="C56" s="2">
+        <f t="shared" si="28"/>
+        <v>0.18390053809907606</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" si="29"/>
+        <v>3.381940791312972E-2</v>
+      </c>
+      <c r="F56">
+        <v>6</v>
+      </c>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="I56" s="2">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>6</v>
+      </c>
+      <c r="L56" s="2">
+        <v>-29.822600000000001</v>
+      </c>
+      <c r="M56" s="2">
+        <f t="shared" si="32"/>
+        <v>3.2275278616212232E-2</v>
+      </c>
+      <c r="N56" s="2">
+        <f t="shared" si="33"/>
+        <v>1.0416936097541265E-3</v>
+      </c>
+      <c r="P56">
+        <v>6</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>-41.634569999999997</v>
+      </c>
+      <c r="R56" s="2">
+        <f t="shared" si="34"/>
+        <v>8.2845991510970794E-3</v>
+      </c>
+      <c r="S56" s="2">
+        <f t="shared" si="35"/>
+        <v>6.8634583094358449E-5</v>
+      </c>
+      <c r="U56">
+        <v>6</v>
+      </c>
+      <c r="V56" s="2">
+        <v>-47.333219999999997</v>
+      </c>
+      <c r="W56" s="2">
+        <f t="shared" si="36"/>
+        <v>4.2987184363179618E-3</v>
+      </c>
+      <c r="X56" s="2">
+        <f t="shared" si="37"/>
+        <v>1.8478980194739941E-5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57" s="2">
+        <v>-34.294128999999998</v>
+      </c>
+      <c r="C57" s="2">
+        <f t="shared" si="28"/>
+        <v>1.9288282136753567E-2</v>
+      </c>
+      <c r="D57" s="2">
+        <f t="shared" si="29"/>
+        <v>3.7203782778700678E-4</v>
+      </c>
+      <c r="F57">
+        <v>7</v>
+      </c>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="I57" s="2">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>7</v>
+      </c>
+      <c r="L57" s="2">
+        <v>-45.264719999999997</v>
+      </c>
+      <c r="M57" s="2">
+        <f t="shared" si="32"/>
+        <v>5.454613713323099E-3</v>
+      </c>
+      <c r="N57" s="2">
+        <f t="shared" si="33"/>
+        <v>2.9752810761572407E-5</v>
+      </c>
+      <c r="P57">
+        <v>7</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>-42.151352000000003</v>
+      </c>
+      <c r="R57" s="2">
+        <f t="shared" si="34"/>
+        <v>7.8060692550336363E-3</v>
+      </c>
+      <c r="S57" s="2">
+        <f t="shared" si="35"/>
+        <v>6.0934717214381387E-5</v>
+      </c>
+      <c r="U57">
+        <v>7</v>
+      </c>
+      <c r="V57" s="2">
+        <v>-40.07349</v>
+      </c>
+      <c r="W57" s="2">
+        <f t="shared" si="36"/>
+        <v>9.9157484332487635E-3</v>
+      </c>
+      <c r="X57" s="2">
+        <f t="shared" si="37"/>
+        <v>9.8322066991475313E-5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>8</v>
+      </c>
+      <c r="B58" s="2">
+        <v>-19.902857000000001</v>
+      </c>
+      <c r="C58" s="2">
+        <f t="shared" si="28"/>
+        <v>0.1011246775931692</v>
+      </c>
+      <c r="D58" s="2">
+        <f t="shared" si="29"/>
+        <v>1.0226200418322418E-2</v>
+      </c>
+      <c r="F58">
+        <v>8</v>
+      </c>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="I58" s="2">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+      <c r="K58">
+        <v>8</v>
+      </c>
+      <c r="L58" s="2">
+        <v>-35.542929999999998</v>
+      </c>
+      <c r="M58" s="2">
+        <f t="shared" si="32"/>
+        <v>1.6705270025258196E-2</v>
+      </c>
+      <c r="N58" s="2">
+        <f t="shared" si="33"/>
+        <v>2.7906604661678998E-4</v>
+      </c>
+      <c r="P58">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>-36.452325000000002</v>
+      </c>
+      <c r="R58" s="2">
+        <f t="shared" si="34"/>
+        <v>1.5044707549126774E-2</v>
+      </c>
+      <c r="S58" s="2">
+        <f t="shared" si="35"/>
+        <v>2.2634322523875215E-4</v>
+      </c>
+      <c r="U58">
+        <v>8</v>
+      </c>
+      <c r="V58" s="2">
+        <v>-60.536642000000001</v>
+      </c>
+      <c r="W58" s="2">
+        <f t="shared" si="36"/>
+        <v>9.4008668162610552E-4</v>
+      </c>
+      <c r="X58" s="2">
+        <f t="shared" si="37"/>
+        <v>8.837629689707827E-7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" s="2">
+        <f>SQRT(SUM(D52:D58)/D51)</f>
+        <v>0.71656648499661879</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2">
+        <f>SQRT(SUM(I52:I58)/I51)</f>
+        <v>2.6457513110645907</v>
+      </c>
+      <c r="K59" t="s">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2">
+        <f>SQRT(SUM(N52:N58)/N51)</f>
+        <v>0.22749789012894206</v>
+      </c>
+      <c r="P59" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="2">
+        <f>SQRT(SUM(S52:S58)/S51)</f>
+        <v>0.10869463364035319</v>
+      </c>
+      <c r="U59" t="s">
+        <v>1</v>
+      </c>
+      <c r="V59" s="2">
+        <f>SQRT(SUM(X52:X58)/X51)</f>
+        <v>3.6164811843770912E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="2">
+        <f>B59*100</f>
+        <v>71.656648499661884</v>
+      </c>
+      <c r="F60" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="2">
+        <f>G59*100</f>
+        <v>264.57513110645908</v>
+      </c>
+      <c r="K60" t="s">
+        <v>6</v>
+      </c>
+      <c r="L60" s="2">
+        <f>L59*100</f>
+        <v>22.749789012894205</v>
+      </c>
+      <c r="P60" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q60" s="2">
+        <f>Q59*100</f>
+        <v>10.869463364035319</v>
+      </c>
+      <c r="U60" t="s">
+        <v>6</v>
+      </c>
+      <c r="V60" s="2">
+        <f>V59*100</f>
+        <v>3.6164811843770912</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="65" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="F65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="K65" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="P65" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q65" s="1"/>
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="U65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+    </row>
+    <row r="66" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2</v>
+      </c>
+      <c r="F66" t="s">
+        <v>0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" t="s">
+        <v>2</v>
+      </c>
+      <c r="K66" t="s">
+        <v>0</v>
+      </c>
+      <c r="L66" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" t="s">
+        <v>2</v>
+      </c>
+      <c r="P66" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" t="s">
+        <v>2</v>
+      </c>
+      <c r="U66" t="s">
+        <v>0</v>
+      </c>
+      <c r="V66" t="s">
+        <v>4</v>
+      </c>
+      <c r="W66" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>1</v>
+      </c>
+      <c r="B67" s="2">
+        <v>10.213380000000001</v>
+      </c>
+      <c r="C67" s="2">
+        <f>10^(B67/20)</f>
+        <v>3.2409251424982437</v>
+      </c>
+      <c r="D67" s="2">
+        <f>C67^2</f>
+        <v>10.503595779277262</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2">
+        <v>7.6886840000000003</v>
+      </c>
+      <c r="H67" s="2">
+        <f>10^(G67/20)</f>
+        <v>2.4234507594729195</v>
+      </c>
+      <c r="I67" s="2">
+        <f>H67^2</f>
+        <v>5.8731135835898707</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2">
+        <v>9.7336778000000006</v>
+      </c>
+      <c r="M67" s="2">
+        <f>10^(L67/20)</f>
+        <v>3.0667889516022617</v>
+      </c>
+      <c r="N67" s="2">
+        <f>M67^2</f>
+        <v>9.4051944736696989</v>
+      </c>
+      <c r="P67">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>3.9975963000000001</v>
+      </c>
+      <c r="R67" s="2">
+        <f>10^(Q67/20)</f>
+        <v>1.5844546558406989</v>
+      </c>
+      <c r="S67" s="2">
+        <f>R67^2</f>
+        <v>2.5104965564152675</v>
+      </c>
+      <c r="U67">
+        <v>1</v>
+      </c>
+      <c r="V67" s="2">
+        <v>1.1579819</v>
+      </c>
+      <c r="W67" s="2">
+        <f>10^(V67/20)</f>
+        <v>1.142612826598657</v>
+      </c>
+      <c r="X67" s="2">
+        <f>W67^2</f>
+        <v>1.3055640715077728</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>2</v>
+      </c>
+      <c r="B68" s="2">
+        <v>6.6581945999999999</v>
+      </c>
+      <c r="C68" s="2">
+        <f t="shared" ref="C68:C74" si="38">10^(B68/20)</f>
+        <v>2.152334316163111</v>
+      </c>
+      <c r="D68" s="2">
+        <f t="shared" ref="D68:D74" si="39">C68^2</f>
+        <v>4.632543008533327</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68" s="2">
+        <v>-3.8390048999999999</v>
+      </c>
+      <c r="H68" s="2">
+        <f t="shared" ref="H68:H74" si="40">10^(G68/20)</f>
+        <v>0.64276135113116617</v>
+      </c>
+      <c r="I68" s="2">
+        <f t="shared" ref="I68:I74" si="41">H68^2</f>
+        <v>0.41314215450796227</v>
+      </c>
+      <c r="K68">
+        <v>2</v>
+      </c>
+      <c r="L68" s="2">
+        <v>3.2868900000000001</v>
+      </c>
+      <c r="M68" s="2">
+        <f t="shared" ref="M68:M74" si="42">10^(L68/20)</f>
+        <v>1.4599719100093851</v>
+      </c>
+      <c r="N68" s="2">
+        <f t="shared" ref="N68:N74" si="43">M68^2</f>
+        <v>2.1315179780164519</v>
+      </c>
+      <c r="P68">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>-17.12059</v>
+      </c>
+      <c r="R68" s="2">
+        <f t="shared" ref="R68:R74" si="44">10^(Q68/20)</f>
+        <v>0.13930621742276703</v>
+      </c>
+      <c r="S68" s="2">
+        <f t="shared" ref="S68:S74" si="45">R68^2</f>
+        <v>1.940622221263924E-2</v>
+      </c>
+      <c r="U68">
+        <v>2</v>
+      </c>
+      <c r="V68" s="2">
+        <v>-32.539209999999997</v>
+      </c>
+      <c r="W68" s="2">
+        <f t="shared" ref="W68:W74" si="46">10^(V68/20)</f>
+        <v>2.3606929334228362E-2</v>
+      </c>
+      <c r="X68" s="2">
+        <f t="shared" ref="X68:X74" si="47">W68^2</f>
+        <v>5.5728711259125159E-4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>3</v>
+      </c>
+      <c r="B69" s="2">
+        <v>-0.71119622999999998</v>
+      </c>
+      <c r="C69" s="2">
+        <f t="shared" si="38"/>
+        <v>0.92138298614742209</v>
+      </c>
+      <c r="D69" s="2">
+        <f t="shared" si="39"/>
+        <v>0.84894660716194059</v>
+      </c>
+      <c r="F69">
+        <v>3</v>
+      </c>
+      <c r="G69" s="2">
+        <v>-14.001612</v>
+      </c>
+      <c r="H69" s="2">
+        <f t="shared" si="40"/>
+        <v>0.19948920518704</v>
+      </c>
+      <c r="I69" s="2">
+        <f t="shared" si="41"/>
+        <v>3.9795942986156949E-2</v>
+      </c>
+      <c r="K69">
+        <v>3</v>
+      </c>
+      <c r="L69" s="2">
+        <v>-17.306818</v>
+      </c>
+      <c r="M69" s="2">
+        <f t="shared" si="42"/>
+        <v>0.13635124256218747</v>
+      </c>
+      <c r="N69" s="2">
+        <f t="shared" si="43"/>
+        <v>1.8591661348252485E-2</v>
+      </c>
+      <c r="P69">
+        <v>3</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>-19.760771999999999</v>
+      </c>
+      <c r="R69" s="2">
+        <f t="shared" si="44"/>
+        <v>0.1027924932319688</v>
+      </c>
+      <c r="S69" s="2">
+        <f t="shared" si="45"/>
+        <v>1.0566296664844353E-2</v>
+      </c>
+      <c r="U69">
+        <v>3</v>
+      </c>
+      <c r="V69" s="2">
+        <v>-30.609535000000001</v>
+      </c>
+      <c r="W69" s="2">
+        <f t="shared" si="46"/>
+        <v>2.9479712923301316E-2</v>
+      </c>
+      <c r="X69" s="2">
+        <f t="shared" si="47"/>
+        <v>8.690534740402586E-4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>4</v>
+      </c>
+      <c r="B70" s="2">
+        <v>-27.195322000000001</v>
+      </c>
+      <c r="C70" s="2">
+        <f t="shared" si="38"/>
+        <v>4.3675099192299137E-2</v>
+      </c>
+      <c r="D70" s="2">
+        <f t="shared" si="39"/>
+        <v>1.9075142894571686E-3</v>
+      </c>
+      <c r="F70">
+        <v>4</v>
+      </c>
+      <c r="G70" s="2">
+        <v>-23.803443999999999</v>
+      </c>
+      <c r="H70" s="2">
+        <f t="shared" si="40"/>
+        <v>6.4539827455276713E-2</v>
+      </c>
+      <c r="I70" s="2">
+        <f t="shared" si="41"/>
+        <v>4.1653893279568902E-3</v>
+      </c>
+      <c r="K70">
+        <v>4</v>
+      </c>
+      <c r="L70" s="2">
+        <v>-10.96701</v>
+      </c>
+      <c r="M70" s="2">
+        <f t="shared" si="42"/>
+        <v>0.2829107825538919</v>
+      </c>
+      <c r="N70" s="2">
+        <f t="shared" si="43"/>
+        <v>8.0038510885255501E-2</v>
+      </c>
+      <c r="P70">
+        <v>4</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>-26.777850000000001</v>
+      </c>
+      <c r="R70" s="2">
+        <f t="shared" si="44"/>
+        <v>4.5825530364885549E-2</v>
+      </c>
+      <c r="S70" s="2">
+        <f t="shared" si="45"/>
+        <v>2.0999792332230473E-3</v>
+      </c>
+      <c r="U70">
+        <v>4</v>
+      </c>
+      <c r="V70" s="2">
+        <v>-37.325380000000003</v>
+      </c>
+      <c r="W70" s="2">
+        <f t="shared" si="46"/>
+        <v>1.3606016710115248E-2</v>
+      </c>
+      <c r="X70" s="2">
+        <f t="shared" si="47"/>
+        <v>1.8512369071593536E-4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71" s="2">
+        <v>-10.644600000000001</v>
+      </c>
+      <c r="C71" s="2">
+        <f t="shared" si="38"/>
+        <v>0.29360943005423967</v>
+      </c>
+      <c r="D71" s="2">
+        <f t="shared" si="39"/>
+        <v>8.6206497416775454E-2</v>
+      </c>
+      <c r="F71">
+        <v>5</v>
+      </c>
+      <c r="G71" s="2">
+        <v>-21.88279</v>
+      </c>
+      <c r="H71" s="2">
+        <f t="shared" si="40"/>
+        <v>8.0511978663377406E-2</v>
+      </c>
+      <c r="I71" s="2">
+        <f t="shared" si="41"/>
+        <v>6.4821787082921384E-3</v>
+      </c>
+      <c r="K71">
+        <v>5</v>
+      </c>
+      <c r="L71" s="2">
+        <v>-20.722280000000001</v>
+      </c>
+      <c r="M71" s="2">
+        <f t="shared" si="42"/>
+        <v>9.2020799032672421E-2</v>
+      </c>
+      <c r="N71" s="2">
+        <f t="shared" si="43"/>
+        <v>8.4678274546114863E-3</v>
+      </c>
+      <c r="P71">
+        <v>5</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>-33.885595000000002</v>
+      </c>
+      <c r="R71" s="2">
+        <f t="shared" si="44"/>
+        <v>2.0217164741691072E-2</v>
+      </c>
+      <c r="S71" s="2">
+        <f t="shared" si="45"/>
+        <v>4.0873375019267663E-4</v>
+      </c>
+      <c r="U71">
+        <v>5</v>
+      </c>
+      <c r="V71" s="2">
+        <v>-34.319760000000002</v>
+      </c>
+      <c r="W71" s="2">
+        <f t="shared" si="46"/>
+        <v>1.923144866632448E-2</v>
+      </c>
+      <c r="X71" s="2">
+        <f t="shared" si="47"/>
+        <v>3.698486178054736E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>6</v>
+      </c>
+      <c r="B72" s="2">
+        <v>-13.612009</v>
+      </c>
+      <c r="C72" s="2">
+        <f t="shared" si="38"/>
+        <v>0.20864094927009671</v>
+      </c>
+      <c r="D72" s="2">
+        <f t="shared" si="39"/>
+        <v>4.353104571232707E-2</v>
+      </c>
+      <c r="F72">
+        <v>6</v>
+      </c>
+      <c r="G72" s="2">
+        <v>-34.39678</v>
+      </c>
+      <c r="H72" s="2">
+        <f t="shared" si="40"/>
+        <v>1.9061672340701982E-2</v>
+      </c>
+      <c r="I72" s="2">
+        <f t="shared" si="41"/>
+        <v>3.6334735242428298E-4</v>
+      </c>
+      <c r="K72">
+        <v>6</v>
+      </c>
+      <c r="L72" s="2">
+        <v>-20.412289999999999</v>
+      </c>
+      <c r="M72" s="2">
+        <f t="shared" si="42"/>
+        <v>9.5364228572764248E-2</v>
+      </c>
+      <c r="N72" s="2">
+        <f t="shared" si="43"/>
+        <v>9.0943360912784255E-3</v>
+      </c>
+      <c r="P72">
+        <v>6</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>-38.725464000000002</v>
+      </c>
+      <c r="R72" s="2">
+        <f t="shared" si="44"/>
+        <v>1.1580486376622446E-2</v>
+      </c>
+      <c r="S72" s="2">
+        <f t="shared" si="45"/>
+        <v>1.3410766471913806E-4</v>
+      </c>
+      <c r="U72">
+        <v>6</v>
+      </c>
+      <c r="V72" s="2">
+        <v>-46.315759999999997</v>
+      </c>
+      <c r="W72" s="2">
+        <f t="shared" si="46"/>
+        <v>4.8329466381010211E-3</v>
+      </c>
+      <c r="X72" s="2">
+        <f t="shared" si="47"/>
+        <v>2.3357373206731961E-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <v>7</v>
+      </c>
+      <c r="B73" s="2">
+        <v>-51.453702999999997</v>
+      </c>
+      <c r="C73" s="2">
+        <f t="shared" si="38"/>
+        <v>2.6749449578323142E-3</v>
+      </c>
+      <c r="D73" s="2">
+        <f t="shared" si="39"/>
+        <v>7.1553305274325207E-6</v>
+      </c>
+      <c r="F73">
+        <v>7</v>
+      </c>
+      <c r="G73" s="2">
+        <v>-27.474930000000001</v>
+      </c>
+      <c r="H73" s="2">
+        <f t="shared" si="40"/>
+        <v>4.2291540020292617E-2</v>
+      </c>
+      <c r="I73" s="2">
+        <f t="shared" si="41"/>
+        <v>1.7885743572880121E-3</v>
+      </c>
+      <c r="K73">
+        <v>7</v>
+      </c>
+      <c r="L73" s="2">
+        <v>-26.607890000000001</v>
+      </c>
+      <c r="M73" s="2">
+        <f t="shared" si="42"/>
+        <v>4.6731045771555117E-2</v>
+      </c>
+      <c r="N73" s="2">
+        <f t="shared" si="43"/>
+        <v>2.1837906389031796E-3</v>
+      </c>
+      <c r="P73">
+        <v>7</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>-40.383141999999999</v>
+      </c>
+      <c r="R73" s="2">
+        <f t="shared" si="44"/>
+        <v>9.5684788224553296E-3</v>
+      </c>
+      <c r="S73" s="2">
+        <f t="shared" si="45"/>
+        <v>9.1555786975776131E-5</v>
+      </c>
+      <c r="U73">
+        <v>7</v>
+      </c>
+      <c r="V73" s="2">
+        <v>-39.640098999999999</v>
+      </c>
+      <c r="W73" s="2">
+        <f t="shared" si="46"/>
+        <v>1.0423055493393609E-2</v>
+      </c>
+      <c r="X73" s="2">
+        <f t="shared" si="47"/>
+        <v>1.086400858183627E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>8</v>
+      </c>
+      <c r="B74" s="2">
+        <v>-19.997854</v>
+      </c>
+      <c r="C74" s="2">
+        <f t="shared" si="38"/>
+        <v>0.10002470979041372</v>
+      </c>
+      <c r="D74" s="2">
+        <f t="shared" si="39"/>
+        <v>1.0004942568656488E-2</v>
+      </c>
+      <c r="F74">
+        <v>8</v>
+      </c>
+      <c r="G74" s="2">
+        <v>-34.282798</v>
+      </c>
+      <c r="H74" s="2">
+        <f t="shared" si="40"/>
+        <v>1.9313460690947599E-2</v>
+      </c>
+      <c r="I74" s="2">
+        <f t="shared" si="41"/>
+        <v>3.7300976386077812E-4</v>
+      </c>
+      <c r="K74">
+        <v>8</v>
+      </c>
+      <c r="L74" s="2">
+        <v>-24.836721000000001</v>
+      </c>
+      <c r="M74" s="2">
+        <f t="shared" si="42"/>
+        <v>5.7301230736357414E-2</v>
+      </c>
+      <c r="N74" s="2">
+        <f t="shared" si="43"/>
+        <v>3.2834310439012718E-3</v>
+      </c>
+      <c r="P74">
+        <v>8</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>-35.942659999999997</v>
+      </c>
+      <c r="R74" s="2">
+        <f t="shared" si="44"/>
+        <v>1.5953904939419682E-2</v>
+      </c>
+      <c r="S74" s="2">
+        <f t="shared" si="45"/>
+        <v>2.5452708281603972E-4</v>
+      </c>
+      <c r="U74">
+        <v>8</v>
+      </c>
+      <c r="V74" s="2">
+        <v>-55.865409999999997</v>
+      </c>
+      <c r="W74" s="2">
+        <f t="shared" si="46"/>
+        <v>1.6096427580770041E-3</v>
+      </c>
+      <c r="X74" s="2">
+        <f t="shared" si="47"/>
+        <v>2.5909498086297447E-6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>1</v>
+      </c>
+      <c r="B75" s="2">
+        <f>SQRT(SUM(D68:D74)/D67)</f>
+        <v>0.73167920075383452</v>
+      </c>
+      <c r="F75" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2">
+        <f>SQRT(SUM(I68:I74)/I67)</f>
+        <v>0.2817152053786387</v>
+      </c>
+      <c r="K75" t="s">
+        <v>1</v>
+      </c>
+      <c r="L75" s="2">
+        <f>SQRT(SUM(N68:N74)/N67)</f>
+        <v>0.48945617989768869</v>
+      </c>
+      <c r="P75" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="2">
+        <f>SQRT(SUM(S68:S74)/S67)</f>
+        <v>0.11458378323700356</v>
+      </c>
+      <c r="U75" t="s">
+        <v>1</v>
+      </c>
+      <c r="V75" s="2">
+        <f>SQRT(SUM(X68:X74)/X67)</f>
+        <v>4.0257667456496685E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="2">
+        <f>B75*100</f>
+        <v>73.167920075383449</v>
+      </c>
+      <c r="F76" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="2">
+        <f>G75*100</f>
+        <v>28.17152053786387</v>
+      </c>
+      <c r="K76" t="s">
+        <v>6</v>
+      </c>
+      <c r="L76" s="2">
+        <f>L75*100</f>
+        <v>48.94561798976887</v>
+      </c>
+      <c r="P76" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q76" s="2">
+        <f>Q75*100</f>
+        <v>11.458378323700357</v>
+      </c>
+      <c r="U76" t="s">
+        <v>6</v>
+      </c>
+      <c r="V76" s="2">
+        <f>V75*100</f>
+        <v>4.0257667456496682</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -543,30 +4345,33 @@
     <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB168559-730A-4F75-AB40-09C18ACC4F80}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="11.73046875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A9" s="1"/>
-    </row>
-  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="K65:N65"/>
+    <mergeCell ref="P65:S65"/>
+    <mergeCell ref="U65:X65"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="P33:S33"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="F49:I49"/>
+    <mergeCell ref="K49:N49"/>
+    <mergeCell ref="P49:S49"/>
+    <mergeCell ref="U49:X49"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="U17:X17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/EXCEL FILEOVI/ZAVRSNI EXCEL - SIM RESULTS .xlsx
+++ b/EXCEL FILEOVI/ZAVRSNI EXCEL - SIM RESULTS .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/523341E057C2D1B5/Documents/2526 - LJETNI SEMESTAR/ZAVRŠNI RAD 2026/EXCEL FILEOVI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/523341E057C2D1B5/Documents/2526 - LJETNI SEMESTAR/Bachelor-Thesis/EXCEL FILEOVI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1402" documentId="8_{749E225B-507B-4645-922D-F24EE2B83FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F6582BD-CA3B-40DA-954D-316EB031F865}"/>
+  <xr:revisionPtr revIDLastSave="1420" documentId="8_{749E225B-507B-4645-922D-F24EE2B83FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE654EA-1992-46BF-950F-FF4E50D62520}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5A5A50C3-7C6B-466F-847F-D23E3D13151B}"/>
   </bookViews>
@@ -145,7 +145,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -178,10 +178,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,36 +551,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="K1" s="1" t="s">
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="P1" s="1" t="s">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="P1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="U1" s="1" t="s">
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="U1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
     </row>
     <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
@@ -648,70 +648,70 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>9.7472340000000006</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <f>10^(B3/20)</f>
         <v>3.0715790727751315</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <f>C3^2</f>
         <v>9.4345980003101371</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>8.9462379999999992</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <f>10^(G3/20)</f>
         <v>2.8009922036538724</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <f>H3^2</f>
         <v>7.8455573249297759</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>6.601788</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <f>10^(L3/20)</f>
         <v>2.1384022366665874</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="1">
         <f>M3^2</f>
         <v>4.5727641257806635</v>
       </c>
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>2.6878380000000002</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <f>10^(Q3/20)</f>
         <v>1.362673781611937</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <f>R3^2</f>
         <v>1.8568798350925768</v>
       </c>
       <c r="U3">
         <v>1</v>
       </c>
-      <c r="V3" s="2">
+      <c r="V3" s="1">
         <v>-0.24507419999999999</v>
       </c>
-      <c r="W3" s="2">
+      <c r="W3" s="1">
         <f>10^(V3/20)</f>
         <v>0.97217912163703113</v>
       </c>
-      <c r="X3" s="2">
+      <c r="X3" s="1">
         <f>W3^2</f>
         <v>0.94513224454694933</v>
       </c>
@@ -720,71 +720,71 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>5.8321823999999998</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <f t="shared" ref="C4:C10" si="0">10^(B4/20)</f>
         <v>1.9570824389506696</v>
       </c>
-      <c r="D4" s="2">
-        <f t="shared" ref="D4:D12" si="1">C4^2</f>
+      <c r="D4" s="1">
+        <f t="shared" ref="D4:D10" si="1">C4^2</f>
         <v>3.8301716728491013</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>1.93266</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <f t="shared" ref="H4:H10" si="2">10^(G4/20)</f>
         <v>1.2492029466970178</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <f t="shared" ref="I4:I10" si="3">H4^2</f>
         <v>1.5605080020365123</v>
       </c>
       <c r="K4">
         <v>2</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="1">
         <v>-5.7993300000000003</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="1">
         <f t="shared" ref="M4:M10" si="4">10^(L4/20)</f>
         <v>0.51290094590092872</v>
       </c>
-      <c r="N4" s="2">
-        <f t="shared" ref="N4:N12" si="5">M4^2</f>
+      <c r="N4" s="1">
+        <f t="shared" ref="N4:N10" si="5">M4^2</f>
         <v>0.26306738030606741</v>
       </c>
       <c r="P4">
         <v>2</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
         <v>-20.03003</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="1">
         <f t="shared" ref="R4:R10" si="6">10^(Q4/20)</f>
         <v>9.9654863817176587E-2</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="1">
         <f t="shared" ref="S4:S10" si="7">R4^2</f>
         <v>9.9310918824200116E-3</v>
       </c>
       <c r="U4">
         <v>2</v>
       </c>
-      <c r="V4" s="2">
+      <c r="V4" s="1">
         <v>-37.879820000000002</v>
       </c>
-      <c r="W4" s="2">
+      <c r="W4" s="1">
         <f t="shared" ref="W4:W10" si="8">10^(V4/20)</f>
         <v>1.2764652610661897E-2</v>
       </c>
-      <c r="X4" s="2">
-        <f t="shared" ref="X4:X12" si="9">W4^2</f>
+      <c r="X4" s="1">
+        <f t="shared" ref="X4:X10" si="9">W4^2</f>
         <v>1.629363562708776E-4</v>
       </c>
     </row>
@@ -792,70 +792,70 @@
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>-2.5565099999999998</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>0.74503126815571452</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <f t="shared" si="1"/>
         <v>0.55507159052971222</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>-26.298290000000001</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <f t="shared" si="2"/>
         <v>4.8426769647804124E-2</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <f t="shared" si="3"/>
         <v>2.3451520185214826E-3</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="1">
         <v>-14.659330000000001</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="1">
         <f t="shared" si="4"/>
         <v>0.18494112707747365</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="1">
         <f t="shared" si="5"/>
         <v>3.4203220484686256E-2</v>
       </c>
       <c r="P5">
         <v>3</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
         <v>-22.202839999999998</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="1">
         <f t="shared" si="6"/>
         <v>7.759933508619081E-2</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="1">
         <f t="shared" si="7"/>
         <v>6.021656805818924E-3</v>
       </c>
       <c r="U5">
         <v>3</v>
       </c>
-      <c r="V5" s="2">
+      <c r="V5" s="1">
         <v>-34.638710000000003</v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5" s="1">
         <f t="shared" si="8"/>
         <v>1.8538069243291141E-2</v>
       </c>
-      <c r="X5" s="2">
+      <c r="X5" s="1">
         <f t="shared" si="9"/>
         <v>3.43660011269057E-4</v>
       </c>
@@ -864,70 +864,70 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>-25.062999999999999</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>5.5827733927191446E-2</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <f t="shared" si="1"/>
         <v>3.1167358754452829E-3</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>-11.9879</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <f t="shared" si="2"/>
         <v>0.25153880884721458</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="1">
         <f t="shared" si="3"/>
         <v>6.3271772356275555E-2</v>
       </c>
       <c r="K6">
         <v>4</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="1">
         <v>-30.51709</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="1">
         <f t="shared" si="4"/>
         <v>2.979514477441499E-2</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="1">
         <f t="shared" si="5"/>
         <v>8.8775065212834891E-4</v>
       </c>
       <c r="P6">
         <v>4</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="1">
         <v>-28.17287</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="1">
         <f t="shared" si="6"/>
         <v>3.9026221038674994E-2</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="1">
         <f t="shared" si="7"/>
         <v>1.5230459285595188E-3</v>
       </c>
       <c r="U6">
         <v>4</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6" s="1">
         <v>-42.636589999999998</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6" s="1">
         <f t="shared" si="8"/>
         <v>7.3819398138351153E-3</v>
       </c>
-      <c r="X6" s="2">
+      <c r="X6" s="1">
         <f t="shared" si="9"/>
         <v>5.4493035415084014E-5</v>
       </c>
@@ -936,70 +936,70 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>-11.007</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>0.28161124979805008</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <f t="shared" si="1"/>
         <v>7.9304896012819759E-2</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>-28.661259999999999</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <f t="shared" si="2"/>
         <v>3.6892407750616203E-2</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="1">
         <f t="shared" si="3"/>
         <v>1.3610497496377265E-3</v>
       </c>
       <c r="K7">
         <v>5</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="1">
         <v>-23.499700000000001</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="1">
         <f t="shared" si="4"/>
         <v>6.6836700174838559E-2</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="1">
         <f t="shared" si="5"/>
         <v>4.4671444902612649E-3</v>
       </c>
       <c r="P7">
         <v>5</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="1">
         <v>-33.332484000000001</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="1">
         <f t="shared" si="6"/>
         <v>2.1546453676641462E-2</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7" s="1">
         <f t="shared" si="7"/>
         <v>4.6424966603965639E-4</v>
       </c>
       <c r="U7">
         <v>5</v>
       </c>
-      <c r="V7" s="2">
+      <c r="V7" s="1">
         <v>-37.548200000000001</v>
       </c>
-      <c r="W7" s="2">
+      <c r="W7" s="1">
         <f t="shared" si="8"/>
         <v>1.3261419091999134E-2</v>
       </c>
-      <c r="X7" s="2">
+      <c r="X7" s="1">
         <f t="shared" si="9"/>
         <v>1.7586523633363914E-4</v>
       </c>
@@ -1008,70 +1008,70 @@
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>-17.115110000000001</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>0.13939413460466141</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <f t="shared" si="1"/>
         <v>1.9430724762182463E-2</v>
       </c>
       <c r="F8">
         <v>6</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="1">
         <v>-20.3627</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="1">
         <f t="shared" si="2"/>
         <v>9.5910244914821211E-2</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <f t="shared" si="3"/>
         <v>9.1987750796209879E-3</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="1">
         <v>-30.574729999999999</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="1">
         <f t="shared" si="4"/>
         <v>2.9598077294880985E-2</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="1">
         <f t="shared" si="5"/>
         <v>8.7604617955374926E-4</v>
       </c>
       <c r="P8">
         <v>6</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1">
         <v>-49.12724</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="1">
         <f t="shared" si="6"/>
         <v>3.4965359673634028E-3</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S8" s="1">
         <f t="shared" si="7"/>
         <v>1.2225763771065926E-5</v>
       </c>
       <c r="U8">
         <v>6</v>
       </c>
-      <c r="V8" s="2">
+      <c r="V8" s="1">
         <v>-50.121259999999999</v>
       </c>
-      <c r="W8" s="2">
+      <c r="W8" s="1">
         <f t="shared" si="8"/>
         <v>3.1184371818623381E-3</v>
       </c>
-      <c r="X8" s="2">
+      <c r="X8" s="1">
         <f t="shared" si="9"/>
         <v>9.7246504572215207E-6</v>
       </c>
@@ -1080,70 +1080,70 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>-26.020900000000001</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>4.9998272591817702E-2</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <f t="shared" si="1"/>
         <v>2.4998272621657093E-3</v>
       </c>
       <c r="F9">
         <v>7</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="1">
         <v>-36.463700000000003</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="1">
         <f t="shared" si="2"/>
         <v>1.5025017966763249E-2</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <f t="shared" si="3"/>
         <v>2.2575116490155845E-4</v>
       </c>
       <c r="K9">
         <v>7</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="1">
         <v>-31.937999999999999</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="1">
         <f t="shared" si="4"/>
         <v>2.5298804558879277E-2</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="1">
         <f t="shared" si="5"/>
         <v>6.4002951210837087E-4</v>
       </c>
       <c r="P9">
         <v>7</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
         <v>-46.446350000000002</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="1">
         <f t="shared" si="6"/>
         <v>4.760828093251528E-3</v>
       </c>
-      <c r="S9" s="2">
+      <c r="S9" s="1">
         <f t="shared" si="7"/>
         <v>2.266548413349298E-5</v>
       </c>
       <c r="U9">
         <v>7</v>
       </c>
-      <c r="V9" s="2">
+      <c r="V9" s="1">
         <v>-41.249771000000003</v>
       </c>
-      <c r="W9" s="2">
+      <c r="W9" s="1">
         <f t="shared" si="8"/>
         <v>8.659871544634358E-3</v>
       </c>
-      <c r="X9" s="2">
+      <c r="X9" s="1">
         <f t="shared" si="9"/>
         <v>7.4993375169567862E-5</v>
       </c>
@@ -1152,70 +1152,70 @@
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>-20.358229999999999</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>9.595961569281436E-2</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <f t="shared" si="1"/>
         <v>9.2082478439126231E-3</v>
       </c>
       <c r="F10">
         <v>8</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="1">
         <v>-24.412800000000001</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="1">
         <f t="shared" si="2"/>
         <v>6.0167227540845261E-2</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="1">
         <f t="shared" si="3"/>
         <v>3.6200952699518485E-3</v>
       </c>
       <c r="K10">
         <v>8</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="1">
         <v>-33.131920000000001</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="1">
         <f t="shared" si="4"/>
         <v>2.2049766764618117E-2</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="1">
         <f t="shared" si="5"/>
         <v>4.8619221437405771E-4</v>
       </c>
       <c r="P10">
         <v>8</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1">
         <v>-37.78837</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="1">
         <f t="shared" si="6"/>
         <v>1.2899756128931869E-2</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="1">
         <f t="shared" si="7"/>
         <v>1.6640370818591532E-4</v>
       </c>
       <c r="U10">
         <v>8</v>
       </c>
-      <c r="V10" s="2">
+      <c r="V10" s="1">
         <v>-68.736670000000004</v>
       </c>
-      <c r="W10" s="2">
+      <c r="W10" s="1">
         <f t="shared" si="8"/>
         <v>3.657349803682403E-4</v>
       </c>
-      <c r="X10" s="2">
+      <c r="X10" s="1">
         <f t="shared" si="9"/>
         <v>1.3376207586495713E-7</v>
       </c>
@@ -1224,35 +1224,35 @@
       <c r="A11" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <f>SQRT(SUM(D4:D10)/D3)</f>
         <v>0.69053678997098566</v>
       </c>
       <c r="F11" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="1">
         <f>SQRT(SUM(I4:I10)/I3)</f>
         <v>0.45727795766436541</v>
       </c>
       <c r="K11" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="1">
         <f>SQRT(SUM(N4:N10)/N3)</f>
         <v>0.25810436021943967</v>
       </c>
       <c r="P11" t="s">
         <v>1</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1">
         <f>SQRT(SUM(S4:S10)/S3)</f>
         <v>9.8842283997892091E-2</v>
       </c>
       <c r="U11" t="s">
         <v>1</v>
       </c>
-      <c r="V11" s="2">
+      <c r="V11" s="1">
         <f>SQRT(SUM(X4:X10)/X3)</f>
         <v>2.9487535496158849E-2</v>
       </c>
@@ -1261,35 +1261,35 @@
       <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <f>B11*100</f>
         <v>69.053678997098572</v>
       </c>
       <c r="F12" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <f>G11*100</f>
         <v>45.727795766436543</v>
       </c>
       <c r="K12" t="s">
         <v>6</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="1">
         <f>L11*100</f>
         <v>25.810436021943968</v>
       </c>
       <c r="P12" t="s">
         <v>6</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
         <f>Q11*100</f>
         <v>9.88422839978921</v>
       </c>
       <c r="U12" t="s">
         <v>6</v>
       </c>
-      <c r="V12" s="2">
+      <c r="V12" s="1">
         <f>V11*100</f>
         <v>2.9487535496158848</v>
       </c>
@@ -1298,49 +1298,93 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="B13">
+        <v>6.3334999999999999</v>
+      </c>
+      <c r="F13">
+        <v>4.3105000000000002</v>
+      </c>
+      <c r="K13">
+        <v>2.2159</v>
+      </c>
+      <c r="P13">
+        <v>8.5100000000000002E-3</v>
+      </c>
     </row>
     <row r="14" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>13</v>
       </c>
+      <c r="B14">
+        <v>54.844999999999999</v>
+      </c>
+      <c r="F14">
+        <v>54.774999999999999</v>
+      </c>
+      <c r="K14">
+        <v>47.563000000000002</v>
+      </c>
+      <c r="P14">
+        <v>35.597999999999999</v>
+      </c>
     </row>
     <row r="15" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>11</v>
       </c>
+      <c r="B15">
+        <f>(B13/B14)*100</f>
+        <v>11.547998906007841</v>
+      </c>
+      <c r="F15">
+        <f>(F13/F14)*100</f>
+        <v>7.8694659972615248</v>
+      </c>
+      <c r="K15">
+        <f>(K13/K14)*100</f>
+        <v>4.6588734941025587</v>
+      </c>
+      <c r="P15">
+        <f>(P13/P14)*100</f>
+        <v>2.3905837406595878E-2</v>
+      </c>
+      <c r="U15" t="e">
+        <f>(U13/U14)*100</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="16" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="17" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="F17" s="1" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="F17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="K17" s="1" t="s">
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="K17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="P17" s="1" t="s">
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="P17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="U17" s="1" t="s">
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="U17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
     </row>
     <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
@@ -1408,70 +1452,70 @@
       <c r="A19">
         <v>1</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>6.7682770000000003</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <f>10^(B19/20)</f>
         <v>2.1797859551571217</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="1">
         <f>C19^2</f>
         <v>4.7514668103002453</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="1">
         <v>4.9325409999999996</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="1">
         <f>10^(G19/20)</f>
         <v>1.7645218882746261</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="1">
         <f>H19^2</f>
         <v>3.1135374942002518</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="L19" s="2">
+      <c r="L19" s="1">
         <v>1.7835570000000001</v>
       </c>
-      <c r="M19" s="2">
+      <c r="M19" s="1">
         <f>10^(L19/20)</f>
         <v>1.2279419885753484</v>
       </c>
-      <c r="N19" s="2">
+      <c r="N19" s="1">
         <f>M19^2</f>
         <v>1.5078415273063812</v>
       </c>
       <c r="P19">
         <v>1</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
         <v>-2.7031450000000001</v>
       </c>
-      <c r="R19" s="2">
+      <c r="R19" s="1">
         <f>10^(Q19/20)</f>
         <v>0.73255923896036046</v>
       </c>
-      <c r="S19" s="2">
+      <c r="S19" s="1">
         <f>R19^2</f>
         <v>0.53664303858618245</v>
       </c>
       <c r="U19">
         <v>1</v>
       </c>
-      <c r="V19" s="2">
+      <c r="V19" s="1">
         <v>-5.8865530000000001</v>
       </c>
-      <c r="W19" s="2">
+      <c r="W19" s="1">
         <f>10^(V19/20)</f>
         <v>0.50777621031291997</v>
       </c>
-      <c r="X19" s="2">
+      <c r="X19" s="1">
         <f>W19^2</f>
         <v>0.25783667975975072</v>
       </c>
@@ -1480,70 +1524,70 @@
       <c r="A20">
         <v>2</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <v>1.5660780000000001</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <f t="shared" ref="C20:C26" si="10">10^(B20/20)</f>
         <v>1.1975782502725438</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <f t="shared" ref="D20:D26" si="11">C20^2</f>
         <v>1.4341936655258476</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="1">
         <v>-3.9363000000000001</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <f t="shared" ref="H20:H26" si="12">10^(G20/20)</f>
         <v>0.63560162665626685</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="1">
         <f t="shared" ref="I20:I26" si="13">H20^2</f>
         <v>0.40398942780809244</v>
       </c>
       <c r="K20">
         <v>2</v>
       </c>
-      <c r="L20" s="2">
+      <c r="L20" s="1">
         <v>-13.43887</v>
       </c>
-      <c r="M20" s="2">
+      <c r="M20" s="1">
         <f t="shared" ref="M20:M26" si="14">10^(L20/20)</f>
         <v>0.2128415926493088</v>
       </c>
-      <c r="N20" s="2">
+      <c r="N20" s="1">
         <f t="shared" ref="N20:N26" si="15">M20^2</f>
         <v>4.5301543561494302E-2</v>
       </c>
       <c r="P20">
         <v>2</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="1">
         <v>-30.990259999999999</v>
       </c>
-      <c r="R20" s="2">
+      <c r="R20" s="1">
         <f t="shared" ref="R20:R26" si="16">10^(Q20/20)</f>
         <v>2.8215451228061027E-2</v>
       </c>
-      <c r="S20" s="2">
+      <c r="S20" s="1">
         <f t="shared" ref="S20:S26" si="17">R20^2</f>
         <v>7.9611168800309054E-4</v>
       </c>
       <c r="U20">
         <v>2</v>
       </c>
-      <c r="V20" s="2">
+      <c r="V20" s="1">
         <v>-65.969729999999998</v>
       </c>
-      <c r="W20" s="2">
+      <c r="W20" s="1">
         <f t="shared" ref="W20:W26" si="18">10^(V20/20)</f>
         <v>5.0293689935005737E-4</v>
       </c>
-      <c r="X20" s="2">
+      <c r="X20" s="1">
         <f t="shared" ref="X20:X26" si="19">W20^2</f>
         <v>2.5294552472784976E-7</v>
       </c>
@@ -1552,70 +1596,70 @@
       <c r="A21">
         <v>3</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>-11.415800000000001</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <f t="shared" si="10"/>
         <v>0.26866432388032097</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <f t="shared" si="11"/>
         <v>7.2180518926069998E-2</v>
       </c>
       <c r="F21">
         <v>3</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="1">
         <v>-22.321069999999999</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="1">
         <f t="shared" si="12"/>
         <v>7.6550230017373253E-2</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="1">
         <f t="shared" si="13"/>
         <v>5.8599377157127529E-3</v>
       </c>
       <c r="K21">
         <v>3</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L21" s="1">
         <v>-19.567900000000002</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21" s="1">
         <f t="shared" si="14"/>
         <v>0.10510055272648611</v>
       </c>
-      <c r="N21" s="2">
+      <c r="N21" s="1">
         <f t="shared" si="15"/>
         <v>1.1046126183412887E-2</v>
       </c>
       <c r="P21">
         <v>3</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="1">
         <v>-32.109788000000002</v>
       </c>
-      <c r="R21" s="2">
+      <c r="R21" s="1">
         <f t="shared" si="16"/>
         <v>2.4803364755235858E-2</v>
       </c>
-      <c r="S21" s="2">
+      <c r="S21" s="1">
         <f t="shared" si="17"/>
         <v>6.1520690318127638E-4</v>
       </c>
       <c r="U21">
         <v>3</v>
       </c>
-      <c r="V21" s="2">
+      <c r="V21" s="1">
         <v>-50.223329999999997</v>
       </c>
-      <c r="W21" s="2">
+      <c r="W21" s="1">
         <f t="shared" si="18"/>
         <v>3.0820061429196353E-3</v>
       </c>
-      <c r="X21" s="2">
+      <c r="X21" s="1">
         <f t="shared" si="19"/>
         <v>9.4987618649943669E-6</v>
       </c>
@@ -1624,70 +1668,70 @@
       <c r="A22">
         <v>4</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>-15.617190000000001</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <f t="shared" si="10"/>
         <v>0.16563057135745332</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <f t="shared" si="11"/>
         <v>2.7433486168196436E-2</v>
       </c>
       <c r="F22">
         <v>4</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="1">
         <v>-18.847539999999999</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="1">
         <f t="shared" si="12"/>
         <v>0.11418866616446387</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="1">
         <f t="shared" si="13"/>
         <v>1.3039051480419376E-2</v>
       </c>
       <c r="K22">
         <v>4</v>
       </c>
-      <c r="L22" s="2">
+      <c r="L22" s="1">
         <v>-34.189619999999998</v>
       </c>
-      <c r="M22" s="2">
+      <c r="M22" s="1">
         <f t="shared" si="14"/>
         <v>1.952176138156932E-2</v>
       </c>
-      <c r="N22" s="2">
+      <c r="N22" s="1">
         <f t="shared" si="15"/>
         <v>3.810991674389313E-4</v>
       </c>
       <c r="P22">
         <v>4</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="1">
         <v>-36.027729999999998</v>
       </c>
-      <c r="R22" s="2">
+      <c r="R22" s="1">
         <f t="shared" si="16"/>
         <v>1.5798414349361647E-2</v>
       </c>
-      <c r="S22" s="2">
+      <c r="S22" s="1">
         <f t="shared" si="17"/>
         <v>2.49589895954116E-4</v>
       </c>
       <c r="U22">
         <v>4</v>
       </c>
-      <c r="V22" s="2">
+      <c r="V22" s="1">
         <v>-61.591799999999999</v>
       </c>
-      <c r="W22" s="2">
+      <c r="W22" s="1">
         <f t="shared" si="18"/>
         <v>8.3254937668637862E-4</v>
       </c>
-      <c r="X22" s="2">
+      <c r="X22" s="1">
         <f t="shared" si="19"/>
         <v>6.9313846462087754E-7</v>
       </c>
@@ -1696,70 +1740,70 @@
       <c r="A23">
         <v>5</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <v>-17.219830000000002</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <f t="shared" si="10"/>
         <v>0.13772364238646667</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <f t="shared" si="11"/>
         <v>1.8967801672195358E-2</v>
       </c>
       <c r="F23">
         <v>5</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="1">
         <v>-27.135739999999998</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <f t="shared" si="12"/>
         <v>4.3975724177045733E-2</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="1">
         <f t="shared" si="13"/>
         <v>1.9338643168956046E-3</v>
       </c>
       <c r="K23">
         <v>5</v>
       </c>
-      <c r="L23" s="2">
+      <c r="L23" s="1">
         <v>-33.874360000000003</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23" s="1">
         <f t="shared" si="14"/>
         <v>2.0243332102641398E-2</v>
       </c>
-      <c r="N23" s="2">
+      <c r="N23" s="1">
         <f t="shared" si="15"/>
         <v>4.097924946178318E-4</v>
       </c>
       <c r="P23">
         <v>5</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
         <v>-38.085560000000001</v>
       </c>
-      <c r="R23" s="2">
+      <c r="R23" s="1">
         <f t="shared" si="16"/>
         <v>1.246585296288831E-2</v>
       </c>
-      <c r="S23" s="2">
+      <c r="S23" s="1">
         <f t="shared" si="17"/>
         <v>1.5539749009235127E-4</v>
       </c>
       <c r="U23">
         <v>5</v>
       </c>
-      <c r="V23" s="2">
+      <c r="V23" s="1">
         <v>-52.544119999999999</v>
       </c>
-      <c r="W23" s="2">
+      <c r="W23" s="1">
         <f t="shared" si="18"/>
         <v>2.35935884707182E-3</v>
       </c>
-      <c r="X23" s="2">
+      <c r="X23" s="1">
         <f t="shared" si="19"/>
         <v>5.5665741692560674E-6</v>
       </c>
@@ -1768,70 +1812,70 @@
       <c r="A24">
         <v>6</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <v>-31.648599999999998</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <f t="shared" si="10"/>
         <v>2.6155919977842376E-2</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="1">
         <f t="shared" si="11"/>
         <v>6.8413214988729393E-4</v>
       </c>
       <c r="F24">
         <v>6</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="1">
         <v>-27.937919999999998</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <f t="shared" si="12"/>
         <v>4.0096272421387906E-2</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="1">
         <f t="shared" si="13"/>
         <v>1.6077110620901524E-3</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
-      <c r="L24" s="2">
+      <c r="L24" s="1">
         <v>-32.442239999999998</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24" s="1">
         <f t="shared" si="14"/>
         <v>2.3871955707789751E-2</v>
       </c>
-      <c r="N24" s="2">
+      <c r="N24" s="1">
         <f t="shared" si="15"/>
         <v>5.6987026931467569E-4</v>
       </c>
       <c r="P24">
         <v>6</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="1">
         <v>-46.484569999999998</v>
       </c>
-      <c r="R24" s="2">
+      <c r="R24" s="1">
         <f t="shared" si="16"/>
         <v>4.7399253288239298E-3</v>
       </c>
-      <c r="S24" s="2">
+      <c r="S24" s="1">
         <f t="shared" si="17"/>
         <v>2.246689212282664E-5</v>
       </c>
       <c r="U24">
         <v>6</v>
       </c>
-      <c r="V24" s="2">
+      <c r="V24" s="1">
         <v>-59.123550000000002</v>
       </c>
-      <c r="W24" s="2">
+      <c r="W24" s="1">
         <f>10^(V24/20)</f>
         <v>1.1061715894533477E-3</v>
       </c>
-      <c r="X24" s="2">
+      <c r="X24" s="1">
         <f t="shared" si="19"/>
         <v>1.2236155853137456E-6</v>
       </c>
@@ -1840,70 +1884,70 @@
       <c r="A25">
         <v>7</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <v>-22.412500000000001</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="1">
         <f t="shared" si="10"/>
         <v>7.5748667929495014E-2</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <f t="shared" si="11"/>
         <v>5.7378606930929069E-3</v>
       </c>
       <c r="F25">
         <v>7</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="1">
         <v>-30.596316000000002</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="1">
         <f t="shared" si="12"/>
         <v>2.9524612067430886E-2</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="1">
         <f t="shared" si="13"/>
         <v>8.7170271773228552E-4</v>
       </c>
       <c r="K25">
         <v>7</v>
       </c>
-      <c r="L25" s="2">
+      <c r="L25" s="1">
         <v>-43.529693000000002</v>
       </c>
-      <c r="M25" s="2">
+      <c r="M25" s="1">
         <f t="shared" si="14"/>
         <v>6.6606306266898362E-3</v>
       </c>
-      <c r="N25" s="2">
+      <c r="N25" s="1">
         <f t="shared" si="15"/>
         <v>4.4364000345198639E-5</v>
       </c>
       <c r="P25">
         <v>7</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="1">
         <v>-49.811889999999998</v>
       </c>
-      <c r="R25" s="2">
+      <c r="R25" s="1">
         <f t="shared" si="16"/>
         <v>3.2315099687674985E-3</v>
       </c>
-      <c r="S25" s="2">
+      <c r="S25" s="1">
         <f t="shared" si="17"/>
         <v>1.044265667824372E-5</v>
       </c>
       <c r="U25">
         <v>7</v>
       </c>
-      <c r="V25" s="2">
+      <c r="V25" s="1">
         <v>-54.15334</v>
       </c>
-      <c r="W25" s="2">
+      <c r="W25" s="1">
         <f>10^(V25/20)</f>
         <v>1.9603472148566931E-3</v>
       </c>
-      <c r="X25" s="2">
+      <c r="X25" s="1">
         <f t="shared" si="19"/>
         <v>3.8429612027963939E-6</v>
       </c>
@@ -1912,70 +1956,70 @@
       <c r="A26">
         <v>8</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>-39.467100000000002</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <f t="shared" si="10"/>
         <v>1.0632735242956418E-2</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="1">
         <f t="shared" si="11"/>
         <v>1.1305505874680748E-4</v>
       </c>
       <c r="F26">
         <v>8</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="1">
         <v>-35.761539999999997</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="1">
         <f t="shared" si="12"/>
         <v>1.6290071856043555E-2</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="1">
         <f t="shared" si="13"/>
         <v>2.6536644107506233E-4</v>
       </c>
       <c r="K26">
         <v>8</v>
       </c>
-      <c r="L26" s="2">
+      <c r="L26" s="1">
         <v>-43.648229999999998</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26" s="1">
         <f t="shared" si="14"/>
         <v>6.5703499262493798E-3</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="1">
         <f t="shared" si="15"/>
         <v>4.3169498153365231E-5</v>
       </c>
       <c r="P26">
         <v>8</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="1">
         <v>-54.7545</v>
       </c>
-      <c r="R26" s="2">
+      <c r="R26" s="1">
         <f t="shared" si="16"/>
         <v>1.8292581556982267E-3</v>
       </c>
-      <c r="S26" s="2">
+      <c r="S26" s="1">
         <f t="shared" si="17"/>
         <v>3.3461854001884778E-6</v>
       </c>
       <c r="U26">
         <v>8</v>
       </c>
-      <c r="V26" s="2">
+      <c r="V26" s="1">
         <v>-58.685600000000001</v>
       </c>
-      <c r="W26" s="2">
+      <c r="W26" s="1">
         <f t="shared" si="18"/>
         <v>1.1633757315162722E-3</v>
       </c>
-      <c r="X26" s="2">
+      <c r="X26" s="1">
         <f t="shared" si="19"/>
         <v>1.3534430926810213E-6</v>
       </c>
@@ -1984,35 +2028,35 @@
       <c r="A27" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <f>SQRT(SUM(D20:D26)/D19)</f>
         <v>0.57286521798157586</v>
       </c>
       <c r="F27" t="s">
         <v>1</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="1">
         <f>SQRT(SUM(I20:I26)/I19)</f>
         <v>0.37057410684906278</v>
       </c>
       <c r="K27" t="s">
         <v>1</v>
       </c>
-      <c r="L27" s="2">
+      <c r="L27" s="1">
         <f>SQRT(SUM(N20:N26)/N19)</f>
         <v>0.19578116585594971</v>
       </c>
       <c r="P27" t="s">
         <v>1</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="1">
         <f>SQRT(SUM(S20:S26)/S19)</f>
         <v>5.8754832421509827E-2</v>
       </c>
       <c r="U27" t="s">
         <v>1</v>
       </c>
-      <c r="V27" s="2">
+      <c r="V27" s="1">
         <f>SQRT(SUM(X20:X26)/X19)</f>
         <v>9.3273060292258965E-3</v>
       </c>
@@ -2021,35 +2065,35 @@
       <c r="A28" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="1">
         <f>B27*100</f>
         <v>57.286521798157587</v>
       </c>
       <c r="F28" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="1">
         <f>G27*100</f>
         <v>37.05741068490628</v>
       </c>
       <c r="K28" t="s">
         <v>6</v>
       </c>
-      <c r="L28" s="2">
+      <c r="L28" s="1">
         <f>L27*100</f>
         <v>19.578116585594969</v>
       </c>
       <c r="P28" t="s">
         <v>6</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="1">
         <f>Q27*100</f>
         <v>5.8754832421509828</v>
       </c>
       <c r="U28" t="s">
         <v>6</v>
       </c>
-      <c r="V28" s="2">
+      <c r="V28" s="1">
         <f>V27*100</f>
         <v>0.93273060292258969</v>
       </c>
@@ -2071,36 +2115,36 @@
     </row>
     <row r="32" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="33" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="F33" s="1" t="s">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="F33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="K33" s="1" t="s">
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="K33" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="P33" s="1" t="s">
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="P33" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="U33" s="1" t="s">
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="U33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
     </row>
     <row r="34" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
@@ -2168,70 +2212,70 @@
       <c r="A35">
         <v>1</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="1">
         <v>8.7264093000000003</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="1">
         <f>10^(B35/20)</f>
         <v>2.7309922330078882</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <f>C35^2</f>
         <v>7.4583185767494111</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35" s="1">
         <v>4.9325400000000004</v>
       </c>
-      <c r="H35" s="2">
-        <f>10^(G35/20)</f>
+      <c r="H35" s="1">
+        <f t="shared" ref="H35:H42" si="20">10^(G35/20)</f>
         <v>1.7645216851265479</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I35" s="1">
         <f>H35^2</f>
         <v>3.1135367772818325</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
-      <c r="L35" s="2">
+      <c r="L35" s="1">
         <v>1.7835570000000001</v>
       </c>
-      <c r="M35" s="2">
-        <f>10^(L35/20)</f>
+      <c r="M35" s="1">
+        <f t="shared" ref="M35:M42" si="21">10^(L35/20)</f>
         <v>1.2279419885753484</v>
       </c>
-      <c r="N35" s="2">
+      <c r="N35" s="1">
         <f>M35^2</f>
         <v>1.5078415273063812</v>
       </c>
       <c r="P35">
         <v>1</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="1">
         <v>0.51427613999999999</v>
       </c>
-      <c r="R35" s="2">
+      <c r="R35" s="1">
         <f>10^(Q35/20)</f>
         <v>1.0609961475695531</v>
       </c>
-      <c r="S35" s="2">
+      <c r="S35" s="1">
         <f>R35^2</f>
         <v>1.1257128251574329</v>
       </c>
       <c r="U35">
         <v>1</v>
       </c>
-      <c r="V35" s="2">
+      <c r="V35" s="1">
         <v>-2.5384099999999998</v>
       </c>
-      <c r="W35" s="2">
+      <c r="W35" s="1">
         <f>10^(V35/20)</f>
         <v>0.74658541247913746</v>
       </c>
-      <c r="X35" s="2">
+      <c r="X35" s="1">
         <f>W35^2</f>
         <v>0.55738977812664381</v>
       </c>
@@ -2240,71 +2284,71 @@
       <c r="A36">
         <v>2</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="1">
         <v>4.2524160000000002</v>
       </c>
-      <c r="C36" s="2">
-        <f t="shared" ref="C36:C42" si="20">10^(B36/20)</f>
+      <c r="C36" s="1">
+        <f t="shared" ref="C36:C42" si="22">10^(B36/20)</f>
         <v>1.6316266867970712</v>
       </c>
-      <c r="D36" s="2">
-        <f t="shared" ref="D36:D42" si="21">C36^2</f>
+      <c r="D36" s="1">
+        <f t="shared" ref="D36:D42" si="23">C36^2</f>
         <v>2.6622056450683882</v>
       </c>
       <c r="F36">
         <v>2</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="1">
         <v>-3.9363100000000002</v>
       </c>
-      <c r="H36" s="2">
-        <f>10^(G36/20)</f>
+      <c r="H36" s="1">
+        <f t="shared" si="20"/>
         <v>0.63560089489327276</v>
       </c>
-      <c r="I36" s="2">
-        <f t="shared" ref="I36:I42" si="22">H36^2</f>
+      <c r="I36" s="1">
+        <f t="shared" ref="I36:I42" si="24">H36^2</f>
         <v>0.40398849758912919</v>
       </c>
       <c r="K36">
         <v>2</v>
       </c>
-      <c r="L36" s="2">
+      <c r="L36" s="1">
         <v>-13.438800000000001</v>
       </c>
-      <c r="M36" s="2">
-        <f>10^(L36/20)</f>
+      <c r="M36" s="1">
+        <f t="shared" si="21"/>
         <v>0.21284330795679507</v>
       </c>
-      <c r="N36" s="2">
-        <f t="shared" ref="N36:N42" si="23">M36^2</f>
+      <c r="N36" s="1">
+        <f t="shared" ref="N36:N42" si="25">M36^2</f>
         <v>4.5302273741991105E-2</v>
       </c>
       <c r="P36">
         <v>2</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="1">
         <v>-24.62462</v>
       </c>
-      <c r="R36" s="2">
-        <f t="shared" ref="R36:R42" si="24">10^(Q36/20)</f>
+      <c r="R36" s="1">
+        <f t="shared" ref="R36:R42" si="26">10^(Q36/20)</f>
         <v>5.8717695170362363E-2</v>
       </c>
-      <c r="S36" s="2">
-        <f t="shared" ref="S36:S42" si="25">R36^2</f>
+      <c r="S36" s="1">
+        <f t="shared" ref="S36:S42" si="27">R36^2</f>
         <v>3.4477677261195955E-3</v>
       </c>
       <c r="U36">
         <v>2</v>
       </c>
-      <c r="V36" s="2">
+      <c r="V36" s="1">
         <v>-47.950449999999996</v>
       </c>
-      <c r="W36" s="2">
-        <f t="shared" ref="W36:W42" si="26">10^(V36/20)</f>
+      <c r="W36" s="1">
+        <f t="shared" ref="W36:W42" si="28">10^(V36/20)</f>
         <v>4.0038472459549114E-3</v>
       </c>
-      <c r="X36" s="2">
-        <f t="shared" ref="X36:X42" si="27">W36^2</f>
+      <c r="X36" s="1">
+        <f t="shared" ref="X36:X42" si="29">W36^2</f>
         <v>1.6030792768940728E-5</v>
       </c>
     </row>
@@ -2312,71 +2356,71 @@
       <c r="A37">
         <v>3</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="1">
         <v>-5.9124749999999997</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="1">
+        <f t="shared" si="22"/>
+        <v>0.50626307188618402</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="23"/>
+        <v>0.25630229795563553</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" s="1">
+        <v>-22.321000000000002</v>
+      </c>
+      <c r="H37" s="1">
         <f t="shared" si="20"/>
-        <v>0.50626307188618402</v>
-      </c>
-      <c r="D37" s="2">
+        <v>7.655084694182393E-2</v>
+      </c>
+      <c r="I37" s="1">
+        <f t="shared" si="24"/>
+        <v>5.8600321675105543E-3</v>
+      </c>
+      <c r="K37">
+        <v>3</v>
+      </c>
+      <c r="L37" s="1">
+        <v>-19.567900000000002</v>
+      </c>
+      <c r="M37" s="1">
         <f t="shared" si="21"/>
-        <v>0.25630229795563553</v>
-      </c>
-      <c r="F37">
-        <v>3</v>
-      </c>
-      <c r="G37" s="2">
-        <v>-22.321000000000002</v>
-      </c>
-      <c r="H37" s="2">
-        <f>10^(G37/20)</f>
-        <v>7.655084694182393E-2</v>
-      </c>
-      <c r="I37" s="2">
-        <f t="shared" si="22"/>
-        <v>5.8600321675105543E-3</v>
-      </c>
-      <c r="K37">
-        <v>3</v>
-      </c>
-      <c r="L37" s="2">
-        <v>-19.567900000000002</v>
-      </c>
-      <c r="M37" s="2">
-        <f>10^(L37/20)</f>
         <v>0.10510055272648611</v>
       </c>
-      <c r="N37" s="2">
-        <f t="shared" si="23"/>
+      <c r="N37" s="1">
+        <f t="shared" si="25"/>
         <v>1.1046126183412887E-2</v>
       </c>
       <c r="P37">
         <v>3</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
         <v>-26.244759999999999</v>
       </c>
-      <c r="R37" s="2">
-        <f t="shared" si="24"/>
+      <c r="R37" s="1">
+        <f t="shared" si="26"/>
         <v>4.8726139024904185E-2</v>
       </c>
-      <c r="S37" s="2">
-        <f t="shared" si="25"/>
+      <c r="S37" s="1">
+        <f t="shared" si="27"/>
         <v>2.3742366242742903E-3</v>
       </c>
       <c r="U37">
         <v>3</v>
       </c>
-      <c r="V37" s="2">
+      <c r="V37" s="1">
         <v>-41.345280000000002</v>
       </c>
-      <c r="W37" s="2">
-        <f t="shared" si="26"/>
+      <c r="W37" s="1">
+        <f t="shared" si="28"/>
         <v>8.5651702526749647E-3</v>
       </c>
-      <c r="X37" s="2">
-        <f t="shared" si="27"/>
+      <c r="X37" s="1">
+        <f t="shared" si="29"/>
         <v>7.3362141457308113E-5</v>
       </c>
     </row>
@@ -2384,71 +2428,71 @@
       <c r="A38">
         <v>4</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="1">
         <v>-17.163319999999999</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="1">
+        <f t="shared" si="22"/>
+        <v>0.13862258716932108</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="23"/>
+        <v>1.9216221673516019E-2</v>
+      </c>
+      <c r="F38">
+        <v>4</v>
+      </c>
+      <c r="G38" s="1">
+        <v>-18.847548</v>
+      </c>
+      <c r="H38" s="1">
         <f t="shared" si="20"/>
-        <v>0.13862258716932108</v>
-      </c>
-      <c r="D38" s="2">
+        <v>0.11418856099286408</v>
+      </c>
+      <c r="I38" s="1">
+        <f t="shared" si="24"/>
+        <v>1.303902746162104E-2</v>
+      </c>
+      <c r="K38">
+        <v>4</v>
+      </c>
+      <c r="L38" s="1">
+        <v>-34.189619999999998</v>
+      </c>
+      <c r="M38" s="1">
         <f t="shared" si="21"/>
-        <v>1.9216221673516019E-2</v>
-      </c>
-      <c r="F38">
-        <v>4</v>
-      </c>
-      <c r="G38" s="2">
-        <v>-18.847548</v>
-      </c>
-      <c r="H38" s="2">
-        <f>10^(G38/20)</f>
-        <v>0.11418856099286408</v>
-      </c>
-      <c r="I38" s="2">
-        <f t="shared" si="22"/>
-        <v>1.303902746162104E-2</v>
-      </c>
-      <c r="K38">
-        <v>4</v>
-      </c>
-      <c r="L38" s="2">
-        <v>-34.189619999999998</v>
-      </c>
-      <c r="M38" s="2">
-        <f>10^(L38/20)</f>
         <v>1.952176138156932E-2</v>
       </c>
-      <c r="N38" s="2">
-        <f t="shared" si="23"/>
+      <c r="N38" s="1">
+        <f t="shared" si="25"/>
         <v>3.810991674389313E-4</v>
       </c>
       <c r="P38">
         <v>4</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="1">
         <v>-31.102039999999999</v>
       </c>
-      <c r="R38" s="2">
-        <f t="shared" si="24"/>
+      <c r="R38" s="1">
+        <f t="shared" si="26"/>
         <v>2.7854668867971395E-2</v>
       </c>
-      <c r="S38" s="2">
-        <f t="shared" si="25"/>
+      <c r="S38" s="1">
+        <f t="shared" si="27"/>
         <v>7.7588257774433489E-4</v>
       </c>
       <c r="U38">
         <v>4</v>
       </c>
-      <c r="V38" s="2">
+      <c r="V38" s="1">
         <v>-55.475811999999998</v>
       </c>
-      <c r="W38" s="2">
-        <f t="shared" si="26"/>
+      <c r="W38" s="1">
+        <f t="shared" si="28"/>
         <v>1.6834855770393963E-3</v>
       </c>
-      <c r="X38" s="2">
-        <f t="shared" si="27"/>
+      <c r="X38" s="1">
+        <f t="shared" si="29"/>
         <v>2.8341236880996692E-6</v>
       </c>
     </row>
@@ -2456,71 +2500,71 @@
       <c r="A39">
         <v>5</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="1">
         <v>-12.8383</v>
       </c>
-      <c r="C39" s="2">
-        <f t="shared" si="20"/>
+      <c r="C39" s="1">
+        <f t="shared" si="22"/>
         <v>0.22807884236201659</v>
       </c>
-      <c r="D39" s="2">
-        <f t="shared" si="21"/>
+      <c r="D39" s="1">
+        <f t="shared" si="23"/>
         <v>5.2019958333197613E-2</v>
       </c>
       <c r="F39">
         <v>5</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="1">
         <v>-27.135739999999998</v>
       </c>
-      <c r="H39" s="2">
-        <f>10^(G39/20)</f>
+      <c r="H39" s="1">
+        <f t="shared" si="20"/>
         <v>4.3975724177045733E-2</v>
       </c>
-      <c r="I39" s="2">
-        <f t="shared" si="22"/>
+      <c r="I39" s="1">
+        <f t="shared" si="24"/>
         <v>1.9338643168956046E-3</v>
       </c>
       <c r="K39">
         <v>5</v>
       </c>
-      <c r="L39" s="2">
+      <c r="L39" s="1">
         <v>-33.874360000000003</v>
       </c>
-      <c r="M39" s="2">
-        <f>10^(L39/20)</f>
+      <c r="M39" s="1">
+        <f t="shared" si="21"/>
         <v>2.0243332102641398E-2</v>
       </c>
-      <c r="N39" s="2">
-        <f t="shared" si="23"/>
+      <c r="N39" s="1">
+        <f t="shared" si="25"/>
         <v>4.097924946178318E-4</v>
       </c>
       <c r="P39">
         <v>5</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="1">
         <v>-34.502673000000001</v>
       </c>
-      <c r="R39" s="2">
-        <f t="shared" si="24"/>
+      <c r="R39" s="1">
+        <f t="shared" si="26"/>
         <v>1.8830695035671519E-2</v>
       </c>
-      <c r="S39" s="2">
-        <f t="shared" si="25"/>
+      <c r="S39" s="1">
+        <f t="shared" si="27"/>
         <v>3.5459507552646402E-4</v>
       </c>
       <c r="U39">
         <v>5</v>
       </c>
-      <c r="V39" s="2">
+      <c r="V39" s="1">
         <v>-43.596539999999997</v>
       </c>
-      <c r="W39" s="2">
-        <f t="shared" si="26"/>
+      <c r="W39" s="1">
+        <f t="shared" si="28"/>
         <v>6.6095668583314778E-3</v>
       </c>
-      <c r="X39" s="2">
-        <f t="shared" si="27"/>
+      <c r="X39" s="1">
+        <f t="shared" si="29"/>
         <v>4.3686374054753841E-5</v>
       </c>
     </row>
@@ -2528,71 +2572,71 @@
       <c r="A40">
         <v>6</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="1">
         <v>-26.64396</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="1">
+        <f t="shared" si="22"/>
+        <v>4.6537387568645443E-2</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="23"/>
+        <v>2.1657284417143153E-3</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40" s="1">
+        <v>-27.937923999999999</v>
+      </c>
+      <c r="H40" s="1">
         <f t="shared" si="20"/>
-        <v>4.6537387568645443E-2</v>
-      </c>
-      <c r="D40" s="2">
+        <v>4.0096253956376324E-2</v>
+      </c>
+      <c r="I40" s="1">
+        <f t="shared" si="24"/>
+        <v>1.6077095813342239E-3</v>
+      </c>
+      <c r="K40">
+        <v>6</v>
+      </c>
+      <c r="L40" s="1">
+        <v>-32.442239999999998</v>
+      </c>
+      <c r="M40" s="1">
         <f t="shared" si="21"/>
-        <v>2.1657284417143153E-3</v>
-      </c>
-      <c r="F40">
-        <v>6</v>
-      </c>
-      <c r="G40" s="2">
-        <v>-27.937923999999999</v>
-      </c>
-      <c r="H40" s="2">
-        <f>10^(G40/20)</f>
-        <v>4.0096253956376324E-2</v>
-      </c>
-      <c r="I40" s="2">
-        <f t="shared" si="22"/>
-        <v>1.6077095813342239E-3</v>
-      </c>
-      <c r="K40">
-        <v>6</v>
-      </c>
-      <c r="L40" s="2">
-        <v>-32.442239999999998</v>
-      </c>
-      <c r="M40" s="2">
-        <f>10^(L40/20)</f>
         <v>2.3871955707789751E-2</v>
       </c>
-      <c r="N40" s="2">
-        <f t="shared" si="23"/>
+      <c r="N40" s="1">
+        <f t="shared" si="25"/>
         <v>5.6987026931467569E-4</v>
       </c>
       <c r="P40">
         <v>6</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="1">
         <v>-50.60031</v>
       </c>
-      <c r="R40" s="2">
-        <f t="shared" si="24"/>
+      <c r="R40" s="1">
+        <f t="shared" si="26"/>
         <v>2.9511038996851966E-3</v>
       </c>
-      <c r="S40" s="2">
-        <f t="shared" si="25"/>
+      <c r="S40" s="1">
+        <f t="shared" si="27"/>
         <v>8.709014226737175E-6</v>
       </c>
       <c r="U40">
         <v>6</v>
       </c>
-      <c r="V40" s="2">
+      <c r="V40" s="1">
         <v>-67.411060000000006</v>
       </c>
-      <c r="W40" s="2">
-        <f t="shared" si="26"/>
+      <c r="W40" s="1">
+        <f t="shared" si="28"/>
         <v>4.2603668816662614E-4</v>
       </c>
-      <c r="X40" s="2">
-        <f t="shared" si="27"/>
+      <c r="X40" s="1">
+        <f t="shared" si="29"/>
         <v>1.8150725966398703E-7</v>
       </c>
     </row>
@@ -2600,71 +2644,71 @@
       <c r="A41">
         <v>7</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="1">
         <v>-21.305900000000001</v>
       </c>
-      <c r="C41" s="2">
-        <f t="shared" si="20"/>
+      <c r="C41" s="1">
+        <f t="shared" si="22"/>
         <v>8.6040910991310754E-2</v>
       </c>
-      <c r="D41" s="2">
-        <f t="shared" si="21"/>
+      <c r="D41" s="1">
+        <f t="shared" si="23"/>
         <v>7.40303836421466E-3</v>
       </c>
       <c r="F41">
         <v>7</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41" s="1">
         <v>-30.596299999999999</v>
       </c>
-      <c r="H41" s="2">
-        <f>10^(G41/20)</f>
+      <c r="H41" s="1">
+        <f t="shared" si="20"/>
         <v>2.9524666453826294E-2</v>
       </c>
-      <c r="I41" s="2">
-        <f t="shared" si="22"/>
+      <c r="I41" s="1">
+        <f t="shared" si="24"/>
         <v>8.717059292096957E-4</v>
       </c>
       <c r="K41">
         <v>7</v>
       </c>
-      <c r="L41" s="2">
+      <c r="L41" s="1">
         <v>-43.529690000000002</v>
       </c>
-      <c r="M41" s="2">
-        <f>10^(L41/20)</f>
+      <c r="M41" s="1">
+        <f t="shared" si="21"/>
         <v>6.6606329271905506E-3</v>
       </c>
-      <c r="N41" s="2">
-        <f t="shared" si="23"/>
+      <c r="N41" s="1">
+        <f t="shared" si="25"/>
         <v>4.436403099077496E-5</v>
       </c>
       <c r="P41">
         <v>7</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
         <v>-64.501450000000006</v>
       </c>
-      <c r="R41" s="2">
-        <f t="shared" si="24"/>
+      <c r="R41" s="1">
+        <f t="shared" si="26"/>
         <v>5.9556271352755323E-4</v>
       </c>
-      <c r="S41" s="2">
-        <f t="shared" si="25"/>
+      <c r="S41" s="1">
+        <f t="shared" si="27"/>
         <v>3.5469494574430246E-7</v>
       </c>
       <c r="U41">
         <v>7</v>
       </c>
-      <c r="V41" s="2">
+      <c r="V41" s="1">
         <v>-45.820599999999999</v>
       </c>
-      <c r="W41" s="2">
-        <f t="shared" si="26"/>
+      <c r="W41" s="1">
+        <f t="shared" si="28"/>
         <v>5.1164649103207123E-3</v>
       </c>
-      <c r="X41" s="2">
-        <f t="shared" si="27"/>
+      <c r="X41" s="1">
+        <f t="shared" si="29"/>
         <v>2.6178213178543136E-5</v>
       </c>
     </row>
@@ -2672,71 +2716,71 @@
       <c r="A42">
         <v>8</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="1">
         <v>-24.253699999999998</v>
       </c>
-      <c r="C42" s="2">
-        <f t="shared" si="20"/>
+      <c r="C42" s="1">
+        <f t="shared" si="22"/>
         <v>6.1279469933498504E-2</v>
       </c>
-      <c r="D42" s="2">
-        <f t="shared" si="21"/>
+      <c r="D42" s="1">
+        <f t="shared" si="23"/>
         <v>3.7551734353305473E-3</v>
       </c>
       <c r="F42">
         <v>8</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42" s="1">
         <v>-35.761546000000003</v>
       </c>
-      <c r="H42" s="2">
-        <f>10^(G42/20)</f>
+      <c r="H42" s="1">
+        <f t="shared" si="20"/>
         <v>1.6290060603264447E-2</v>
       </c>
-      <c r="I42" s="2">
-        <f t="shared" si="22"/>
+      <c r="I42" s="1">
+        <f t="shared" si="24"/>
         <v>2.6536607445802845E-4</v>
       </c>
       <c r="K42">
         <v>8</v>
       </c>
-      <c r="L42" s="2">
+      <c r="L42" s="1">
         <v>-43.648229999999998</v>
       </c>
-      <c r="M42" s="2">
-        <f>10^(L42/20)</f>
+      <c r="M42" s="1">
+        <f t="shared" si="21"/>
         <v>6.5703499262493798E-3</v>
       </c>
-      <c r="N42" s="2">
-        <f t="shared" si="23"/>
+      <c r="N42" s="1">
+        <f t="shared" si="25"/>
         <v>4.3169498153365231E-5</v>
       </c>
       <c r="P42">
         <v>8</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="1">
         <v>-42.891917999999997</v>
       </c>
-      <c r="R42" s="2">
-        <f t="shared" si="24"/>
+      <c r="R42" s="1">
+        <f t="shared" si="26"/>
         <v>7.1681007360048805E-3</v>
       </c>
-      <c r="S42" s="2">
-        <f t="shared" si="25"/>
+      <c r="S42" s="1">
+        <f t="shared" si="27"/>
         <v>5.1381668161513708E-5</v>
       </c>
       <c r="U42">
         <v>8</v>
       </c>
-      <c r="V42" s="2">
+      <c r="V42" s="1">
         <v>-67.42407</v>
       </c>
-      <c r="W42" s="2">
-        <f t="shared" si="26"/>
+      <c r="W42" s="1">
+        <f t="shared" si="28"/>
         <v>4.2539903461908822E-4</v>
       </c>
-      <c r="X42" s="2">
-        <f t="shared" si="27"/>
+      <c r="X42" s="1">
+        <f t="shared" si="29"/>
         <v>1.8096433865485222E-7</v>
       </c>
     </row>
@@ -2744,35 +2788,35 @@
       <c r="A43" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="1">
         <f>SQRT(SUM(D36:D42)/D35)</f>
         <v>0.63454455632488627</v>
       </c>
       <c r="F43" t="s">
         <v>1</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43" s="1">
         <f>SQRT(SUM(I36:I42)/I35)</f>
         <v>0.37057377751390241</v>
       </c>
       <c r="K43" t="s">
         <v>1</v>
       </c>
-      <c r="L43" s="2">
+      <c r="L43" s="1">
         <f>SQRT(SUM(N36:N42)/N35)</f>
         <v>0.19578240263032307</v>
       </c>
       <c r="P43" t="s">
         <v>1</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="1">
         <f>SQRT(SUM(S36:S42)/S35)</f>
         <v>7.892886612997603E-2</v>
       </c>
       <c r="U43" t="s">
         <v>1</v>
       </c>
-      <c r="V43" s="2">
+      <c r="V43" s="1">
         <f>SQRT(SUM(X36:X42)/X35)</f>
         <v>1.7072057335423756E-2</v>
       </c>
@@ -2781,35 +2825,35 @@
       <c r="A44" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="1">
         <f>B43*100</f>
         <v>63.454455632488624</v>
       </c>
       <c r="F44" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44" s="1">
         <f>G43*100</f>
         <v>37.057377751390241</v>
       </c>
       <c r="K44" t="s">
         <v>6</v>
       </c>
-      <c r="L44" s="2">
+      <c r="L44" s="1">
         <f>L43*100</f>
         <v>19.578240263032306</v>
       </c>
       <c r="P44" t="s">
         <v>6</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="1">
         <f>Q43*100</f>
         <v>7.8928866129976027</v>
       </c>
       <c r="U44" t="s">
         <v>6</v>
       </c>
-      <c r="V44" s="2">
+      <c r="V44" s="1">
         <f>V43*100</f>
         <v>1.7072057335423756</v>
       </c>
@@ -2831,36 +2875,36 @@
     </row>
     <row r="48" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="49" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="F49" s="1" t="s">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="F49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="K49" s="1" t="s">
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="K49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="P49" s="1" t="s">
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="P49" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="U49" s="1" t="s">
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="2"/>
+      <c r="U49" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="V49" s="1"/>
-      <c r="W49" s="1"/>
-      <c r="X49" s="1"/>
+      <c r="V49" s="2"/>
+      <c r="W49" s="2"/>
+      <c r="X49" s="2"/>
     </row>
     <row r="50" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
@@ -2928,68 +2972,68 @@
       <c r="A51">
         <v>1</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="1">
         <v>10.066017</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="1">
         <f>10^(B51/20)</f>
         <v>3.1864040837436325</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="1">
         <f>C51^2</f>
         <v>10.153170984898098</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2">
+      <c r="G51" s="1"/>
+      <c r="H51" s="1">
         <f>10^(G51/20)</f>
         <v>1</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I51" s="1">
         <f>H51^2</f>
         <v>1</v>
       </c>
       <c r="K51">
         <v>1</v>
       </c>
-      <c r="L51" s="2">
+      <c r="L51" s="1">
         <v>4.7132839999999998</v>
       </c>
-      <c r="M51" s="2">
+      <c r="M51" s="1">
         <f>10^(L51/20)</f>
         <v>1.7205377268786246</v>
       </c>
-      <c r="N51" s="2">
+      <c r="N51" s="1">
         <f>M51^2</f>
         <v>2.9602500696126648</v>
       </c>
       <c r="P51">
         <v>1</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q51" s="1">
         <v>3.5412034000000001</v>
       </c>
-      <c r="R51" s="2">
+      <c r="R51" s="1">
         <f>10^(Q51/20)</f>
         <v>1.5033502356433173</v>
       </c>
-      <c r="S51" s="2">
+      <c r="S51" s="1">
         <f>R51^2</f>
         <v>2.2600619310088175</v>
       </c>
       <c r="U51">
         <v>1</v>
       </c>
-      <c r="V51" s="2">
+      <c r="V51" s="1">
         <v>0.66674623</v>
       </c>
-      <c r="W51" s="2">
+      <c r="W51" s="1">
         <f>10^(V51/20)</f>
         <v>1.0797850531861271</v>
       </c>
-      <c r="X51" s="2">
+      <c r="X51" s="1">
         <f>W51^2</f>
         <v>1.1659357610841672</v>
       </c>
@@ -2998,69 +3042,69 @@
       <c r="A52">
         <v>2</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="1">
         <v>6.3832149999999999</v>
       </c>
-      <c r="C52" s="2">
-        <f t="shared" ref="C52:C58" si="28">10^(B52/20)</f>
+      <c r="C52" s="1">
+        <f t="shared" ref="C52:C58" si="30">10^(B52/20)</f>
         <v>2.0852625805163836</v>
       </c>
-      <c r="D52" s="2">
-        <f t="shared" ref="D52:D58" si="29">C52^2</f>
+      <c r="D52" s="1">
+        <f t="shared" ref="D52:D58" si="31">C52^2</f>
         <v>4.3483200297018474</v>
       </c>
       <c r="F52">
         <v>2</v>
       </c>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2">
-        <f t="shared" ref="H52:H58" si="30">10^(G52/20)</f>
-        <v>1</v>
-      </c>
-      <c r="I52" s="2">
-        <f t="shared" ref="I52:I58" si="31">H52^2</f>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1">
+        <f t="shared" ref="H52:H58" si="32">10^(G52/20)</f>
+        <v>1</v>
+      </c>
+      <c r="I52" s="1">
+        <f t="shared" ref="I52:I58" si="33">H52^2</f>
         <v>1</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
-      <c r="L52" s="2">
+      <c r="L52" s="1">
         <v>-8.9661418000000008</v>
       </c>
-      <c r="M52" s="2">
-        <f t="shared" ref="M52:M58" si="32">10^(L52/20)</f>
+      <c r="M52" s="1">
+        <f t="shared" ref="M52:M58" si="34">10^(L52/20)</f>
         <v>0.3561991756148925</v>
       </c>
-      <c r="N52" s="2">
-        <f t="shared" ref="N52:N58" si="33">M52^2</f>
+      <c r="N52" s="1">
+        <f t="shared" ref="N52:N58" si="35">M52^2</f>
         <v>0.12687785270872903</v>
       </c>
       <c r="P52">
         <v>2</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q52" s="1">
         <v>-18.148479999999999</v>
       </c>
-      <c r="R52" s="2">
-        <f t="shared" ref="R52:R58" si="34">10^(Q52/20)</f>
+      <c r="R52" s="1">
+        <f t="shared" ref="R52:R58" si="36">10^(Q52/20)</f>
         <v>0.12375877444696284</v>
       </c>
-      <c r="S52" s="2">
-        <f t="shared" ref="S52:S58" si="35">R52^2</f>
+      <c r="S52" s="1">
+        <f t="shared" ref="S52:S58" si="37">R52^2</f>
         <v>1.5316234252614223E-2</v>
       </c>
       <c r="U52">
         <v>2</v>
       </c>
-      <c r="V52" s="2">
+      <c r="V52" s="1">
         <v>-34.361789999999999</v>
       </c>
-      <c r="W52" s="2">
-        <f t="shared" ref="W52:W58" si="36">10^(V52/20)</f>
+      <c r="W52" s="1">
+        <f t="shared" ref="W52:W58" si="38">10^(V52/20)</f>
         <v>1.9138614731915041E-2</v>
       </c>
-      <c r="X52" s="2">
-        <f t="shared" ref="X52:X58" si="37">W52^2</f>
+      <c r="X52" s="1">
+        <f t="shared" ref="X52:X58" si="39">W52^2</f>
         <v>3.662865738566754E-4</v>
       </c>
     </row>
@@ -3068,69 +3112,69 @@
       <c r="A53">
         <v>3</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="1">
         <v>-1.3378989999999999</v>
       </c>
-      <c r="C53" s="2">
-        <f t="shared" si="28"/>
+      <c r="C53" s="1">
+        <f t="shared" si="30"/>
         <v>0.8572451762442691</v>
       </c>
-      <c r="D53" s="2">
-        <f t="shared" si="29"/>
+      <c r="D53" s="1">
+        <f t="shared" si="31"/>
         <v>0.73486929219406805</v>
       </c>
       <c r="F53">
         <v>3</v>
       </c>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-      <c r="I53" s="2">
-        <f t="shared" si="31"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="I53" s="1">
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="K53">
         <v>3</v>
       </c>
-      <c r="L53" s="2">
+      <c r="L53" s="1">
         <v>-16.372800000000002</v>
       </c>
-      <c r="M53" s="2">
-        <f t="shared" si="32"/>
+      <c r="M53" s="1">
+        <f t="shared" si="34"/>
         <v>0.15183084183278672</v>
       </c>
-      <c r="N53" s="2">
-        <f t="shared" si="33"/>
+      <c r="N53" s="1">
+        <f t="shared" si="35"/>
         <v>2.3052604531652698E-2</v>
       </c>
       <c r="P53">
         <v>3</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q53" s="1">
         <v>-20.612100000000002</v>
       </c>
-      <c r="R53" s="2">
-        <f t="shared" si="34"/>
+      <c r="R53" s="1">
+        <f t="shared" si="36"/>
         <v>9.3195512297420985E-2</v>
       </c>
-      <c r="S53" s="2">
-        <f t="shared" si="35"/>
+      <c r="S53" s="1">
+        <f t="shared" si="37"/>
         <v>8.6854035123787466E-3</v>
       </c>
       <c r="U53">
         <v>3</v>
       </c>
-      <c r="V53" s="2">
+      <c r="V53" s="1">
         <v>-32.015265999999997</v>
       </c>
-      <c r="W53" s="2">
-        <f t="shared" si="36"/>
+      <c r="W53" s="1">
+        <f t="shared" si="38"/>
         <v>2.5074755097236185E-2</v>
       </c>
-      <c r="X53" s="2">
-        <f t="shared" si="37"/>
+      <c r="X53" s="1">
+        <f t="shared" si="39"/>
         <v>6.2874334318637208E-4</v>
       </c>
     </row>
@@ -3138,69 +3182,69 @@
       <c r="A54">
         <v>4</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="1">
         <v>-34.740749999999998</v>
       </c>
-      <c r="C54" s="2">
-        <f t="shared" si="28"/>
+      <c r="C54" s="1">
+        <f t="shared" si="30"/>
         <v>1.8321562144563951E-2</v>
       </c>
-      <c r="D54" s="2">
-        <f t="shared" si="29"/>
+      <c r="D54" s="1">
+        <f t="shared" si="31"/>
         <v>3.3567963941711878E-4</v>
       </c>
       <c r="F54">
         <v>4</v>
       </c>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-      <c r="I54" s="2">
-        <f t="shared" si="31"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="I54" s="1">
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="K54">
         <v>4</v>
       </c>
-      <c r="L54" s="2">
+      <c r="L54" s="1">
         <v>-50.403146999999997</v>
       </c>
-      <c r="M54" s="2">
-        <f t="shared" si="32"/>
+      <c r="M54" s="1">
+        <f t="shared" si="34"/>
         <v>3.0188577545561608E-3</v>
       </c>
-      <c r="N54" s="2">
-        <f t="shared" si="33"/>
+      <c r="N54" s="1">
+        <f t="shared" si="35"/>
         <v>9.1135021422438646E-6</v>
       </c>
       <c r="P54">
         <v>4</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q54" s="1">
         <v>-27.214974999999999</v>
       </c>
-      <c r="R54" s="2">
-        <f t="shared" si="34"/>
+      <c r="R54" s="1">
+        <f t="shared" si="36"/>
         <v>4.3576390087146852E-2</v>
       </c>
-      <c r="S54" s="2">
-        <f t="shared" si="35"/>
+      <c r="S54" s="1">
+        <f t="shared" si="37"/>
         <v>1.8989017730271904E-3</v>
       </c>
       <c r="U54">
         <v>4</v>
       </c>
-      <c r="V54" s="2">
+      <c r="V54" s="1">
         <v>-39.060518000000002</v>
       </c>
-      <c r="W54" s="2">
-        <f t="shared" si="36"/>
+      <c r="W54" s="1">
+        <f t="shared" si="38"/>
         <v>1.114228082441481E-2</v>
       </c>
-      <c r="X54" s="2">
-        <f t="shared" si="37"/>
+      <c r="X54" s="1">
+        <f t="shared" si="39"/>
         <v>1.2415042197012197E-4</v>
       </c>
     </row>
@@ -3208,69 +3252,69 @@
       <c r="A55">
         <v>5</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="1">
         <v>-10.686389999999999</v>
       </c>
-      <c r="C55" s="2">
-        <f t="shared" si="28"/>
+      <c r="C55" s="1">
+        <f t="shared" si="30"/>
         <v>0.29220019404117403</v>
       </c>
-      <c r="D55" s="2">
-        <f t="shared" si="29"/>
+      <c r="D55" s="1">
+        <f t="shared" si="31"/>
         <v>8.5380953397699758E-2</v>
       </c>
       <c r="F55">
         <v>5</v>
       </c>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-      <c r="I55" s="2">
-        <f t="shared" si="31"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="I55" s="1">
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="K55">
         <v>5</v>
       </c>
-      <c r="L55" s="2">
+      <c r="L55" s="1">
         <v>-27.170342000000002</v>
       </c>
-      <c r="M55" s="2">
-        <f t="shared" si="32"/>
+      <c r="M55" s="1">
+        <f t="shared" si="34"/>
         <v>4.3800886457996166E-2</v>
       </c>
-      <c r="N55" s="2">
-        <f t="shared" si="33"/>
+      <c r="N55" s="1">
+        <f t="shared" si="35"/>
         <v>1.9185176545062719E-3</v>
       </c>
       <c r="P55">
         <v>5</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q55" s="1">
         <v>-33.5154</v>
       </c>
-      <c r="R55" s="2">
-        <f t="shared" si="34"/>
+      <c r="R55" s="1">
+        <f t="shared" si="36"/>
         <v>2.1097451637106794E-2</v>
       </c>
-      <c r="S55" s="2">
-        <f t="shared" si="35"/>
+      <c r="S55" s="1">
+        <f t="shared" si="37"/>
         <v>4.4510246558006014E-4</v>
       </c>
       <c r="U55">
         <v>5</v>
       </c>
-      <c r="V55" s="2">
+      <c r="V55" s="1">
         <v>-35.405248999999998</v>
       </c>
-      <c r="W55" s="2">
-        <f t="shared" si="36"/>
+      <c r="W55" s="1">
+        <f t="shared" si="38"/>
         <v>1.6972176910005642E-2</v>
       </c>
-      <c r="X55" s="2">
-        <f t="shared" si="37"/>
+      <c r="X55" s="1">
+        <f t="shared" si="39"/>
         <v>2.8805478906452866E-4</v>
       </c>
     </row>
@@ -3278,69 +3322,69 @@
       <c r="A56">
         <v>6</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>-14.70834</v>
       </c>
-      <c r="C56" s="2">
-        <f t="shared" si="28"/>
+      <c r="C56" s="1">
+        <f t="shared" si="30"/>
         <v>0.18390053809907606</v>
       </c>
-      <c r="D56" s="2">
-        <f t="shared" si="29"/>
+      <c r="D56" s="1">
+        <f t="shared" si="31"/>
         <v>3.381940791312972E-2</v>
       </c>
       <c r="F56">
         <v>6</v>
       </c>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-      <c r="I56" s="2">
-        <f t="shared" si="31"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="I56" s="1">
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="K56">
         <v>6</v>
       </c>
-      <c r="L56" s="2">
+      <c r="L56" s="1">
         <v>-29.822600000000001</v>
       </c>
-      <c r="M56" s="2">
-        <f t="shared" si="32"/>
+      <c r="M56" s="1">
+        <f t="shared" si="34"/>
         <v>3.2275278616212232E-2</v>
       </c>
-      <c r="N56" s="2">
-        <f t="shared" si="33"/>
+      <c r="N56" s="1">
+        <f t="shared" si="35"/>
         <v>1.0416936097541265E-3</v>
       </c>
       <c r="P56">
         <v>6</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="Q56" s="1">
         <v>-41.634569999999997</v>
       </c>
-      <c r="R56" s="2">
-        <f t="shared" si="34"/>
+      <c r="R56" s="1">
+        <f t="shared" si="36"/>
         <v>8.2845991510970794E-3</v>
       </c>
-      <c r="S56" s="2">
-        <f t="shared" si="35"/>
+      <c r="S56" s="1">
+        <f t="shared" si="37"/>
         <v>6.8634583094358449E-5</v>
       </c>
       <c r="U56">
         <v>6</v>
       </c>
-      <c r="V56" s="2">
+      <c r="V56" s="1">
         <v>-47.333219999999997</v>
       </c>
-      <c r="W56" s="2">
-        <f t="shared" si="36"/>
+      <c r="W56" s="1">
+        <f t="shared" si="38"/>
         <v>4.2987184363179618E-3</v>
       </c>
-      <c r="X56" s="2">
-        <f t="shared" si="37"/>
+      <c r="X56" s="1">
+        <f t="shared" si="39"/>
         <v>1.8478980194739941E-5</v>
       </c>
     </row>
@@ -3348,69 +3392,69 @@
       <c r="A57">
         <v>7</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="1">
         <v>-34.294128999999998</v>
       </c>
-      <c r="C57" s="2">
-        <f t="shared" si="28"/>
+      <c r="C57" s="1">
+        <f t="shared" si="30"/>
         <v>1.9288282136753567E-2</v>
       </c>
-      <c r="D57" s="2">
-        <f t="shared" si="29"/>
+      <c r="D57" s="1">
+        <f t="shared" si="31"/>
         <v>3.7203782778700678E-4</v>
       </c>
       <c r="F57">
         <v>7</v>
       </c>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-      <c r="I57" s="2">
-        <f t="shared" si="31"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="I57" s="1">
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="K57">
         <v>7</v>
       </c>
-      <c r="L57" s="2">
+      <c r="L57" s="1">
         <v>-45.264719999999997</v>
       </c>
-      <c r="M57" s="2">
-        <f t="shared" si="32"/>
+      <c r="M57" s="1">
+        <f t="shared" si="34"/>
         <v>5.454613713323099E-3</v>
       </c>
-      <c r="N57" s="2">
-        <f t="shared" si="33"/>
+      <c r="N57" s="1">
+        <f t="shared" si="35"/>
         <v>2.9752810761572407E-5</v>
       </c>
       <c r="P57">
         <v>7</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="Q57" s="1">
         <v>-42.151352000000003</v>
       </c>
-      <c r="R57" s="2">
-        <f t="shared" si="34"/>
+      <c r="R57" s="1">
+        <f t="shared" si="36"/>
         <v>7.8060692550336363E-3</v>
       </c>
-      <c r="S57" s="2">
-        <f t="shared" si="35"/>
+      <c r="S57" s="1">
+        <f t="shared" si="37"/>
         <v>6.0934717214381387E-5</v>
       </c>
       <c r="U57">
         <v>7</v>
       </c>
-      <c r="V57" s="2">
+      <c r="V57" s="1">
         <v>-40.07349</v>
       </c>
-      <c r="W57" s="2">
-        <f t="shared" si="36"/>
+      <c r="W57" s="1">
+        <f t="shared" si="38"/>
         <v>9.9157484332487635E-3</v>
       </c>
-      <c r="X57" s="2">
-        <f t="shared" si="37"/>
+      <c r="X57" s="1">
+        <f t="shared" si="39"/>
         <v>9.8322066991475313E-5</v>
       </c>
     </row>
@@ -3418,69 +3462,69 @@
       <c r="A58">
         <v>8</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="1">
         <v>-19.902857000000001</v>
       </c>
-      <c r="C58" s="2">
-        <f t="shared" si="28"/>
+      <c r="C58" s="1">
+        <f t="shared" si="30"/>
         <v>0.1011246775931692</v>
       </c>
-      <c r="D58" s="2">
-        <f t="shared" si="29"/>
+      <c r="D58" s="1">
+        <f t="shared" si="31"/>
         <v>1.0226200418322418E-2</v>
       </c>
       <c r="F58">
         <v>8</v>
       </c>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
-      <c r="I58" s="2">
-        <f t="shared" si="31"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="K58">
         <v>8</v>
       </c>
-      <c r="L58" s="2">
+      <c r="L58" s="1">
         <v>-35.542929999999998</v>
       </c>
-      <c r="M58" s="2">
-        <f t="shared" si="32"/>
+      <c r="M58" s="1">
+        <f t="shared" si="34"/>
         <v>1.6705270025258196E-2</v>
       </c>
-      <c r="N58" s="2">
-        <f t="shared" si="33"/>
+      <c r="N58" s="1">
+        <f t="shared" si="35"/>
         <v>2.7906604661678998E-4</v>
       </c>
       <c r="P58">
         <v>8</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q58" s="1">
         <v>-36.452325000000002</v>
       </c>
-      <c r="R58" s="2">
-        <f t="shared" si="34"/>
+      <c r="R58" s="1">
+        <f t="shared" si="36"/>
         <v>1.5044707549126774E-2</v>
       </c>
-      <c r="S58" s="2">
-        <f t="shared" si="35"/>
+      <c r="S58" s="1">
+        <f t="shared" si="37"/>
         <v>2.2634322523875215E-4</v>
       </c>
       <c r="U58">
         <v>8</v>
       </c>
-      <c r="V58" s="2">
+      <c r="V58" s="1">
         <v>-60.536642000000001</v>
       </c>
-      <c r="W58" s="2">
-        <f t="shared" si="36"/>
+      <c r="W58" s="1">
+        <f t="shared" si="38"/>
         <v>9.4008668162610552E-4</v>
       </c>
-      <c r="X58" s="2">
-        <f t="shared" si="37"/>
+      <c r="X58" s="1">
+        <f t="shared" si="39"/>
         <v>8.837629689707827E-7</v>
       </c>
     </row>
@@ -3488,35 +3532,35 @@
       <c r="A59" t="s">
         <v>1</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="1">
         <f>SQRT(SUM(D52:D58)/D51)</f>
         <v>0.71656648499661879</v>
       </c>
       <c r="F59" t="s">
         <v>1</v>
       </c>
-      <c r="G59" s="2">
+      <c r="G59" s="1">
         <f>SQRT(SUM(I52:I58)/I51)</f>
         <v>2.6457513110645907</v>
       </c>
       <c r="K59" t="s">
         <v>1</v>
       </c>
-      <c r="L59" s="2">
+      <c r="L59" s="1">
         <f>SQRT(SUM(N52:N58)/N51)</f>
         <v>0.22749789012894206</v>
       </c>
       <c r="P59" t="s">
         <v>1</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q59" s="1">
         <f>SQRT(SUM(S52:S58)/S51)</f>
         <v>0.10869463364035319</v>
       </c>
       <c r="U59" t="s">
         <v>1</v>
       </c>
-      <c r="V59" s="2">
+      <c r="V59" s="1">
         <f>SQRT(SUM(X52:X58)/X51)</f>
         <v>3.6164811843770912E-2</v>
       </c>
@@ -3525,35 +3569,35 @@
       <c r="A60" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <f>B59*100</f>
         <v>71.656648499661884</v>
       </c>
       <c r="F60" t="s">
         <v>6</v>
       </c>
-      <c r="G60" s="2">
+      <c r="G60" s="1">
         <f>G59*100</f>
         <v>264.57513110645908</v>
       </c>
       <c r="K60" t="s">
         <v>6</v>
       </c>
-      <c r="L60" s="2">
+      <c r="L60" s="1">
         <f>L59*100</f>
         <v>22.749789012894205</v>
       </c>
       <c r="P60" t="s">
         <v>6</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q60" s="1">
         <f>Q59*100</f>
         <v>10.869463364035319</v>
       </c>
       <c r="U60" t="s">
         <v>6</v>
       </c>
-      <c r="V60" s="2">
+      <c r="V60" s="1">
         <f>V59*100</f>
         <v>3.6164811843770912</v>
       </c>
@@ -3575,36 +3619,36 @@
     </row>
     <row r="64" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="65" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="F65" s="1" t="s">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="F65" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="K65" s="1" t="s">
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="K65" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="P65" s="1" t="s">
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="P65" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="Q65" s="1"/>
-      <c r="R65" s="1"/>
-      <c r="S65" s="1"/>
-      <c r="U65" s="1" t="s">
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+      <c r="U65" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="V65" s="1"/>
-      <c r="W65" s="1"/>
-      <c r="X65" s="1"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="2"/>
+      <c r="X65" s="2"/>
     </row>
     <row r="66" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
@@ -3672,70 +3716,70 @@
       <c r="A67">
         <v>1</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="1">
         <v>10.213380000000001</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="1">
         <f>10^(B67/20)</f>
         <v>3.2409251424982437</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="1">
         <f>C67^2</f>
         <v>10.503595779277262</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
-      <c r="G67" s="2">
+      <c r="G67" s="1">
         <v>7.6886840000000003</v>
       </c>
-      <c r="H67" s="2">
+      <c r="H67" s="1">
         <f>10^(G67/20)</f>
         <v>2.4234507594729195</v>
       </c>
-      <c r="I67" s="2">
+      <c r="I67" s="1">
         <f>H67^2</f>
         <v>5.8731135835898707</v>
       </c>
       <c r="K67">
         <v>1</v>
       </c>
-      <c r="L67" s="2">
+      <c r="L67" s="1">
         <v>9.7336778000000006</v>
       </c>
-      <c r="M67" s="2">
+      <c r="M67" s="1">
         <f>10^(L67/20)</f>
         <v>3.0667889516022617</v>
       </c>
-      <c r="N67" s="2">
+      <c r="N67" s="1">
         <f>M67^2</f>
         <v>9.4051944736696989</v>
       </c>
       <c r="P67">
         <v>1</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="Q67" s="1">
         <v>3.9975963000000001</v>
       </c>
-      <c r="R67" s="2">
+      <c r="R67" s="1">
         <f>10^(Q67/20)</f>
         <v>1.5844546558406989</v>
       </c>
-      <c r="S67" s="2">
+      <c r="S67" s="1">
         <f>R67^2</f>
         <v>2.5104965564152675</v>
       </c>
       <c r="U67">
         <v>1</v>
       </c>
-      <c r="V67" s="2">
+      <c r="V67" s="1">
         <v>1.1579819</v>
       </c>
-      <c r="W67" s="2">
+      <c r="W67" s="1">
         <f>10^(V67/20)</f>
         <v>1.142612826598657</v>
       </c>
-      <c r="X67" s="2">
+      <c r="X67" s="1">
         <f>W67^2</f>
         <v>1.3055640715077728</v>
       </c>
@@ -3744,71 +3788,71 @@
       <c r="A68">
         <v>2</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="1">
         <v>6.6581945999999999</v>
       </c>
-      <c r="C68" s="2">
-        <f t="shared" ref="C68:C74" si="38">10^(B68/20)</f>
+      <c r="C68" s="1">
+        <f t="shared" ref="C68:C74" si="40">10^(B68/20)</f>
         <v>2.152334316163111</v>
       </c>
-      <c r="D68" s="2">
-        <f t="shared" ref="D68:D74" si="39">C68^2</f>
+      <c r="D68" s="1">
+        <f t="shared" ref="D68:D74" si="41">C68^2</f>
         <v>4.632543008533327</v>
       </c>
       <c r="F68">
         <v>2</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G68" s="1">
         <v>-3.8390048999999999</v>
       </c>
-      <c r="H68" s="2">
-        <f t="shared" ref="H68:H74" si="40">10^(G68/20)</f>
+      <c r="H68" s="1">
+        <f t="shared" ref="H68:H74" si="42">10^(G68/20)</f>
         <v>0.64276135113116617</v>
       </c>
-      <c r="I68" s="2">
-        <f t="shared" ref="I68:I74" si="41">H68^2</f>
+      <c r="I68" s="1">
+        <f t="shared" ref="I68:I74" si="43">H68^2</f>
         <v>0.41314215450796227</v>
       </c>
       <c r="K68">
         <v>2</v>
       </c>
-      <c r="L68" s="2">
+      <c r="L68" s="1">
         <v>3.2868900000000001</v>
       </c>
-      <c r="M68" s="2">
-        <f t="shared" ref="M68:M74" si="42">10^(L68/20)</f>
+      <c r="M68" s="1">
+        <f t="shared" ref="M68:M74" si="44">10^(L68/20)</f>
         <v>1.4599719100093851</v>
       </c>
-      <c r="N68" s="2">
-        <f t="shared" ref="N68:N74" si="43">M68^2</f>
+      <c r="N68" s="1">
+        <f t="shared" ref="N68:N74" si="45">M68^2</f>
         <v>2.1315179780164519</v>
       </c>
       <c r="P68">
         <v>2</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="Q68" s="1">
         <v>-17.12059</v>
       </c>
-      <c r="R68" s="2">
-        <f t="shared" ref="R68:R74" si="44">10^(Q68/20)</f>
+      <c r="R68" s="1">
+        <f t="shared" ref="R68:R74" si="46">10^(Q68/20)</f>
         <v>0.13930621742276703</v>
       </c>
-      <c r="S68" s="2">
-        <f t="shared" ref="S68:S74" si="45">R68^2</f>
+      <c r="S68" s="1">
+        <f t="shared" ref="S68:S74" si="47">R68^2</f>
         <v>1.940622221263924E-2</v>
       </c>
       <c r="U68">
         <v>2</v>
       </c>
-      <c r="V68" s="2">
+      <c r="V68" s="1">
         <v>-32.539209999999997</v>
       </c>
-      <c r="W68" s="2">
-        <f t="shared" ref="W68:W74" si="46">10^(V68/20)</f>
+      <c r="W68" s="1">
+        <f t="shared" ref="W68:W74" si="48">10^(V68/20)</f>
         <v>2.3606929334228362E-2</v>
       </c>
-      <c r="X68" s="2">
-        <f t="shared" ref="X68:X74" si="47">W68^2</f>
+      <c r="X68" s="1">
+        <f t="shared" ref="X68:X74" si="49">W68^2</f>
         <v>5.5728711259125159E-4</v>
       </c>
     </row>
@@ -3816,71 +3860,71 @@
       <c r="A69">
         <v>3</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="1">
         <v>-0.71119622999999998</v>
       </c>
-      <c r="C69" s="2">
-        <f t="shared" si="38"/>
+      <c r="C69" s="1">
+        <f t="shared" si="40"/>
         <v>0.92138298614742209</v>
       </c>
-      <c r="D69" s="2">
-        <f t="shared" si="39"/>
+      <c r="D69" s="1">
+        <f t="shared" si="41"/>
         <v>0.84894660716194059</v>
       </c>
       <c r="F69">
         <v>3</v>
       </c>
-      <c r="G69" s="2">
+      <c r="G69" s="1">
         <v>-14.001612</v>
       </c>
-      <c r="H69" s="2">
-        <f t="shared" si="40"/>
+      <c r="H69" s="1">
+        <f t="shared" si="42"/>
         <v>0.19948920518704</v>
       </c>
-      <c r="I69" s="2">
-        <f t="shared" si="41"/>
+      <c r="I69" s="1">
+        <f t="shared" si="43"/>
         <v>3.9795942986156949E-2</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
-      <c r="L69" s="2">
+      <c r="L69" s="1">
         <v>-17.306818</v>
       </c>
-      <c r="M69" s="2">
-        <f t="shared" si="42"/>
+      <c r="M69" s="1">
+        <f t="shared" si="44"/>
         <v>0.13635124256218747</v>
       </c>
-      <c r="N69" s="2">
-        <f t="shared" si="43"/>
+      <c r="N69" s="1">
+        <f t="shared" si="45"/>
         <v>1.8591661348252485E-2</v>
       </c>
       <c r="P69">
         <v>3</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69" s="1">
         <v>-19.760771999999999</v>
       </c>
-      <c r="R69" s="2">
-        <f t="shared" si="44"/>
+      <c r="R69" s="1">
+        <f t="shared" si="46"/>
         <v>0.1027924932319688</v>
       </c>
-      <c r="S69" s="2">
-        <f t="shared" si="45"/>
+      <c r="S69" s="1">
+        <f t="shared" si="47"/>
         <v>1.0566296664844353E-2</v>
       </c>
       <c r="U69">
         <v>3</v>
       </c>
-      <c r="V69" s="2">
+      <c r="V69" s="1">
         <v>-30.609535000000001</v>
       </c>
-      <c r="W69" s="2">
-        <f t="shared" si="46"/>
+      <c r="W69" s="1">
+        <f t="shared" si="48"/>
         <v>2.9479712923301316E-2</v>
       </c>
-      <c r="X69" s="2">
-        <f t="shared" si="47"/>
+      <c r="X69" s="1">
+        <f t="shared" si="49"/>
         <v>8.690534740402586E-4</v>
       </c>
     </row>
@@ -3888,71 +3932,71 @@
       <c r="A70">
         <v>4</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="1">
         <v>-27.195322000000001</v>
       </c>
-      <c r="C70" s="2">
-        <f t="shared" si="38"/>
+      <c r="C70" s="1">
+        <f t="shared" si="40"/>
         <v>4.3675099192299137E-2</v>
       </c>
-      <c r="D70" s="2">
-        <f t="shared" si="39"/>
+      <c r="D70" s="1">
+        <f t="shared" si="41"/>
         <v>1.9075142894571686E-3</v>
       </c>
       <c r="F70">
         <v>4</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G70" s="1">
         <v>-23.803443999999999</v>
       </c>
-      <c r="H70" s="2">
-        <f t="shared" si="40"/>
+      <c r="H70" s="1">
+        <f t="shared" si="42"/>
         <v>6.4539827455276713E-2</v>
       </c>
-      <c r="I70" s="2">
-        <f t="shared" si="41"/>
+      <c r="I70" s="1">
+        <f t="shared" si="43"/>
         <v>4.1653893279568902E-3</v>
       </c>
       <c r="K70">
         <v>4</v>
       </c>
-      <c r="L70" s="2">
+      <c r="L70" s="1">
         <v>-10.96701</v>
       </c>
-      <c r="M70" s="2">
-        <f t="shared" si="42"/>
+      <c r="M70" s="1">
+        <f t="shared" si="44"/>
         <v>0.2829107825538919</v>
       </c>
-      <c r="N70" s="2">
-        <f t="shared" si="43"/>
+      <c r="N70" s="1">
+        <f t="shared" si="45"/>
         <v>8.0038510885255501E-2</v>
       </c>
       <c r="P70">
         <v>4</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70" s="1">
         <v>-26.777850000000001</v>
       </c>
-      <c r="R70" s="2">
-        <f t="shared" si="44"/>
+      <c r="R70" s="1">
+        <f t="shared" si="46"/>
         <v>4.5825530364885549E-2</v>
       </c>
-      <c r="S70" s="2">
-        <f t="shared" si="45"/>
+      <c r="S70" s="1">
+        <f t="shared" si="47"/>
         <v>2.0999792332230473E-3</v>
       </c>
       <c r="U70">
         <v>4</v>
       </c>
-      <c r="V70" s="2">
+      <c r="V70" s="1">
         <v>-37.325380000000003</v>
       </c>
-      <c r="W70" s="2">
-        <f t="shared" si="46"/>
+      <c r="W70" s="1">
+        <f t="shared" si="48"/>
         <v>1.3606016710115248E-2</v>
       </c>
-      <c r="X70" s="2">
-        <f t="shared" si="47"/>
+      <c r="X70" s="1">
+        <f t="shared" si="49"/>
         <v>1.8512369071593536E-4</v>
       </c>
     </row>
@@ -3960,71 +4004,71 @@
       <c r="A71">
         <v>5</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="1">
         <v>-10.644600000000001</v>
       </c>
-      <c r="C71" s="2">
-        <f t="shared" si="38"/>
+      <c r="C71" s="1">
+        <f t="shared" si="40"/>
         <v>0.29360943005423967</v>
       </c>
-      <c r="D71" s="2">
-        <f t="shared" si="39"/>
+      <c r="D71" s="1">
+        <f t="shared" si="41"/>
         <v>8.6206497416775454E-2</v>
       </c>
       <c r="F71">
         <v>5</v>
       </c>
-      <c r="G71" s="2">
+      <c r="G71" s="1">
         <v>-21.88279</v>
       </c>
-      <c r="H71" s="2">
-        <f t="shared" si="40"/>
+      <c r="H71" s="1">
+        <f t="shared" si="42"/>
         <v>8.0511978663377406E-2</v>
       </c>
-      <c r="I71" s="2">
-        <f t="shared" si="41"/>
+      <c r="I71" s="1">
+        <f t="shared" si="43"/>
         <v>6.4821787082921384E-3</v>
       </c>
       <c r="K71">
         <v>5</v>
       </c>
-      <c r="L71" s="2">
+      <c r="L71" s="1">
         <v>-20.722280000000001</v>
       </c>
-      <c r="M71" s="2">
-        <f t="shared" si="42"/>
+      <c r="M71" s="1">
+        <f t="shared" si="44"/>
         <v>9.2020799032672421E-2</v>
       </c>
-      <c r="N71" s="2">
-        <f t="shared" si="43"/>
+      <c r="N71" s="1">
+        <f t="shared" si="45"/>
         <v>8.4678274546114863E-3</v>
       </c>
       <c r="P71">
         <v>5</v>
       </c>
-      <c r="Q71" s="2">
+      <c r="Q71" s="1">
         <v>-33.885595000000002</v>
       </c>
-      <c r="R71" s="2">
-        <f t="shared" si="44"/>
+      <c r="R71" s="1">
+        <f t="shared" si="46"/>
         <v>2.0217164741691072E-2</v>
       </c>
-      <c r="S71" s="2">
-        <f t="shared" si="45"/>
+      <c r="S71" s="1">
+        <f t="shared" si="47"/>
         <v>4.0873375019267663E-4</v>
       </c>
       <c r="U71">
         <v>5</v>
       </c>
-      <c r="V71" s="2">
+      <c r="V71" s="1">
         <v>-34.319760000000002</v>
       </c>
-      <c r="W71" s="2">
-        <f t="shared" si="46"/>
+      <c r="W71" s="1">
+        <f t="shared" si="48"/>
         <v>1.923144866632448E-2</v>
       </c>
-      <c r="X71" s="2">
-        <f t="shared" si="47"/>
+      <c r="X71" s="1">
+        <f t="shared" si="49"/>
         <v>3.698486178054736E-4</v>
       </c>
     </row>
@@ -4032,71 +4076,71 @@
       <c r="A72">
         <v>6</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="1">
         <v>-13.612009</v>
       </c>
-      <c r="C72" s="2">
-        <f t="shared" si="38"/>
+      <c r="C72" s="1">
+        <f t="shared" si="40"/>
         <v>0.20864094927009671</v>
       </c>
-      <c r="D72" s="2">
-        <f t="shared" si="39"/>
+      <c r="D72" s="1">
+        <f t="shared" si="41"/>
         <v>4.353104571232707E-2</v>
       </c>
       <c r="F72">
         <v>6</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G72" s="1">
         <v>-34.39678</v>
       </c>
-      <c r="H72" s="2">
-        <f t="shared" si="40"/>
+      <c r="H72" s="1">
+        <f t="shared" si="42"/>
         <v>1.9061672340701982E-2</v>
       </c>
-      <c r="I72" s="2">
-        <f t="shared" si="41"/>
+      <c r="I72" s="1">
+        <f t="shared" si="43"/>
         <v>3.6334735242428298E-4</v>
       </c>
       <c r="K72">
         <v>6</v>
       </c>
-      <c r="L72" s="2">
+      <c r="L72" s="1">
         <v>-20.412289999999999</v>
       </c>
-      <c r="M72" s="2">
-        <f t="shared" si="42"/>
+      <c r="M72" s="1">
+        <f t="shared" si="44"/>
         <v>9.5364228572764248E-2</v>
       </c>
-      <c r="N72" s="2">
-        <f t="shared" si="43"/>
+      <c r="N72" s="1">
+        <f t="shared" si="45"/>
         <v>9.0943360912784255E-3</v>
       </c>
       <c r="P72">
         <v>6</v>
       </c>
-      <c r="Q72" s="2">
+      <c r="Q72" s="1">
         <v>-38.725464000000002</v>
       </c>
-      <c r="R72" s="2">
-        <f t="shared" si="44"/>
+      <c r="R72" s="1">
+        <f t="shared" si="46"/>
         <v>1.1580486376622446E-2</v>
       </c>
-      <c r="S72" s="2">
-        <f t="shared" si="45"/>
+      <c r="S72" s="1">
+        <f t="shared" si="47"/>
         <v>1.3410766471913806E-4</v>
       </c>
       <c r="U72">
         <v>6</v>
       </c>
-      <c r="V72" s="2">
+      <c r="V72" s="1">
         <v>-46.315759999999997</v>
       </c>
-      <c r="W72" s="2">
-        <f t="shared" si="46"/>
+      <c r="W72" s="1">
+        <f t="shared" si="48"/>
         <v>4.8329466381010211E-3</v>
       </c>
-      <c r="X72" s="2">
-        <f t="shared" si="47"/>
+      <c r="X72" s="1">
+        <f t="shared" si="49"/>
         <v>2.3357373206731961E-5</v>
       </c>
     </row>
@@ -4104,71 +4148,71 @@
       <c r="A73">
         <v>7</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="1">
         <v>-51.453702999999997</v>
       </c>
-      <c r="C73" s="2">
-        <f t="shared" si="38"/>
+      <c r="C73" s="1">
+        <f t="shared" si="40"/>
         <v>2.6749449578323142E-3</v>
       </c>
-      <c r="D73" s="2">
-        <f t="shared" si="39"/>
+      <c r="D73" s="1">
+        <f t="shared" si="41"/>
         <v>7.1553305274325207E-6</v>
       </c>
       <c r="F73">
         <v>7</v>
       </c>
-      <c r="G73" s="2">
+      <c r="G73" s="1">
         <v>-27.474930000000001</v>
       </c>
-      <c r="H73" s="2">
-        <f t="shared" si="40"/>
+      <c r="H73" s="1">
+        <f t="shared" si="42"/>
         <v>4.2291540020292617E-2</v>
       </c>
-      <c r="I73" s="2">
-        <f t="shared" si="41"/>
+      <c r="I73" s="1">
+        <f t="shared" si="43"/>
         <v>1.7885743572880121E-3</v>
       </c>
       <c r="K73">
         <v>7</v>
       </c>
-      <c r="L73" s="2">
+      <c r="L73" s="1">
         <v>-26.607890000000001</v>
       </c>
-      <c r="M73" s="2">
-        <f t="shared" si="42"/>
+      <c r="M73" s="1">
+        <f t="shared" si="44"/>
         <v>4.6731045771555117E-2</v>
       </c>
-      <c r="N73" s="2">
-        <f t="shared" si="43"/>
+      <c r="N73" s="1">
+        <f t="shared" si="45"/>
         <v>2.1837906389031796E-3</v>
       </c>
       <c r="P73">
         <v>7</v>
       </c>
-      <c r="Q73" s="2">
+      <c r="Q73" s="1">
         <v>-40.383141999999999</v>
       </c>
-      <c r="R73" s="2">
-        <f t="shared" si="44"/>
+      <c r="R73" s="1">
+        <f t="shared" si="46"/>
         <v>9.5684788224553296E-3</v>
       </c>
-      <c r="S73" s="2">
-        <f t="shared" si="45"/>
+      <c r="S73" s="1">
+        <f t="shared" si="47"/>
         <v>9.1555786975776131E-5</v>
       </c>
       <c r="U73">
         <v>7</v>
       </c>
-      <c r="V73" s="2">
+      <c r="V73" s="1">
         <v>-39.640098999999999</v>
       </c>
-      <c r="W73" s="2">
-        <f t="shared" si="46"/>
+      <c r="W73" s="1">
+        <f t="shared" si="48"/>
         <v>1.0423055493393609E-2</v>
       </c>
-      <c r="X73" s="2">
-        <f t="shared" si="47"/>
+      <c r="X73" s="1">
+        <f t="shared" si="49"/>
         <v>1.086400858183627E-4</v>
       </c>
     </row>
@@ -4176,71 +4220,71 @@
       <c r="A74">
         <v>8</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="1">
         <v>-19.997854</v>
       </c>
-      <c r="C74" s="2">
-        <f t="shared" si="38"/>
+      <c r="C74" s="1">
+        <f t="shared" si="40"/>
         <v>0.10002470979041372</v>
       </c>
-      <c r="D74" s="2">
-        <f t="shared" si="39"/>
+      <c r="D74" s="1">
+        <f t="shared" si="41"/>
         <v>1.0004942568656488E-2</v>
       </c>
       <c r="F74">
         <v>8</v>
       </c>
-      <c r="G74" s="2">
+      <c r="G74" s="1">
         <v>-34.282798</v>
       </c>
-      <c r="H74" s="2">
-        <f t="shared" si="40"/>
+      <c r="H74" s="1">
+        <f t="shared" si="42"/>
         <v>1.9313460690947599E-2</v>
       </c>
-      <c r="I74" s="2">
-        <f t="shared" si="41"/>
+      <c r="I74" s="1">
+        <f t="shared" si="43"/>
         <v>3.7300976386077812E-4</v>
       </c>
       <c r="K74">
         <v>8</v>
       </c>
-      <c r="L74" s="2">
+      <c r="L74" s="1">
         <v>-24.836721000000001</v>
       </c>
-      <c r="M74" s="2">
-        <f t="shared" si="42"/>
+      <c r="M74" s="1">
+        <f t="shared" si="44"/>
         <v>5.7301230736357414E-2</v>
       </c>
-      <c r="N74" s="2">
-        <f t="shared" si="43"/>
+      <c r="N74" s="1">
+        <f t="shared" si="45"/>
         <v>3.2834310439012718E-3</v>
       </c>
       <c r="P74">
         <v>8</v>
       </c>
-      <c r="Q74" s="2">
+      <c r="Q74" s="1">
         <v>-35.942659999999997</v>
       </c>
-      <c r="R74" s="2">
-        <f t="shared" si="44"/>
+      <c r="R74" s="1">
+        <f t="shared" si="46"/>
         <v>1.5953904939419682E-2</v>
       </c>
-      <c r="S74" s="2">
-        <f t="shared" si="45"/>
+      <c r="S74" s="1">
+        <f t="shared" si="47"/>
         <v>2.5452708281603972E-4</v>
       </c>
       <c r="U74">
         <v>8</v>
       </c>
-      <c r="V74" s="2">
+      <c r="V74" s="1">
         <v>-55.865409999999997</v>
       </c>
-      <c r="W74" s="2">
-        <f t="shared" si="46"/>
+      <c r="W74" s="1">
+        <f t="shared" si="48"/>
         <v>1.6096427580770041E-3</v>
       </c>
-      <c r="X74" s="2">
-        <f t="shared" si="47"/>
+      <c r="X74" s="1">
+        <f t="shared" si="49"/>
         <v>2.5909498086297447E-6</v>
       </c>
     </row>
@@ -4248,35 +4292,35 @@
       <c r="A75" t="s">
         <v>1</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="1">
         <f>SQRT(SUM(D68:D74)/D67)</f>
         <v>0.73167920075383452</v>
       </c>
       <c r="F75" t="s">
         <v>1</v>
       </c>
-      <c r="G75" s="2">
+      <c r="G75" s="1">
         <f>SQRT(SUM(I68:I74)/I67)</f>
         <v>0.2817152053786387</v>
       </c>
       <c r="K75" t="s">
         <v>1</v>
       </c>
-      <c r="L75" s="2">
+      <c r="L75" s="1">
         <f>SQRT(SUM(N68:N74)/N67)</f>
         <v>0.48945617989768869</v>
       </c>
       <c r="P75" t="s">
         <v>1</v>
       </c>
-      <c r="Q75" s="2">
+      <c r="Q75" s="1">
         <f>SQRT(SUM(S68:S74)/S67)</f>
         <v>0.11458378323700356</v>
       </c>
       <c r="U75" t="s">
         <v>1</v>
       </c>
-      <c r="V75" s="2">
+      <c r="V75" s="1">
         <f>SQRT(SUM(X68:X74)/X67)</f>
         <v>4.0257667456496685E-2</v>
       </c>
@@ -4285,35 +4329,35 @@
       <c r="A76" t="s">
         <v>6</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="1">
         <f>B75*100</f>
         <v>73.167920075383449</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="2">
+      <c r="G76" s="1">
         <f>G75*100</f>
         <v>28.17152053786387</v>
       </c>
       <c r="K76" t="s">
         <v>6</v>
       </c>
-      <c r="L76" s="2">
+      <c r="L76" s="1">
         <f>L75*100</f>
         <v>48.94561798976887</v>
       </c>
       <c r="P76" t="s">
         <v>6</v>
       </c>
-      <c r="Q76" s="2">
+      <c r="Q76" s="1">
         <f>Q75*100</f>
         <v>11.458378323700357</v>
       </c>
       <c r="U76" t="s">
         <v>6</v>
       </c>
-      <c r="V76" s="2">
+      <c r="V76" s="1">
         <f>V75*100</f>
         <v>4.0257667456496682</v>
       </c>

--- a/EXCEL FILEOVI/ZAVRSNI EXCEL - SIM RESULTS .xlsx
+++ b/EXCEL FILEOVI/ZAVRSNI EXCEL - SIM RESULTS .xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/523341E057C2D1B5/Documents/2526 - LJETNI SEMESTAR/Bachelor-Thesis/EXCEL FILEOVI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2054" documentId="8_{749E225B-507B-4645-922D-F24EE2B83FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F76783B9-34B5-4C8E-8708-90FAA853D165}"/>
+  <xr:revisionPtr revIDLastSave="2055" documentId="8_{749E225B-507B-4645-922D-F24EE2B83FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94C9D64A-A2CF-4231-925A-18DBFBDA2286}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="4" xr2:uid="{5A5A50C3-7C6B-466F-847F-D23E3D13151B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{5A5A50C3-7C6B-466F-847F-D23E3D13151B}"/>
   </bookViews>
   <sheets>
     <sheet name="SZE SIM RESULTS" sheetId="1" r:id="rId1"/>
     <sheet name="SZC SIM RESULTS" sheetId="2" r:id="rId2"/>
-    <sheet name="B-SIM" sheetId="3" r:id="rId3"/>
-    <sheet name="AB-L-SIM" sheetId="6" r:id="rId4"/>
-    <sheet name="AB-H-SIM" sheetId="9" r:id="rId5"/>
+    <sheet name="AB-L-SIM" sheetId="6" r:id="rId3"/>
+    <sheet name="AB-H-SIM" sheetId="9" r:id="rId4"/>
+    <sheet name="B-SIM" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,85 +42,70 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="46">
   <si>
+    <t>Harmonik</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>HD value</t>
+  </si>
+  <si>
+    <t>HD [V]</t>
+  </si>
+  <si>
+    <t>HD [dB]</t>
+  </si>
+  <si>
+    <t>THD [%]</t>
+  </si>
+  <si>
+    <t>korisnost [%]</t>
+  </si>
+  <si>
+    <t>Output Power [W]</t>
+  </si>
+  <si>
+    <t>Input Power [W]</t>
+  </si>
+  <si>
     <t>SZE / Re = 250 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 500 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 1000 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 2000 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 3000 / Rt = 550</t>
+  </si>
+  <si>
+    <t>SZE / Re = 3000 / Rt = 1100</t>
+  </si>
+  <si>
+    <t>SZE / Re = 2000 / Rt = 1100</t>
+  </si>
+  <si>
+    <t>SZE / Re = 1000 / Rt = 1100</t>
+  </si>
+  <si>
+    <t>SZE / Re = 500 / Rt = 1100</t>
   </si>
   <si>
     <t>SZE / Re = 250 / Rt = 1100</t>
   </si>
   <si>
-    <t>Re = 250 Rt = 2200</t>
-  </si>
-  <si>
     <t>SZE / Re = 250 / Rt = 3300</t>
-  </si>
-  <si>
-    <t>SZE / Re = 250 / Rt = 4400</t>
-  </si>
-  <si>
-    <t>Harmonik</t>
-  </si>
-  <si>
-    <t>HD [dB]</t>
-  </si>
-  <si>
-    <t>HD [V]</t>
-  </si>
-  <si>
-    <t>HD value</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>THD [%]</t>
-  </si>
-  <si>
-    <t>Piz [mW]</t>
-  </si>
-  <si>
-    <t>Pcc [mW]</t>
-  </si>
-  <si>
-    <t>korisnost [%]</t>
-  </si>
-  <si>
-    <t>SZE / Re = 500 / Rt = 550</t>
-  </si>
-  <si>
-    <t>SZE / Re = 500 / Rt = 1100</t>
-  </si>
-  <si>
-    <t>Re = 500 Rt = 2200</t>
   </si>
   <si>
     <t>SZE / Re = 500 / Rt = 3300</t>
   </si>
   <si>
-    <t>SZE / Re = 500 / Rt = 4400</t>
-  </si>
-  <si>
-    <t>SZE / Re = 1000 / Rt = 550</t>
-  </si>
-  <si>
-    <t>SZE / Re = 1000 / Rt = 1100</t>
-  </si>
-  <si>
-    <t>Re = 1000 Rt = 2200</t>
-  </si>
-  <si>
     <t>SZE / Re = 1000 / Rt = 3300</t>
-  </si>
-  <si>
-    <t>SZE / Re = 1000 / Rt = 4400</t>
-  </si>
-  <si>
-    <t>SZE / Re = 2000 / Rt = 550</t>
-  </si>
-  <si>
-    <t>SZE / Re = 2000 / Rt = 1100</t>
-  </si>
-  <si>
-    <t>Re = 2000 Rt = 2200</t>
   </si>
   <si>
     <t>SZE / Re = 2000 / Rt = 3300</t>
@@ -129,19 +114,25 @@
     <t>SZE / Re = 3000 / Rt = 3300</t>
   </si>
   <si>
-    <t>SZE / Re = 3000 / Rt = 550</t>
-  </si>
-  <si>
-    <t>SZE / Re = 3000 / Rt = 1100</t>
-  </si>
-  <si>
-    <t>Re = 3000 Rt = 2200</t>
-  </si>
-  <si>
     <t>SZE / Re = 3000 / Rt = 4400</t>
   </si>
   <si>
+    <t>SZE / Re = 1000 / Rt = 4400</t>
+  </si>
+  <si>
+    <t>SZE / Re = 500 / Rt = 4400</t>
+  </si>
+  <si>
+    <t>SZE / Re = 250 / Rt = 4400</t>
+  </si>
+  <si>
     <t>Rt = 250</t>
+  </si>
+  <si>
+    <t>Pcc</t>
+  </si>
+  <si>
+    <t>Piz</t>
   </si>
   <si>
     <t>Rt = 500</t>
@@ -156,18 +147,6 @@
     <t>Rt = 2000</t>
   </si>
   <si>
-    <t>Piz</t>
-  </si>
-  <si>
-    <t>Output Power [W]</t>
-  </si>
-  <si>
-    <t>Pcc</t>
-  </si>
-  <si>
-    <t>Input Power [W]</t>
-  </si>
-  <si>
     <t>Uul = 0.8V</t>
   </si>
   <si>
@@ -177,7 +156,28 @@
     <t>Uul = 16V</t>
   </si>
   <si>
+    <t>Pcc [mW]</t>
+  </si>
+  <si>
+    <t>Piz [mW]</t>
+  </si>
+  <si>
     <t>Pcc [W]</t>
+  </si>
+  <si>
+    <t>Re = 250 Rt = 2200</t>
+  </si>
+  <si>
+    <t>Re = 500 Rt = 2200</t>
+  </si>
+  <si>
+    <t>Re = 1000 Rt = 2200</t>
+  </si>
+  <si>
+    <t>Re = 2000 Rt = 2200</t>
+  </si>
+  <si>
+    <t>Re = 3000 Rt = 2200</t>
   </si>
 </sst>
 </file>
@@ -187,7 +187,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +309,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -629,136 +633,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79FF54C5-DE8F-4674-B282-5F9819316D0D}">
   <dimension ref="A1:X90"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="13" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.46484375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.9296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.46484375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.9296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.53125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.46484375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.9296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.46484375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.9296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.265625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="14" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="8.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="14.25" customHeight="1">
+    <row r="1" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="F1" s="6" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="8"/>
       <c r="K1" s="5" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="P1" s="5" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
       <c r="U1" s="5" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
     </row>
-    <row r="2" spans="1:24" ht="14.25" customHeight="1">
+    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="14.25" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -830,7 +834,7 @@
         <v>10.503595779277262</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="14.25" customHeight="1">
+    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -902,7 +906,7 @@
         <v>4.632543008533327</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="14.25" customHeight="1">
+    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -974,7 +978,7 @@
         <v>0.84894660716194059</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.25" customHeight="1">
+    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1046,7 +1050,7 @@
         <v>1.9075142894571686E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.25" customHeight="1">
+    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1118,7 +1122,7 @@
         <v>8.6206497416775454E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.25" customHeight="1">
+    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1190,7 +1194,7 @@
         <v>4.353104571232707E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" customHeight="1">
+    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1262,7 +1266,7 @@
         <v>7.1553305274325207E-6</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="14.25" customHeight="1">
+    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1334,9 +1338,9 @@
         <v>1.0004942568656488E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="14.25" customHeight="1">
+    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B11" s="2">
         <f>SQRT(SUM(D4:D10)/D3)</f>
@@ -1345,7 +1349,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <f>SQRT(SUM(I4:I10)/I3)</f>
@@ -1354,7 +1358,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2">
         <f>SQRT(SUM(N4:N10)/N3)</f>
@@ -1363,7 +1367,7 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="P11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="2">
         <f>SQRT(SUM(S4:S10)/S3)</f>
@@ -1372,7 +1376,7 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="U11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2">
         <f>SQRT(SUM(X4:X10)/X3)</f>
@@ -1381,9 +1385,9 @@
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
     </row>
-    <row r="12" spans="1:24" ht="14.25" customHeight="1">
+    <row r="12" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B12" s="4">
         <f>B11*100</f>
@@ -1392,7 +1396,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12" s="4">
         <f>G11*100</f>
@@ -1401,7 +1405,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="K12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L12" s="4">
         <f>L11*100</f>
@@ -1410,7 +1414,7 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="P12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="4">
         <f>Q11*100</f>
@@ -1419,7 +1423,7 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="U12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V12" s="4">
         <f>V11*100</f>
@@ -1428,9 +1432,9 @@
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
     </row>
-    <row r="13" spans="1:24" ht="14.25" customHeight="1">
+    <row r="13" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1">
         <v>16.846</v>
@@ -1438,7 +1442,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
         <v>7.3594999999999997</v>
@@ -1446,7 +1450,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L13" s="1">
         <v>5.4745999999999997</v>
@@ -1454,7 +1458,7 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="P13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="Q13" s="1">
         <v>4.6539999999999999</v>
@@ -1462,7 +1466,7 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="U13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="V13" s="1">
         <v>3.6638000000000002</v>
@@ -1470,9 +1474,9 @@
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
     </row>
-    <row r="14" spans="1:24" ht="14.25" customHeight="1">
+    <row r="14" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1">
         <v>78.311999999999998</v>
@@ -1480,7 +1484,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G14" s="1">
         <v>65.12</v>
@@ -1488,7 +1492,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L14" s="1">
         <v>54.844999999999999</v>
@@ -1496,7 +1500,7 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="P14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Q14" s="1">
         <v>50.741</v>
@@ -1504,7 +1508,7 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="U14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="V14" s="1">
         <v>48.582999999999998</v>
@@ -1512,9 +1516,9 @@
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
     </row>
-    <row r="15" spans="1:24" ht="14.25" customHeight="1">
+    <row r="15" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B15" s="4">
         <f>(B13/B14)*100</f>
@@ -1523,7 +1527,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G15" s="4">
         <f>(G13/G14)*100</f>
@@ -1532,7 +1536,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="K15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L15" s="4">
         <f>(L13/L14)*100</f>
@@ -1541,7 +1545,7 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="P15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="4">
         <f>(Q13/Q14)*100</f>
@@ -1550,7 +1554,7 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="U15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V15" s="4">
         <f>(V13/V14)*100</f>
@@ -1559,102 +1563,102 @@
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
     </row>
-    <row r="16" spans="1:24" ht="14.25" customHeight="1"/>
-    <row r="17" spans="1:24" ht="14.25" customHeight="1">
+    <row r="16" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="17" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="F17" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="8"/>
       <c r="K17" s="5" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="P17" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
       <c r="U17" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
       <c r="X17" s="5"/>
     </row>
-    <row r="18" spans="1:24" ht="14.25" customHeight="1">
+    <row r="18" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="14.25" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -1726,7 +1730,7 @@
         <v>5.8731135835898707</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="14.25" customHeight="1">
+    <row r="20" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -1798,7 +1802,7 @@
         <v>0.41314215450796227</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="14.25" customHeight="1">
+    <row r="21" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -1870,7 +1874,7 @@
         <v>3.9795942986156949E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="14.25" customHeight="1">
+    <row r="22" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -1942,7 +1946,7 @@
         <v>4.1653893279568902E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="14.25" customHeight="1">
+    <row r="23" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>5</v>
       </c>
@@ -2014,7 +2018,7 @@
         <v>6.4821787082921384E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="14.25" customHeight="1">
+    <row r="24" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>6</v>
       </c>
@@ -2086,7 +2090,7 @@
         <v>3.6334735242428298E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="14.25" customHeight="1">
+    <row r="25" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>7</v>
       </c>
@@ -2158,7 +2162,7 @@
         <v>1.7885743572880121E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="14.25" customHeight="1">
+    <row r="26" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>8</v>
       </c>
@@ -2230,9 +2234,9 @@
         <v>3.7300976386077812E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="14.25" customHeight="1">
+    <row r="27" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B27" s="2">
         <f>SQRT(SUM(D20:D26)/D19)</f>
@@ -2241,7 +2245,7 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2">
         <f>SQRT(SUM(I20:I26)/I19)</f>
@@ -2250,7 +2254,7 @@
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2">
         <f>SQRT(SUM(N20:N26)/N19)</f>
@@ -2259,7 +2263,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="P27" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="2">
         <f>SQRT(SUM(S20:S26)/S19)</f>
@@ -2268,7 +2272,7 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="U27" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2">
         <f>SQRT(SUM(X20:X26)/X19)</f>
@@ -2277,9 +2281,9 @@
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
     </row>
-    <row r="28" spans="1:24" ht="14.25" customHeight="1">
+    <row r="28" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B28" s="4">
         <f>B27*100</f>
@@ -2288,7 +2292,7 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="F28" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G28" s="4">
         <f>G27*100</f>
@@ -2297,7 +2301,7 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="K28" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L28" s="4">
         <f>L27*100</f>
@@ -2306,7 +2310,7 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="P28" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q28" s="4">
         <f>Q27*100</f>
@@ -2315,7 +2319,7 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="U28" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V28" s="4">
         <f>V27*100</f>
@@ -2324,9 +2328,9 @@
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
     </row>
-    <row r="29" spans="1:24" ht="14.25" customHeight="1">
+    <row r="29" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B29" s="1">
         <v>10.459</v>
@@ -2334,7 +2338,7 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G29" s="1">
         <v>4.3620999999999999</v>
@@ -2342,7 +2346,7 @@
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L29" s="1">
         <v>3.5708000000000002</v>
@@ -2350,7 +2354,7 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
       <c r="P29" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="Q29" s="1">
         <v>3.2911999999999999</v>
@@ -2358,7 +2362,7 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="U29" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="V29" s="1">
         <v>2.6467999999999998</v>
@@ -2366,9 +2370,9 @@
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
     </row>
-    <row r="30" spans="1:24" ht="14.25" customHeight="1">
+    <row r="30" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1">
         <v>70.2</v>
@@ -2376,7 +2380,7 @@
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G30" s="1">
         <v>62.005000000000003</v>
@@ -2384,7 +2388,7 @@
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="K30" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L30" s="1">
         <v>54.774999999999999</v>
@@ -2392,7 +2396,7 @@
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="P30" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Q30" s="1">
         <v>51.695</v>
@@ -2400,7 +2404,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="U30" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="V30" s="1">
         <v>50.021999999999998</v>
@@ -2408,9 +2412,9 @@
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
     </row>
-    <row r="31" spans="1:24" ht="14.25" customHeight="1">
+    <row r="31" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B31" s="4">
         <f>(B29/B30)*100</f>
@@ -2419,7 +2423,7 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="F31" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G31" s="4">
         <f>(G29/G30)*100</f>
@@ -2428,7 +2432,7 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="K31" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L31" s="4">
         <f>(L29/L30)*100</f>
@@ -2437,7 +2441,7 @@
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="P31" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q31" s="4">
         <f>(Q29/Q30)*100</f>
@@ -2446,7 +2450,7 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="U31" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V31" s="4">
         <f>(V29/V30)*100</f>
@@ -2455,102 +2459,102 @@
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
     </row>
-    <row r="32" spans="1:24" ht="14.25" customHeight="1"/>
-    <row r="33" spans="1:24">
+    <row r="32" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A33" s="5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="F33" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="8"/>
       <c r="K33" s="5" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="P33" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
       <c r="U33" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V33" s="5"/>
       <c r="W33" s="5"/>
       <c r="X33" s="5"/>
     </row>
-    <row r="34" spans="1:24" ht="14.25" customHeight="1">
+    <row r="34" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" ht="14.25" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>1</v>
       </c>
@@ -2622,7 +2626,7 @@
         <v>9.4051944736696989</v>
       </c>
     </row>
-    <row r="36" spans="1:24" ht="14.25" customHeight="1">
+    <row r="36" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>2</v>
       </c>
@@ -2694,7 +2698,7 @@
         <v>2.1315179780164519</v>
       </c>
     </row>
-    <row r="37" spans="1:24" ht="14.25" customHeight="1">
+    <row r="37" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>3</v>
       </c>
@@ -2766,7 +2770,7 @@
         <v>1.8591661348252485E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:24" ht="14.25" customHeight="1">
+    <row r="38" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -2838,7 +2842,7 @@
         <v>8.0038510885255501E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:24" ht="14.25" customHeight="1">
+    <row r="39" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -2910,7 +2914,7 @@
         <v>8.4678274546114863E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:24" ht="14.25" customHeight="1">
+    <row r="40" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>6</v>
       </c>
@@ -2982,7 +2986,7 @@
         <v>9.0943360912784255E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:24" ht="14.25" customHeight="1">
+    <row r="41" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>7</v>
       </c>
@@ -3054,7 +3058,7 @@
         <v>2.1837906389031796E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:24" ht="14.25" customHeight="1">
+    <row r="42" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>8</v>
       </c>
@@ -3126,9 +3130,9 @@
         <v>3.2834310439012718E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:24" ht="14.25" customHeight="1">
+    <row r="43" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B43" s="2">
         <f>SQRT(SUM(D36:D42)/D35)</f>
@@ -3137,7 +3141,7 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2">
         <f>SQRT(SUM(I36:I42)/I35)</f>
@@ -3146,7 +3150,7 @@
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="K43" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2">
         <f>SQRT(SUM(N36:N42)/N35)</f>
@@ -3155,7 +3159,7 @@
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="P43" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="2">
         <f>SQRT(SUM(S36:S42)/S35)</f>
@@ -3164,7 +3168,7 @@
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="U43" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2">
         <f>SQRT(SUM(X36:X42)/X35)</f>
@@ -3173,9 +3177,9 @@
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
     </row>
-    <row r="44" spans="1:24" ht="14.25" customHeight="1">
+    <row r="44" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B44" s="4">
         <f>B43*100</f>
@@ -3184,7 +3188,7 @@
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="F44" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G44" s="4">
         <f>G43*100</f>
@@ -3193,7 +3197,7 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="K44" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L44" s="4">
         <f>L43*100</f>
@@ -3202,7 +3206,7 @@
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="P44" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q44" s="4">
         <f>Q43*100</f>
@@ -3211,7 +3215,7 @@
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
       <c r="U44" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V44" s="4">
         <f>V43*100</f>
@@ -3220,9 +3224,9 @@
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
     </row>
-    <row r="45" spans="1:24" ht="14.25" customHeight="1">
+    <row r="45" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B45" s="1">
         <v>5.0016999999999996</v>
@@ -3230,7 +3234,7 @@
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G45" s="1">
         <v>2.0047999999999999</v>
@@ -3238,7 +3242,7 @@
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L45" s="1">
         <v>1.7690999999999999</v>
@@ -3246,7 +3250,7 @@
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="P45" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="Q45" s="1">
         <v>1.7525999999999999</v>
@@ -3254,7 +3258,7 @@
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
       <c r="U45" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="V45" s="1">
         <v>1.4386000000000001</v>
@@ -3262,9 +3266,9 @@
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
     </row>
-    <row r="46" spans="1:24" ht="14.25" customHeight="1">
+    <row r="46" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B46" s="1">
         <v>55.954000000000001</v>
@@ -3272,7 +3276,7 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="F46" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G46" s="1">
         <v>51.558999999999997</v>
@@ -3280,7 +3284,7 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L46" s="1">
         <v>47.563000000000002</v>
@@ -3288,7 +3292,7 @@
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="P46" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Q46" s="1">
         <v>45.780999999999999</v>
@@ -3296,7 +3300,7 @@
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
       <c r="U46" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="V46" s="1">
         <v>44.793999999999997</v>
@@ -3304,9 +3308,9 @@
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
     </row>
-    <row r="47" spans="1:24" ht="14.25" customHeight="1">
+    <row r="47" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B47" s="4">
         <f>(B45/B46)*100</f>
@@ -3315,7 +3319,7 @@
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G47" s="4">
         <f>(G45/G46)*100</f>
@@ -3324,7 +3328,7 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="K47" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L47" s="4">
         <f>(L45/L46)*100</f>
@@ -3333,7 +3337,7 @@
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="P47" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q47" s="4">
         <f>(Q45/Q46)*100</f>
@@ -3342,7 +3346,7 @@
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
       <c r="U47" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V47" s="4">
         <f>(V45/V46)*100</f>
@@ -3351,102 +3355,102 @@
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
     </row>
-    <row r="48" spans="1:24" ht="14.25" customHeight="1"/>
-    <row r="49" spans="1:24" ht="14.25" customHeight="1">
+    <row r="48" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="49" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="5" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="F49" s="6" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
       <c r="I49" s="8"/>
       <c r="K49" s="5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
       <c r="P49" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
       <c r="S49" s="5"/>
       <c r="U49" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="V49" s="5"/>
       <c r="W49" s="5"/>
       <c r="X49" s="5"/>
     </row>
-    <row r="50" spans="1:24" ht="14.25" customHeight="1">
+    <row r="50" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" ht="14.25" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <v>1</v>
       </c>
@@ -3518,7 +3522,7 @@
         <v>1.1659357610841672</v>
       </c>
     </row>
-    <row r="52" spans="1:24" ht="14.25" customHeight="1">
+    <row r="52" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <v>2</v>
       </c>
@@ -3590,7 +3594,7 @@
         <v>3.662865738566754E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:24" ht="14.25" customHeight="1">
+    <row r="53" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
         <v>3</v>
       </c>
@@ -3662,7 +3666,7 @@
         <v>6.2874334318637208E-4</v>
       </c>
     </row>
-    <row r="54" spans="1:24" ht="14.25" customHeight="1">
+    <row r="54" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
         <v>4</v>
       </c>
@@ -3734,7 +3738,7 @@
         <v>1.2415042197012197E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:24" ht="14.25" customHeight="1">
+    <row r="55" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <v>5</v>
       </c>
@@ -3806,7 +3810,7 @@
         <v>2.8805478906452866E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:24" ht="14.25" customHeight="1">
+    <row r="56" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -3878,7 +3882,7 @@
         <v>1.8478980194739941E-5</v>
       </c>
     </row>
-    <row r="57" spans="1:24" ht="14.25" customHeight="1">
+    <row r="57" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <v>7</v>
       </c>
@@ -3950,7 +3954,7 @@
         <v>9.8322066991475313E-5</v>
       </c>
     </row>
-    <row r="58" spans="1:24" ht="14.25" customHeight="1">
+    <row r="58" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <v>8</v>
       </c>
@@ -4022,9 +4026,9 @@
         <v>8.837629689707827E-7</v>
       </c>
     </row>
-    <row r="59" spans="1:24" ht="14.25" customHeight="1">
+    <row r="59" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B59" s="2">
         <f>SQRT(SUM(D52:D58)/D51)</f>
@@ -4033,7 +4037,7 @@
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G59" s="2">
         <f>SQRT(SUM(I52:I58)/I51)</f>
@@ -4042,7 +4046,7 @@
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="K59" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2">
         <f>SQRT(SUM(N52:N58)/N51)</f>
@@ -4051,7 +4055,7 @@
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
       <c r="P59" s="3" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="4">
         <f>SQRT(SUM(S52:S58)/S51)</f>
@@ -4060,7 +4064,7 @@
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
       <c r="U59" s="3" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V59" s="4">
         <f>SQRT(SUM(X52:X58)/X51)</f>
@@ -4069,9 +4073,9 @@
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
     </row>
-    <row r="60" spans="1:24" ht="14.25" customHeight="1">
+    <row r="60" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B60" s="4">
         <f>B59*100</f>
@@ -4080,7 +4084,7 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="F60" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G60" s="4">
         <f>G59*100</f>
@@ -4089,7 +4093,7 @@
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
       <c r="K60" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L60" s="4">
         <f>L59*100</f>
@@ -4098,7 +4102,7 @@
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
       <c r="P60" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q60" s="4">
         <f>Q59*100</f>
@@ -4107,7 +4111,7 @@
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
       <c r="U60" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V60" s="4">
         <f>V59*100</f>
@@ -4116,9 +4120,9 @@
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
     </row>
-    <row r="61" spans="1:24" ht="14.25" customHeight="1">
+    <row r="61" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B61" s="1">
         <v>1.8221000000000001</v>
@@ -4126,7 +4130,7 @@
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="F61" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G61" s="1">
         <v>0.70899999999999996</v>
@@ -4134,7 +4138,7 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="K61" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L61" s="1">
         <v>0.66100000000000003</v>
@@ -4142,7 +4146,7 @@
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
       <c r="P61" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="Q61" s="1">
         <v>0.69099999999999995</v>
@@ -4150,7 +4154,7 @@
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
       <c r="U61" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="V61" s="1">
         <v>0.57699999999999996</v>
@@ -4158,9 +4162,9 @@
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
     </row>
-    <row r="62" spans="1:24" ht="14.25" customHeight="1">
+    <row r="62" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B62" s="1">
         <v>39.250999999999998</v>
@@ -4168,7 +4172,7 @@
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="F62" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G62" s="1">
         <v>37.347999999999999</v>
@@ -4176,7 +4180,7 @@
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
       <c r="K62" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L62" s="1">
         <v>35.597999999999999</v>
@@ -4184,7 +4188,7 @@
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
       <c r="P62" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Q62" s="1">
         <v>34.808999999999997</v>
@@ -4192,7 +4196,7 @@
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
       <c r="U62" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="V62" s="1">
         <v>34.372</v>
@@ -4200,9 +4204,9 @@
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
     </row>
-    <row r="63" spans="1:24" ht="14.25" customHeight="1">
+    <row r="63" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B63" s="4">
         <f>(B61/B62)*100</f>
@@ -4211,7 +4215,7 @@
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="F63" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G63" s="4">
         <f>(G61/G62)*100</f>
@@ -4220,7 +4224,7 @@
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
       <c r="K63" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L63" s="4">
         <f>(L61/L62)*100</f>
@@ -4229,7 +4233,7 @@
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="P63" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q63" s="4">
         <f>(Q61/Q62)*100</f>
@@ -4238,7 +4242,7 @@
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
       <c r="U63" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V63" s="4">
         <f>(V61/V62)*100</f>
@@ -4247,105 +4251,105 @@
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
     </row>
-    <row r="64" spans="1:24" ht="14.25" customHeight="1">
+    <row r="64" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="U64" s="3"/>
       <c r="V64" s="4"/>
     </row>
-    <row r="65" spans="1:24" ht="14.25" customHeight="1">
+    <row r="65" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
       <c r="F65" s="6" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
       <c r="I65" s="8"/>
       <c r="K65" s="5" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="L65" s="5"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
       <c r="P65" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Q65" s="5"/>
       <c r="R65" s="5"/>
       <c r="S65" s="5"/>
       <c r="U65" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="V65" s="5"/>
       <c r="W65" s="5"/>
       <c r="X65" s="5"/>
     </row>
-    <row r="66" spans="1:24" ht="14.25" customHeight="1">
+    <row r="66" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:24" ht="14.25" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <v>1</v>
       </c>
@@ -4417,7 +4421,7 @@
         <v>1.3055640715077728</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <v>2</v>
       </c>
@@ -4489,7 +4493,7 @@
         <v>5.5728711259125159E-4</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <v>3</v>
       </c>
@@ -4561,7 +4565,7 @@
         <v>8.690534740402586E-4</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <v>4</v>
       </c>
@@ -4633,7 +4637,7 @@
         <v>1.8512369071593536E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <v>5</v>
       </c>
@@ -4705,7 +4709,7 @@
         <v>3.698486178054736E-4</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <v>6</v>
       </c>
@@ -4777,7 +4781,7 @@
         <v>2.3357373206731961E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <v>7</v>
       </c>
@@ -4849,7 +4853,7 @@
         <v>1.086400858183627E-4</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>8</v>
       </c>
@@ -4921,9 +4925,9 @@
         <v>2.5909498086297447E-6</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A75" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B75" s="2">
         <f>SQRT(SUM(D68:D74)/D67)</f>
@@ -4932,7 +4936,7 @@
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G75" s="2">
         <f>SQRT(SUM(I68:I74)/I67)</f>
@@ -4941,7 +4945,7 @@
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="K75" s="3" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L75" s="4">
         <f>SQRT(SUM(N68:N74)/N67)</f>
@@ -4950,7 +4954,7 @@
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
       <c r="P75" s="3" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q75" s="4">
         <f>SQRT(SUM(S68:S74)/S67)</f>
@@ -4959,7 +4963,7 @@
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
       <c r="U75" s="3" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V75" s="4">
         <f>SQRT(SUM(X68:X74)/X67)</f>
@@ -4968,9 +4972,9 @@
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A76" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B76" s="4">
         <f>B75*100</f>
@@ -4979,7 +4983,7 @@
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="F76" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G76" s="4">
         <f>G75*100</f>
@@ -4988,7 +4992,7 @@
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="K76" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L76" s="4">
         <f>L75*100</f>
@@ -4997,7 +5001,7 @@
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
       <c r="P76" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q76" s="4">
         <f>Q75*100</f>
@@ -5006,7 +5010,7 @@
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
       <c r="U76" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V76" s="4">
         <f>V75*100</f>
@@ -5015,9 +5019,9 @@
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A77" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B77" s="1">
         <v>0.89615999999999996</v>
@@ -5025,7 +5029,7 @@
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G77" s="1">
         <v>0.34458</v>
@@ -5033,7 +5037,7 @@
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="K77" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L77" s="1">
         <v>0.32983000000000001</v>
@@ -5041,7 +5045,7 @@
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
       <c r="P77" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="Q77" s="1">
         <v>0.35321999999999998</v>
@@ -5049,7 +5053,7 @@
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
       <c r="U77" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="V77" s="1">
         <v>0.29676000000000002</v>
@@ -5057,9 +5061,9 @@
       <c r="W77" s="1"/>
       <c r="X77" s="1"/>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A78" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B78" s="1">
         <v>30.34</v>
@@ -5067,7 +5071,7 @@
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="F78" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G78" s="1">
         <v>29.247</v>
@@ -5075,7 +5079,7 @@
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="K78" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L78" s="1">
         <v>28.254000000000001</v>
@@ -5083,7 +5087,7 @@
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="P78" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Q78" s="1">
         <v>27.812000000000001</v>
@@ -5091,7 +5095,7 @@
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
       <c r="U78" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="V78" s="1">
         <v>27.573</v>
@@ -5099,9 +5103,9 @@
       <c r="W78" s="1"/>
       <c r="X78" s="1"/>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A79" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B79" s="4">
         <f>(B77/B78)*100</f>
@@ -5110,7 +5114,7 @@
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="F79" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G79" s="4">
         <f>(G77/G78)*100</f>
@@ -5119,7 +5123,7 @@
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="K79" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L79" s="4">
         <f>(L77/L78)*100</f>
@@ -5128,7 +5132,7 @@
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
       <c r="P79" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q79" s="4">
         <f>(Q77/Q78)*100</f>
@@ -5137,7 +5141,7 @@
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
       <c r="U79" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V79" s="4">
         <f>(V77/V78)*100</f>
@@ -5146,16 +5150,25 @@
       <c r="W79" s="1"/>
       <c r="X79" s="1"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K49:N49"/>
+    <mergeCell ref="K65:N65"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="P65:S65"/>
     <mergeCell ref="U65:X65"/>
     <mergeCell ref="F1:I1"/>
@@ -5172,15 +5185,6 @@
     <mergeCell ref="U17:X17"/>
     <mergeCell ref="U33:X33"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K49:N49"/>
-    <mergeCell ref="K65:N65"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A65:D65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5189,129 +5193,129 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D65CBD-5C6E-4DA7-A084-10E71B11DDCD}">
   <dimension ref="A1:X15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="K1" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
       <c r="P1" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
       <c r="S1" s="5"/>
       <c r="U1" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="V1" s="5"/>
       <c r="W1" s="5"/>
       <c r="X1" s="5"/>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -5383,7 +5387,7 @@
         <v>15.604372175534285</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -5455,7 +5459,7 @@
         <v>6.8465061089189469E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -5527,7 +5531,7 @@
         <v>3.6744640270521677E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -5599,7 +5603,7 @@
         <v>1.4326166689293917E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -5671,7 +5675,7 @@
         <v>3.2771928600478215E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -5743,7 +5747,7 @@
         <v>1.3067701334182249E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -5815,7 +5819,7 @@
         <v>2.280473342820206E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -5887,9 +5891,9 @@
         <v>5.6373110687600256E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B11" s="2">
         <f>SQRT(SUM(D4:D10)/D3)</f>
@@ -5898,7 +5902,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <f>SQRT(SUM(I4:I10)/I3)</f>
@@ -5907,7 +5911,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2">
         <f>SQRT(SUM(N4:N10)/N3)</f>
@@ -5916,7 +5920,7 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="P11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="2">
         <f>SQRT(SUM(S4:S10)/S3)</f>
@@ -5925,7 +5929,7 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="U11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2">
         <f>SQRT(SUM(X4:X10)/X3)</f>
@@ -5934,9 +5938,9 @@
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B12" s="4">
         <f>B11*100</f>
@@ -5945,7 +5949,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12" s="4">
         <f>G11*100</f>
@@ -5954,7 +5958,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="K12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L12" s="4">
         <f>L11*100</f>
@@ -5963,7 +5967,7 @@
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="P12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="4">
         <f>Q11*100</f>
@@ -5972,7 +5976,7 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="U12" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V12" s="4">
         <f>V11*100</f>
@@ -5981,9 +5985,9 @@
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1">
         <v>14.321999999999999</v>
@@ -5991,7 +5995,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
         <v>14.577999999999999</v>
@@ -5999,7 +6003,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="L13" s="1">
         <v>11.843</v>
@@ -6007,7 +6011,7 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
       <c r="P13" s="1" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="Q13" s="1">
         <v>9.5259999999999998</v>
@@ -6015,7 +6019,7 @@
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="U13" s="1" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="V13" s="1">
         <v>7.8639000000000001</v>
@@ -6023,9 +6027,9 @@
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1">
         <v>116.68</v>
@@ -6033,7 +6037,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
         <v>113.01</v>
@@ -6041,7 +6045,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="L14" s="1">
         <v>109.43</v>
@@ -6049,7 +6053,7 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
       <c r="P14" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="Q14" s="1">
         <v>107.89</v>
@@ -6057,7 +6061,7 @@
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="U14" s="1" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="V14" s="1">
         <v>107.12</v>
@@ -6065,9 +6069,9 @@
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3">
         <f>(B13/B14)*100</f>
@@ -6076,7 +6080,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G15" s="3">
         <f>(G13/G14)*100</f>
@@ -6085,7 +6089,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="K15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L15" s="3">
         <f>(L13/L14)*100</f>
@@ -6094,7 +6098,7 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="P15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q15" s="3">
         <f>(Q13/Q14)*100</f>
@@ -6103,7 +6107,7 @@
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="U15" s="3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="V15" s="3">
         <f>(V13/V14)*100</f>
@@ -6125,569 +6129,569 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{337DBDE6-D9B4-40DA-B7D9-BC3C6570E54B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6A1F29-98A2-4DE1-B093-1F43E9363A49}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="K1" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>-25.274678000000002</v>
+        <v>-6.5587150000000003</v>
       </c>
       <c r="C3" s="2">
         <f>10^(B3/20)</f>
-        <v>5.4483638159108443E-2</v>
+        <v>0.46996363039531042</v>
       </c>
       <c r="D3" s="2">
         <f>C3^2</f>
-        <v>2.9684668270526576E-3</v>
+        <v>0.22086581389433993</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
       <c r="G3" s="2">
-        <v>8.9817060000000009</v>
+        <v>9.3331929999999996</v>
       </c>
       <c r="H3" s="2">
         <f>10^(G3/20)</f>
-        <v>2.8124531715117249</v>
+        <v>2.9285972484433604</v>
       </c>
       <c r="I3" s="2">
         <f>H3^2</f>
-        <v>7.9098928419463599</v>
+        <v>8.5766818435900216</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>19.416899999999998</v>
+        <v>13.50839</v>
       </c>
       <c r="M3" s="2">
         <f>10^(L3/20)</f>
-        <v>9.3507188678557984</v>
+        <v>4.7360851286401662</v>
       </c>
       <c r="N3" s="2">
         <f>M3^2</f>
-        <v>87.435943345674431</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>22.430502345726538</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>-118.995</v>
+        <v>-79.868189999999998</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" ref="C4:C10" si="0">10^(B4/20)</f>
-        <v>1.1226645259802338E-6</v>
+        <v>1.01529091486246E-4</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" ref="D4:D10" si="1">C4^2</f>
-        <v>1.260375637894423E-12</v>
+        <v>1.0308156418022509E-8</v>
       </c>
       <c r="F4" s="1">
         <v>2</v>
       </c>
       <c r="G4" s="2">
-        <v>-31.732075999999999</v>
+        <v>-40.701700000000002</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" ref="H4:H10" si="2">10^(G4/20)</f>
-        <v>2.5905751783015071E-2</v>
+        <v>9.2239087939041103E-3</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" ref="I4:I10" si="3">H4^2</f>
-        <v>6.7110797544318846E-4</v>
+        <v>8.5080493438261583E-5</v>
       </c>
       <c r="K4" s="1">
         <v>2</v>
       </c>
       <c r="L4" s="2">
-        <v>-31.116399999999999</v>
+        <v>3.8890289999999998</v>
       </c>
       <c r="M4" s="2">
         <f t="shared" ref="M4:M10" si="4">10^(L4/20)</f>
-        <v>2.7808656012838967E-2</v>
+        <v>1.5647733826382926</v>
       </c>
       <c r="N4" s="2">
         <f t="shared" ref="N4:N10" si="5">M4^2</f>
-        <v>7.7332134924040482E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>2.4485157390132843</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>-29.106104999999999</v>
+        <v>-105.3182</v>
       </c>
       <c r="C5" s="2">
         <f t="shared" si="0"/>
-        <v>3.5050542967105115E-2</v>
+        <v>5.4211322232599952E-6</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="1"/>
-        <v>1.2285405622888819E-3</v>
+        <v>2.9388674582067861E-11</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
       </c>
       <c r="G5" s="2">
-        <v>-14.11999</v>
+        <v>-46.705500000000001</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" si="2"/>
-        <v>0.19678885553209666</v>
+        <v>4.6208832937396161E-3</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" si="3"/>
-        <v>3.8725853661632406E-2</v>
+        <v>2.1352562414361883E-5</v>
       </c>
       <c r="K5" s="1">
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>-5.471406</v>
+        <v>-7.0390600000000001</v>
       </c>
       <c r="M5" s="2">
         <f t="shared" si="4"/>
-        <v>0.53263499879461385</v>
+        <v>0.44467938873537205</v>
       </c>
       <c r="N5" s="2">
         <f t="shared" si="5"/>
-        <v>0.28370004194093829</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>0.19773975876606414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>-116.8165</v>
+        <v>-130.61250000000001</v>
       </c>
       <c r="C6" s="2">
         <f t="shared" si="0"/>
-        <v>1.4426965724485703E-6</v>
+        <v>2.9469651497753914E-7</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="1"/>
-        <v>2.0813734001548528E-12</v>
+        <v>8.6846035939906947E-14</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="2">
-        <v>-48.047980000000003</v>
+        <v>-51.732596999999998</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" si="2"/>
-        <v>3.9591412835308631E-3</v>
+        <v>2.5904197941962305E-3</v>
       </c>
       <c r="I6" s="2">
         <f t="shared" si="3"/>
-        <v>1.5674799702958411E-5</v>
+        <v>6.7102747101636416E-6</v>
       </c>
       <c r="K6" s="1">
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>-24.66048</v>
+        <v>-5.4231590000000001</v>
       </c>
       <c r="M6" s="2">
         <f t="shared" si="4"/>
-        <v>5.8475776834308088E-2</v>
+        <v>0.53560182728194372</v>
       </c>
       <c r="N6" s="2">
         <f t="shared" si="5"/>
-        <v>3.4194164763758023E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>0.28686931738775706</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>-38.732456999999997</v>
+        <v>-162.10278</v>
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
-        <v>1.1571166692173812E-2</v>
+        <v>7.8498435283527741E-9</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="1"/>
-        <v>1.3389189861807264E-4</v>
+        <v>6.162004341962193E-17</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="2">
-        <v>-19.348206999999999</v>
+        <v>-56.047739999999997</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="2"/>
-        <v>0.10779277438543364</v>
+        <v>1.5762060857899627E-3</v>
       </c>
       <c r="I7" s="2">
         <f t="shared" si="3"/>
-        <v>1.1619282209708998E-2</v>
+        <v>2.4844256248813154E-6</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
       <c r="L7" s="2">
-        <v>-6.723776</v>
+        <v>-40.054273000000002</v>
       </c>
       <c r="M7" s="2">
         <f t="shared" si="4"/>
-        <v>0.46111707044912315</v>
+        <v>9.9377107068077154E-3</v>
       </c>
       <c r="N7" s="2">
         <f t="shared" si="5"/>
-        <v>0.21262895265958159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>9.8758094092200698E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>-114.1957</v>
+        <v>-157.16030000000001</v>
       </c>
       <c r="C8" s="2">
         <f t="shared" si="0"/>
-        <v>1.9508101206001143E-6</v>
+        <v>1.3867079328495399E-8</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="1"/>
-        <v>3.8056601266358327E-12</v>
+        <v>1.922958891027844E-16</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="2">
-        <v>-60.111530000000002</v>
+        <v>-60.011740000000003</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
-        <v>9.8724172001270314E-4</v>
+        <v>9.9864929557387733E-4</v>
       </c>
       <c r="I8" s="2">
         <f t="shared" si="3"/>
-        <v>9.7464621373364063E-7</v>
+        <v>9.9730041555020135E-7</v>
       </c>
       <c r="K8" s="1">
         <v>6</v>
       </c>
       <c r="L8" s="2">
-        <v>-33.230699999999999</v>
+        <v>-19.161850000000001</v>
       </c>
       <c r="M8" s="2">
         <f t="shared" si="4"/>
-        <v>2.1800426994224943E-2</v>
+        <v>0.11013047186355585</v>
       </c>
       <c r="N8" s="2">
         <f t="shared" si="5"/>
-        <v>4.7525861713053157E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>1.2128720832889467E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>-57.957210000000003</v>
+        <v>-160.51499999999999</v>
       </c>
       <c r="C9" s="2">
         <f t="shared" si="0"/>
-        <v>1.2651426594704268E-3</v>
+        <v>9.4243194784517414E-9</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="1"/>
-        <v>1.6005859488119042E-6</v>
+        <v>8.8817797631924903E-17</v>
       </c>
       <c r="F9" s="1">
         <v>7</v>
       </c>
       <c r="G9" s="2">
-        <v>-23.239789999999999</v>
+        <v>-63.79992</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
-        <v>6.8866894619092206E-2</v>
+        <v>6.4566017575725288E-4</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="3"/>
-        <v>4.7426491744771513E-3</v>
+        <v>4.1687706255888668E-7</v>
       </c>
       <c r="K9" s="1">
         <v>7</v>
       </c>
       <c r="L9" s="2">
-        <v>-24.285640000000001</v>
+        <v>-27.700265999999999</v>
       </c>
       <c r="M9" s="2">
         <f t="shared" si="4"/>
-        <v>6.1054545130109272E-2</v>
+        <v>4.1208489905883383E-2</v>
       </c>
       <c r="N9" s="2">
         <f t="shared" si="5"/>
-        <v>3.7276574810445498E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>1.6981396403232926E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>-126.1932</v>
+        <v>-164.17939999999999</v>
       </c>
       <c r="C10" s="2">
         <f t="shared" si="0"/>
-        <v>4.9016240701903493E-7</v>
+        <v>6.1805909267345348E-9</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="1"/>
-        <v>2.4025918525469407E-13</v>
+        <v>3.8199704203633257E-17</v>
       </c>
       <c r="F10" s="1">
         <v>8</v>
       </c>
       <c r="G10" s="2">
-        <v>-77.061824999999999</v>
+        <v>-67.514200000000002</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
-        <v>1.4025189890889075E-4</v>
+        <v>4.2100766227434142E-4</v>
       </c>
       <c r="I10" s="2">
         <f t="shared" si="3"/>
-        <v>1.9670595147549709E-8</v>
+        <v>1.7724745169370592E-7</v>
       </c>
       <c r="K10" s="1">
         <v>8</v>
       </c>
       <c r="L10" s="2">
-        <v>-33.091999999999999</v>
+        <v>-29.479590000000002</v>
       </c>
       <c r="M10" s="2">
         <f t="shared" si="4"/>
-        <v>2.2151339841371936E-2</v>
+        <v>3.3575346243771988E-2</v>
       </c>
       <c r="N10" s="2">
         <f t="shared" si="5"/>
-        <v>4.906818567679517E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>1.1273038753891738E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B11" s="2">
         <f>SQRT(SUM(D4:D10)/D3)</f>
-        <v>0.67786989575810741</v>
+        <v>2.1634471514102925E-4</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <f>SQRT(SUM(I4:I10)/I3)</f>
-        <v>8.3972421687846785E-2</v>
+        <v>3.6969169257777871E-3</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2">
         <f>SQRT(SUM(N4:N10)/N3)</f>
-        <v>7.6013942885339775E-2</v>
+        <v>0.36254116935323427</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2">
         <f>B11*100</f>
-        <v>67.786989575810736</v>
+        <v>2.1634471514102926E-2</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2">
         <f>G11*100</f>
-        <v>8.397242168784679</v>
+        <v>0.36969169257777873</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L12" s="2">
         <f>L11*100</f>
-        <v>7.6013942885339771</v>
+        <v>36.254116935323424</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1">
-        <v>4.3159999999999997E-2</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
-        <v>82.626000000000005</v>
+        <v>85.58</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13" s="1">
-        <v>890.77</v>
+        <v>39</v>
+      </c>
+      <c r="L13">
+        <v>259.51</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1">
-        <v>2.4380999999999999</v>
+        <v>1.2899</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G14" s="1">
-        <v>148.26</v>
+        <v>1296.2</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L14" s="1">
-        <v>251.94</v>
+        <v>921.46</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1">
         <f>(B13/B14)*100</f>
-        <v>1.7702309175177393</v>
+        <v>0.17055585704318163</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
         <f>(G13/G14)*100</f>
-        <v>55.730473492513156</v>
+        <v>6.6023761765159703</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L15" s="1">
         <f>(L13/L14)*100</f>
-        <v>353.56434071604349</v>
+        <v>28.162915373429122</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -6703,569 +6707,569 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6A1F29-98A2-4DE1-B093-1F43E9363A49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E9C2BA6-9E68-49A3-9F6D-9F23522C3FC6}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="K1" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>-6.5587150000000003</v>
+        <v>-5.9874099999999997</v>
       </c>
       <c r="C3" s="2">
         <f>10^(B3/20)</f>
-        <v>0.46996363039531042</v>
+        <v>0.50191421990127816</v>
       </c>
       <c r="D3" s="2">
         <f>C3^2</f>
-        <v>0.22086581389433993</v>
+        <v>0.25191788413910859</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
       <c r="G3" s="2">
-        <v>9.3331929999999996</v>
+        <v>9.7491161999999996</v>
       </c>
       <c r="H3" s="2">
         <f>10^(G3/20)</f>
-        <v>2.9285972484433604</v>
+        <v>3.072244744665162</v>
       </c>
       <c r="I3" s="2">
         <f>H3^2</f>
-        <v>8.5766818435900216</v>
+        <v>9.4386877711227068</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>13.50839</v>
+        <v>13.1944</v>
       </c>
       <c r="M3" s="2">
         <f>10^(L3/20)</f>
-        <v>4.7360851286401662</v>
+        <v>4.5679358894666935</v>
       </c>
       <c r="N3" s="2">
         <f>M3^2</f>
-        <v>22.430502345726538</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>20.866038290277871</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>-79.868189999999998</v>
+        <v>-47.923389999999998</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" ref="C4:C10" si="0">10^(B4/20)</f>
-        <v>1.01529091486246E-4</v>
+        <v>4.0163402724472308E-3</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" ref="D4:D10" si="1">C4^2</f>
-        <v>1.0308156418022509E-8</v>
+        <v>1.6130989184081495E-5</v>
       </c>
       <c r="F4" s="1">
         <v>2</v>
       </c>
       <c r="G4" s="2">
-        <v>-40.701700000000002</v>
+        <v>-25.243649999999999</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" ref="H4:H10" si="2">10^(G4/20)</f>
-        <v>9.2239087939041103E-3</v>
+        <v>5.4678614316365483E-2</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" ref="I4:I10" si="3">H4^2</f>
-        <v>8.5080493438261583E-5</v>
+        <v>2.9897508635578483E-3</v>
       </c>
       <c r="K4" s="1">
         <v>2</v>
       </c>
       <c r="L4" s="2">
-        <v>3.8890289999999998</v>
+        <v>4.1252880000000003</v>
       </c>
       <c r="M4" s="2">
         <f t="shared" ref="M4:M10" si="4">10^(L4/20)</f>
-        <v>1.5647733826382926</v>
+        <v>1.6079198623298983</v>
       </c>
       <c r="N4" s="2">
         <f t="shared" ref="N4:N10" si="5">M4^2</f>
-        <v>2.4485157390132843</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>2.5854062836749989</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>-105.3182</v>
+        <v>-59.354730000000004</v>
       </c>
       <c r="C5" s="2">
         <f t="shared" si="0"/>
-        <v>5.4211322232599952E-6</v>
+        <v>1.0771185368062472E-3</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="1"/>
-        <v>2.9388674582067861E-11</v>
+        <v>1.1601843423316308E-6</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
       </c>
       <c r="G5" s="2">
-        <v>-46.705500000000001</v>
+        <v>-40.991669999999999</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" si="2"/>
-        <v>4.6208832937396161E-3</v>
+        <v>8.9210608155914466E-3</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" si="3"/>
-        <v>2.1352562414361883E-5</v>
+        <v>7.9585326075481128E-5</v>
       </c>
       <c r="K5" s="1">
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>-7.0390600000000001</v>
+        <v>-7.5076200000000002</v>
       </c>
       <c r="M5" s="2">
         <f t="shared" si="4"/>
-        <v>0.44467938873537205</v>
+        <v>0.42132671767257612</v>
       </c>
       <c r="N5" s="2">
         <f t="shared" si="5"/>
-        <v>0.19773975876606414</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>0.17751620302474666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>-130.61250000000001</v>
+        <v>-76.521500000000003</v>
       </c>
       <c r="C6" s="2">
         <f t="shared" si="0"/>
-        <v>2.9469651497753914E-7</v>
+        <v>1.4925366353760677E-4</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="1"/>
-        <v>8.6846035939906947E-14</v>
+        <v>2.2276656079397127E-8</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="2">
-        <v>-51.732596999999998</v>
+        <v>-43.857667999999997</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" si="2"/>
-        <v>2.5904197941962305E-3</v>
+        <v>6.4138175255597308E-3</v>
       </c>
       <c r="I6" s="2">
         <f t="shared" si="3"/>
-        <v>6.7102747101636416E-6</v>
+        <v>4.1137055251177144E-5</v>
       </c>
       <c r="K6" s="1">
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>-5.4231590000000001</v>
+        <v>-3.687646</v>
       </c>
       <c r="M6" s="2">
         <f t="shared" si="4"/>
-        <v>0.53560182728194372</v>
+        <v>0.65406016562230995</v>
       </c>
       <c r="N6" s="2">
         <f t="shared" si="5"/>
-        <v>0.28686931738775706</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>0.42779470025388355</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>-162.10278</v>
+        <v>-92.178910000000002</v>
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
-        <v>7.8498435283527741E-9</v>
+        <v>2.4606763772357145E-5</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="1"/>
-        <v>6.162004341962193E-17</v>
+        <v>6.054928233485881E-10</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="2">
-        <v>-56.047739999999997</v>
+        <v>-58.687959999999997</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="2"/>
-        <v>1.5762060857899627E-3</v>
+        <v>1.1630596794038942E-3</v>
       </c>
       <c r="I7" s="2">
         <f t="shared" si="3"/>
-        <v>2.4844256248813154E-6</v>
+        <v>1.3527078178550891E-6</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
       <c r="L7" s="2">
-        <v>-40.054273000000002</v>
+        <v>-18.63626</v>
       </c>
       <c r="M7" s="2">
         <f t="shared" si="4"/>
-        <v>9.9377107068077154E-3</v>
+        <v>0.11700030664878129</v>
       </c>
       <c r="N7" s="2">
         <f t="shared" si="5"/>
-        <v>9.8758094092200698E-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>1.3689071755908855E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>-157.16030000000001</v>
+        <v>-90.704859999999996</v>
       </c>
       <c r="C8" s="2">
         <f t="shared" si="0"/>
-        <v>1.3867079328495399E-8</v>
+        <v>2.9157950879776206E-5</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="1"/>
-        <v>1.922958891027844E-16</v>
+        <v>8.50186099507442E-10</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="2">
-        <v>-60.011740000000003</v>
+        <v>-47.371000000000002</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
-        <v>9.9864929557387733E-4</v>
+        <v>4.2800614072157203E-3</v>
       </c>
       <c r="I8" s="2">
         <f t="shared" si="3"/>
-        <v>9.9730041555020135E-7</v>
+        <v>1.831892564953741E-5</v>
       </c>
       <c r="K8" s="1">
         <v>6</v>
       </c>
       <c r="L8" s="2">
-        <v>-19.161850000000001</v>
+        <v>-19.527329999999999</v>
       </c>
       <c r="M8" s="2">
         <f t="shared" si="4"/>
-        <v>0.11013047186355585</v>
+        <v>0.10559260398339658</v>
       </c>
       <c r="N8" s="2">
         <f t="shared" si="5"/>
-        <v>1.2128720832889467E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>1.114979801599442E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>-160.51499999999999</v>
+        <v>-98.370769999999993</v>
       </c>
       <c r="C9" s="2">
         <f t="shared" si="0"/>
-        <v>9.4243194784517414E-9</v>
+        <v>1.2063171440136758E-5</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="1"/>
-        <v>8.8817797631924903E-17</v>
+        <v>1.4552010519413115E-10</v>
       </c>
       <c r="F9" s="1">
         <v>7</v>
       </c>
       <c r="G9" s="2">
-        <v>-63.79992</v>
+        <v>-55.532060000000001</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
-        <v>6.4566017575725288E-4</v>
+        <v>1.672618900577613E-3</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="3"/>
-        <v>4.1687706255888668E-7</v>
+        <v>2.7976539865694629E-6</v>
       </c>
       <c r="K9" s="1">
         <v>7</v>
       </c>
       <c r="L9" s="2">
-        <v>-27.700265999999999</v>
+        <v>-41.205199999999998</v>
       </c>
       <c r="M9" s="2">
         <f t="shared" si="4"/>
-        <v>4.1208489905883383E-2</v>
+        <v>8.7044232438275235E-3</v>
       </c>
       <c r="N9" s="2">
         <f t="shared" si="5"/>
-        <v>1.6981396403232926E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>7.576698400768487E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>-164.17939999999999</v>
+        <v>-112.23600999999999</v>
       </c>
       <c r="C10" s="2">
         <f t="shared" si="0"/>
-        <v>6.1805909267345348E-9</v>
+        <v>2.4445532387858817E-6</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="1"/>
-        <v>3.8199704203633257E-17</v>
+        <v>5.9758405372585441E-12</v>
       </c>
       <c r="F10" s="1">
         <v>8</v>
       </c>
       <c r="G10" s="2">
-        <v>-67.514200000000002</v>
+        <v>-54.980759999999997</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
-        <v>4.2100766227434142E-4</v>
+        <v>1.7822228192771439E-3</v>
       </c>
       <c r="I10" s="2">
         <f t="shared" si="3"/>
-        <v>1.7724745169370592E-7</v>
+        <v>3.1763181775521712E-6</v>
       </c>
       <c r="K10" s="1">
         <v>8</v>
       </c>
       <c r="L10" s="2">
-        <v>-29.479590000000002</v>
+        <v>-27.8599</v>
       </c>
       <c r="M10" s="2">
         <f t="shared" si="4"/>
-        <v>3.3575346243771988E-2</v>
+        <v>4.0458054957634139E-2</v>
       </c>
       <c r="N10" s="2">
         <f t="shared" si="5"/>
-        <v>1.1273038753891738E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>1.6368542109549444E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B11" s="2">
         <f>SQRT(SUM(D4:D10)/D3)</f>
-        <v>2.1634471514102925E-4</v>
+        <v>8.2905332850849202E-3</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <f>SQRT(SUM(I4:I10)/I3)</f>
-        <v>3.6969169257777871E-3</v>
+        <v>1.8228059874627934E-2</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2">
         <f>SQRT(SUM(N4:N10)/N3)</f>
-        <v>0.36254116935323427</v>
+        <v>0.39266633186089883</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2">
         <f>B11*100</f>
-        <v>2.1634471514102926E-2</v>
+        <v>0.829053328508492</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2">
         <f>G11*100</f>
-        <v>0.36969169257777873</v>
+        <v>1.8228059874627933</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L12" s="2">
         <f>L11*100</f>
-        <v>36.254116935323424</v>
+        <v>39.266633186089884</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1">
-        <v>2.2000000000000001E-3</v>
+        <v>2.5152000000000001</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
-        <v>85.58</v>
+        <v>94.245999999999995</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13">
-        <v>259.51</v>
+        <v>39</v>
+      </c>
+      <c r="L13" s="1">
+        <v>244.93</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1">
-        <v>1.2899</v>
+        <v>78.765000000000001</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G14" s="1">
-        <v>1296.2</v>
+        <v>224.01</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L14" s="1">
-        <v>921.46</v>
+        <v>388.12</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1">
         <f>(B13/B14)*100</f>
-        <v>0.17055585704318163</v>
+        <v>3.1932965149495334</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
         <f>(G13/G14)*100</f>
-        <v>6.6023761765159703</v>
+        <v>42.072228918351854</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L15" s="1">
         <f>(L13/L14)*100</f>
-        <v>28.162915373429122</v>
+        <v>63.106771101721115</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -7281,569 +7285,569 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E9C2BA6-9E68-49A3-9F6D-9F23522C3FC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{337DBDE6-D9B4-40DA-B7D9-BC3C6570E54B}">
   <dimension ref="A1:N15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="F1" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="K1" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="5"/>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>-5.9874099999999997</v>
+        <v>-25.274678000000002</v>
       </c>
       <c r="C3" s="2">
         <f>10^(B3/20)</f>
-        <v>0.50191421990127816</v>
+        <v>5.4483638159108443E-2</v>
       </c>
       <c r="D3" s="2">
         <f>C3^2</f>
-        <v>0.25191788413910859</v>
+        <v>2.9684668270526576E-3</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
       <c r="G3" s="2">
-        <v>9.7491161999999996</v>
+        <v>8.9817060000000009</v>
       </c>
       <c r="H3" s="2">
         <f>10^(G3/20)</f>
-        <v>3.072244744665162</v>
+        <v>2.8124531715117249</v>
       </c>
       <c r="I3" s="2">
         <f>H3^2</f>
-        <v>9.4386877711227068</v>
+        <v>7.9098928419463599</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>13.1944</v>
+        <v>19.416899999999998</v>
       </c>
       <c r="M3" s="2">
         <f>10^(L3/20)</f>
-        <v>4.5679358894666935</v>
+        <v>9.3507188678557984</v>
       </c>
       <c r="N3" s="2">
         <f>M3^2</f>
-        <v>20.866038290277871</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>87.435943345674431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>-47.923389999999998</v>
+        <v>-118.995</v>
       </c>
       <c r="C4" s="2">
         <f t="shared" ref="C4:C10" si="0">10^(B4/20)</f>
-        <v>4.0163402724472308E-3</v>
+        <v>1.1226645259802338E-6</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" ref="D4:D10" si="1">C4^2</f>
-        <v>1.6130989184081495E-5</v>
+        <v>1.260375637894423E-12</v>
       </c>
       <c r="F4" s="1">
         <v>2</v>
       </c>
       <c r="G4" s="2">
-        <v>-25.243649999999999</v>
+        <v>-31.732075999999999</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" ref="H4:H10" si="2">10^(G4/20)</f>
-        <v>5.4678614316365483E-2</v>
+        <v>2.5905751783015071E-2</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" ref="I4:I10" si="3">H4^2</f>
-        <v>2.9897508635578483E-3</v>
+        <v>6.7110797544318846E-4</v>
       </c>
       <c r="K4" s="1">
         <v>2</v>
       </c>
       <c r="L4" s="2">
-        <v>4.1252880000000003</v>
+        <v>-31.116399999999999</v>
       </c>
       <c r="M4" s="2">
         <f t="shared" ref="M4:M10" si="4">10^(L4/20)</f>
-        <v>1.6079198623298983</v>
+        <v>2.7808656012838967E-2</v>
       </c>
       <c r="N4" s="2">
         <f t="shared" ref="N4:N10" si="5">M4^2</f>
-        <v>2.5854062836749989</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>7.7332134924040482E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>-59.354730000000004</v>
+        <v>-29.106104999999999</v>
       </c>
       <c r="C5" s="2">
         <f t="shared" si="0"/>
-        <v>1.0771185368062472E-3</v>
+        <v>3.5050542967105115E-2</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="1"/>
-        <v>1.1601843423316308E-6</v>
+        <v>1.2285405622888819E-3</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
       </c>
       <c r="G5" s="2">
-        <v>-40.991669999999999</v>
+        <v>-14.11999</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" si="2"/>
-        <v>8.9210608155914466E-3</v>
+        <v>0.19678885553209666</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" si="3"/>
-        <v>7.9585326075481128E-5</v>
+        <v>3.8725853661632406E-2</v>
       </c>
       <c r="K5" s="1">
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>-7.5076200000000002</v>
+        <v>-5.471406</v>
       </c>
       <c r="M5" s="2">
         <f t="shared" si="4"/>
-        <v>0.42132671767257612</v>
+        <v>0.53263499879461385</v>
       </c>
       <c r="N5" s="2">
         <f t="shared" si="5"/>
-        <v>0.17751620302474666</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>0.28370004194093829</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>-76.521500000000003</v>
+        <v>-116.8165</v>
       </c>
       <c r="C6" s="2">
         <f t="shared" si="0"/>
-        <v>1.4925366353760677E-4</v>
+        <v>1.4426965724485703E-6</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" si="1"/>
-        <v>2.2276656079397127E-8</v>
+        <v>2.0813734001548528E-12</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="2">
-        <v>-43.857667999999997</v>
+        <v>-48.047980000000003</v>
       </c>
       <c r="H6" s="2">
         <f t="shared" si="2"/>
-        <v>6.4138175255597308E-3</v>
+        <v>3.9591412835308631E-3</v>
       </c>
       <c r="I6" s="2">
         <f t="shared" si="3"/>
-        <v>4.1137055251177144E-5</v>
+        <v>1.5674799702958411E-5</v>
       </c>
       <c r="K6" s="1">
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>-3.687646</v>
+        <v>-24.66048</v>
       </c>
       <c r="M6" s="2">
         <f t="shared" si="4"/>
-        <v>0.65406016562230995</v>
+        <v>5.8475776834308088E-2</v>
       </c>
       <c r="N6" s="2">
         <f t="shared" si="5"/>
-        <v>0.42779470025388355</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>3.4194164763758023E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>-92.178910000000002</v>
+        <v>-38.732456999999997</v>
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
-        <v>2.4606763772357145E-5</v>
+        <v>1.1571166692173812E-2</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" si="1"/>
-        <v>6.054928233485881E-10</v>
+        <v>1.3389189861807264E-4</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="2">
-        <v>-58.687959999999997</v>
+        <v>-19.348206999999999</v>
       </c>
       <c r="H7" s="2">
         <f t="shared" si="2"/>
-        <v>1.1630596794038942E-3</v>
+        <v>0.10779277438543364</v>
       </c>
       <c r="I7" s="2">
         <f t="shared" si="3"/>
-        <v>1.3527078178550891E-6</v>
+        <v>1.1619282209708998E-2</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
       <c r="L7" s="2">
-        <v>-18.63626</v>
+        <v>-6.723776</v>
       </c>
       <c r="M7" s="2">
         <f t="shared" si="4"/>
-        <v>0.11700030664878129</v>
+        <v>0.46111707044912315</v>
       </c>
       <c r="N7" s="2">
         <f t="shared" si="5"/>
-        <v>1.3689071755908855E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>0.21262895265958159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>-90.704859999999996</v>
+        <v>-114.1957</v>
       </c>
       <c r="C8" s="2">
         <f t="shared" si="0"/>
-        <v>2.9157950879776206E-5</v>
+        <v>1.9508101206001143E-6</v>
       </c>
       <c r="D8" s="2">
         <f t="shared" si="1"/>
-        <v>8.50186099507442E-10</v>
+        <v>3.8056601266358327E-12</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="2">
-        <v>-47.371000000000002</v>
+        <v>-60.111530000000002</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="2"/>
-        <v>4.2800614072157203E-3</v>
+        <v>9.8724172001270314E-4</v>
       </c>
       <c r="I8" s="2">
         <f t="shared" si="3"/>
-        <v>1.831892564953741E-5</v>
+        <v>9.7464621373364063E-7</v>
       </c>
       <c r="K8" s="1">
         <v>6</v>
       </c>
       <c r="L8" s="2">
-        <v>-19.527329999999999</v>
+        <v>-33.230699999999999</v>
       </c>
       <c r="M8" s="2">
         <f t="shared" si="4"/>
-        <v>0.10559260398339658</v>
+        <v>2.1800426994224943E-2</v>
       </c>
       <c r="N8" s="2">
         <f t="shared" si="5"/>
-        <v>1.114979801599442E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>4.7525861713053157E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>-98.370769999999993</v>
+        <v>-57.957210000000003</v>
       </c>
       <c r="C9" s="2">
         <f t="shared" si="0"/>
-        <v>1.2063171440136758E-5</v>
+        <v>1.2651426594704268E-3</v>
       </c>
       <c r="D9" s="2">
         <f t="shared" si="1"/>
-        <v>1.4552010519413115E-10</v>
+        <v>1.6005859488119042E-6</v>
       </c>
       <c r="F9" s="1">
         <v>7</v>
       </c>
       <c r="G9" s="2">
-        <v>-55.532060000000001</v>
+        <v>-23.239789999999999</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="2"/>
-        <v>1.672618900577613E-3</v>
+        <v>6.8866894619092206E-2</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="3"/>
-        <v>2.7976539865694629E-6</v>
+        <v>4.7426491744771513E-3</v>
       </c>
       <c r="K9" s="1">
         <v>7</v>
       </c>
       <c r="L9" s="2">
-        <v>-41.205199999999998</v>
+        <v>-24.285640000000001</v>
       </c>
       <c r="M9" s="2">
         <f t="shared" si="4"/>
-        <v>8.7044232438275235E-3</v>
+        <v>6.1054545130109272E-2</v>
       </c>
       <c r="N9" s="2">
         <f t="shared" si="5"/>
-        <v>7.576698400768487E-5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>3.7276574810445498E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>-112.23600999999999</v>
+        <v>-126.1932</v>
       </c>
       <c r="C10" s="2">
         <f t="shared" si="0"/>
-        <v>2.4445532387858817E-6</v>
+        <v>4.9016240701903493E-7</v>
       </c>
       <c r="D10" s="2">
         <f t="shared" si="1"/>
-        <v>5.9758405372585441E-12</v>
+        <v>2.4025918525469407E-13</v>
       </c>
       <c r="F10" s="1">
         <v>8</v>
       </c>
       <c r="G10" s="2">
-        <v>-54.980759999999997</v>
+        <v>-77.061824999999999</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="2"/>
-        <v>1.7822228192771439E-3</v>
+        <v>1.4025189890889075E-4</v>
       </c>
       <c r="I10" s="2">
         <f t="shared" si="3"/>
-        <v>3.1763181775521712E-6</v>
+        <v>1.9670595147549709E-8</v>
       </c>
       <c r="K10" s="1">
         <v>8</v>
       </c>
       <c r="L10" s="2">
-        <v>-27.8599</v>
+        <v>-33.091999999999999</v>
       </c>
       <c r="M10" s="2">
         <f t="shared" si="4"/>
-        <v>4.0458054957634139E-2</v>
+        <v>2.2151339841371936E-2</v>
       </c>
       <c r="N10" s="2">
         <f t="shared" si="5"/>
-        <v>1.6368542109549444E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>4.906818567679517E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B11" s="2">
         <f>SQRT(SUM(D4:D10)/D3)</f>
-        <v>8.2905332850849202E-3</v>
+        <v>0.67786989575810741</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <f>SQRT(SUM(I4:I10)/I3)</f>
-        <v>1.8228059874627934E-2</v>
+        <v>8.3972421687846785E-2</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2">
         <f>SQRT(SUM(N4:N10)/N3)</f>
-        <v>0.39266633186089883</v>
+        <v>7.6013942885339775E-2</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2">
         <f>B11*100</f>
-        <v>0.829053328508492</v>
+        <v>67.786989575810736</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2">
         <f>G11*100</f>
-        <v>1.8228059874627933</v>
+        <v>8.397242168784679</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L12" s="2">
         <f>L11*100</f>
-        <v>39.266633186089884</v>
+        <v>7.6013942885339771</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1">
-        <v>2.5152000000000001</v>
+        <v>4.3159999999999997E-2</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1">
-        <v>94.245999999999995</v>
+        <v>82.626000000000005</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L13" s="1">
-        <v>244.93</v>
+        <v>890.77</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1">
-        <v>78.765000000000001</v>
+        <v>2.4380999999999999</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="G14" s="1">
-        <v>224.01</v>
+        <v>148.26</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="L14" s="1">
-        <v>388.12</v>
+        <v>251.94</v>
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1">
         <f>(B13/B14)*100</f>
-        <v>3.1932965149495334</v>
+        <v>1.7702309175177393</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
         <f>(G13/G14)*100</f>
-        <v>42.072228918351854</v>
+        <v>55.730473492513156</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L15" s="1">
         <f>(L13/L14)*100</f>
-        <v>63.106771101721115</v>
+        <v>353.56434071604349</v>
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>

--- a/EXCEL FILEOVI/ZAVRSNI EXCEL - SIM RESULTS .xlsx
+++ b/EXCEL FILEOVI/ZAVRSNI EXCEL - SIM RESULTS .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/523341E057C2D1B5/Documents/2526 - LJETNI SEMESTAR/Bachelor-Thesis/EXCEL FILEOVI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2055" documentId="8_{749E225B-507B-4645-922D-F24EE2B83FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94C9D64A-A2CF-4231-925A-18DBFBDA2286}"/>
+  <xr:revisionPtr revIDLastSave="2080" documentId="8_{749E225B-507B-4645-922D-F24EE2B83FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4DF8B01-B38E-4E7D-99DA-CA18E4678049}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{5A5A50C3-7C6B-466F-847F-D23E3D13151B}"/>
+    <workbookView xWindow="8370" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{5A5A50C3-7C6B-466F-847F-D23E3D13151B}"/>
   </bookViews>
   <sheets>
     <sheet name="SZE SIM RESULTS" sheetId="1" r:id="rId1"/>
@@ -184,8 +184,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -276,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -293,6 +294,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5160,15 +5169,6 @@
     <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K49:N49"/>
-    <mergeCell ref="K65:N65"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A65:D65"/>
     <mergeCell ref="P65:S65"/>
     <mergeCell ref="U65:X65"/>
     <mergeCell ref="F1:I1"/>
@@ -5185,6 +5185,15 @@
     <mergeCell ref="U17:X17"/>
     <mergeCell ref="U33:X33"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K49:N49"/>
+    <mergeCell ref="K65:N65"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A65:D65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5196,24 +5205,24 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.59765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.6640625" customWidth="1"/>
     <col min="16" max="16" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.59765625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.3984375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11.73046875" bestFit="1" customWidth="1"/>
@@ -5319,70 +5328,70 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="9">
         <v>4.7282000000000002</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="9">
         <f>10^(B3/20)</f>
         <v>1.7234948895886821</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="9">
         <f>C3^2</f>
         <v>2.9704346344383037</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="9">
         <v>8.2105440000000005</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="9">
         <f>10^(G3/20)</f>
         <v>2.5735179396168371</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="9">
         <f>H3^2</f>
         <v>6.6229945855296899</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="9">
         <v>10.579746999999999</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="9">
         <f>10^(L3/20)</f>
         <v>3.3805498929777942</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="9">
         <f>M3^2</f>
         <v>11.428117578912175</v>
       </c>
       <c r="P3" s="1">
         <v>1</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="11">
         <v>11.47996</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="11">
         <f>10^(Q3/20)</f>
         <v>3.7497127543496922</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="11">
         <f>R3^2</f>
         <v>14.060345740132755</v>
       </c>
       <c r="U3" s="1">
         <v>1</v>
       </c>
-      <c r="V3" s="2">
+      <c r="V3" s="9">
         <v>11.932463</v>
       </c>
-      <c r="W3" s="2">
+      <c r="W3" s="9">
         <f>10^(V3/20)</f>
         <v>3.950236977136218</v>
       </c>
-      <c r="X3" s="2">
+      <c r="X3" s="9">
         <f>W3^2</f>
         <v>15.604372175534285</v>
       </c>
@@ -5391,70 +5400,70 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="9">
         <v>-2.4359999999999999</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="9">
         <f t="shared" ref="C4:C10" si="0">10^(B4/20)</f>
         <v>0.75544004056761893</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="9">
         <f t="shared" ref="D4:D10" si="1">C4^2</f>
         <v>0.57068965489280576</v>
       </c>
       <c r="F4" s="1">
         <v>2</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="9">
         <v>-2.1788400000000001</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="9">
         <f t="shared" ref="H4:H10" si="2">10^(G4/20)</f>
         <v>0.77814046470960674</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="9">
         <f t="shared" ref="I4:I10" si="3">H4^2</f>
         <v>0.60550258281848268</v>
       </c>
       <c r="K4" s="1">
         <v>2</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="9">
         <v>-4.9427500000000002</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="9">
         <f t="shared" ref="M4:M10" si="4">10^(L4/20)</f>
         <v>0.56606004296981571</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="9">
         <f t="shared" ref="N4:N10" si="5">M4^2</f>
         <v>0.3204239722469896</v>
       </c>
       <c r="P4" s="1">
         <v>2</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="11">
         <v>-8.2892419999999998</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="11">
         <f t="shared" ref="R4:R8" si="6">10^(Q4/20)</f>
         <v>0.38506841735340325</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="11">
         <f t="shared" ref="S4:S10" si="7">R4^2</f>
         <v>0.14827768604305475</v>
       </c>
       <c r="U4" s="1">
         <v>2</v>
       </c>
-      <c r="V4" s="2">
+      <c r="V4" s="9">
         <v>-11.64531</v>
       </c>
-      <c r="W4" s="2">
+      <c r="W4" s="9">
         <f t="shared" ref="W4:W10" si="8">10^(V4/20)</f>
         <v>0.26165829069454205</v>
       </c>
-      <c r="X4" s="2">
+      <c r="X4" s="9">
         <f t="shared" ref="X4:X10" si="9">W4^2</f>
         <v>6.8465061089189469E-2</v>
       </c>
@@ -5463,70 +5472,70 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="9">
         <v>-22.338000000000001</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="9">
         <f t="shared" si="0"/>
         <v>7.6401168351701826E-2</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="9">
         <f t="shared" si="1"/>
         <v>5.8371385255050843E-3</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="9">
         <v>-14.470370000000001</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="9">
         <f t="shared" si="2"/>
         <v>0.18900857159329354</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="9">
         <f t="shared" si="3"/>
         <v>3.5724240135737169E-2</v>
       </c>
       <c r="K5" s="1">
         <v>3</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="9">
         <v>-10.854979999999999</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="9">
         <f t="shared" si="4"/>
         <v>0.28658337967398984</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="9">
         <f t="shared" si="5"/>
         <v>8.2130033505366212E-2</v>
       </c>
       <c r="P5" s="1">
         <v>3</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="11">
         <v>-12.060734999999999</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="11">
         <f t="shared" si="6"/>
         <v>0.249438364326283</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="11">
         <f t="shared" si="7"/>
         <v>6.2219497597771491E-2</v>
       </c>
       <c r="U5" s="1">
         <v>3</v>
       </c>
-      <c r="V5" s="2">
+      <c r="V5" s="9">
         <v>-14.34806</v>
       </c>
-      <c r="W5" s="2">
+      <c r="W5" s="9">
         <f t="shared" si="8"/>
         <v>0.19168891535642241</v>
       </c>
-      <c r="X5" s="2">
+      <c r="X5" s="9">
         <f t="shared" si="9"/>
         <v>3.6744640270521677E-2</v>
       </c>
@@ -5535,70 +5544,70 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="9">
         <v>-15.955</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="9">
         <f t="shared" si="0"/>
         <v>0.1593125539925771</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="9">
         <f t="shared" si="1"/>
         <v>2.5380489859637794E-2</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="9">
         <v>-19.469000000000001</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="9">
         <f t="shared" si="2"/>
         <v>0.10630409633445624</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="9">
         <f t="shared" si="3"/>
         <v>1.1300560897485353E-2</v>
       </c>
       <c r="K6" s="1">
         <v>4</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="9">
         <v>-24.02542</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="9">
         <f t="shared" si="4"/>
         <v>6.2911349317847601E-2</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="9">
         <f t="shared" si="5"/>
         <v>3.9578378729922441E-3</v>
       </c>
       <c r="P6" s="1">
         <v>4</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="11">
         <v>-18.432680000000001</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="11">
         <f t="shared" si="6"/>
         <v>0.11977495048699868</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="11">
         <f t="shared" si="7"/>
         <v>1.4346038764162987E-2</v>
       </c>
       <c r="U6" s="1">
         <v>4</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6" s="9">
         <v>-18.438700000000001</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6" s="9">
         <f t="shared" si="8"/>
         <v>0.11969196585107088</v>
       </c>
-      <c r="X6" s="2">
+      <c r="X6" s="9">
         <f t="shared" si="9"/>
         <v>1.4326166689293917E-2</v>
       </c>
@@ -5607,70 +5616,70 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="9">
         <v>-31.186</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="9">
         <f t="shared" si="0"/>
         <v>2.7586715750763942E-2</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="9">
         <f t="shared" si="1"/>
         <v>7.6102688591344735E-4</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="9">
         <v>-20.594619999999999</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="9">
         <f t="shared" si="2"/>
         <v>9.3383253326739343E-2</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="9">
         <f t="shared" si="3"/>
         <v>8.7204320018859742E-3</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="9">
         <v>-25.769276999999999</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="9">
         <f t="shared" si="4"/>
         <v>5.1467864628410208E-2</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="9">
         <f t="shared" si="5"/>
         <v>2.6489410894083585E-3</v>
       </c>
       <c r="P7" s="1">
         <v>5</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="11">
         <v>-32.445210000000003</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="11">
         <f t="shared" si="6"/>
         <v>2.3863794472581724E-2</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7" s="11">
         <f t="shared" si="7"/>
         <v>5.6948068662962211E-4</v>
       </c>
       <c r="U7" s="1">
         <v>5</v>
       </c>
-      <c r="V7" s="2">
+      <c r="V7" s="9">
         <v>-24.84498</v>
       </c>
-      <c r="W7" s="2">
+      <c r="W7" s="9">
         <f t="shared" si="8"/>
         <v>5.7246771612448344E-2</v>
       </c>
-      <c r="X7" s="2">
+      <c r="X7" s="9">
         <f t="shared" si="9"/>
         <v>3.2771928600478215E-3</v>
       </c>
@@ -5679,70 +5688,70 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="9">
         <v>-23.439900000000002</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="9">
         <f t="shared" si="0"/>
         <v>6.7298440425900177E-2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="9">
         <f t="shared" si="1"/>
         <v>4.5290800837584355E-3</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="9">
         <v>-35.854080000000003</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="9">
         <f t="shared" si="2"/>
         <v>1.611743769355151E-2</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="9">
         <f t="shared" si="3"/>
         <v>2.5977179780551501E-4</v>
       </c>
       <c r="K8" s="1">
         <v>6</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="9">
         <v>-23.938179999999999</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="9">
         <f t="shared" si="4"/>
         <v>6.3546407002131045E-2</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="9">
         <f t="shared" si="5"/>
         <v>4.0381458428804893E-3</v>
       </c>
       <c r="P8" s="1">
         <v>6</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="11">
         <v>-31.05416</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="11">
         <f t="shared" si="6"/>
         <v>2.8008638610887291E-2</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S8" s="11">
         <f t="shared" si="7"/>
         <v>7.8448383683528639E-4</v>
       </c>
       <c r="U8" s="1">
         <v>6</v>
       </c>
-      <c r="V8" s="2">
+      <c r="V8" s="9">
         <v>-38.838008000000002</v>
       </c>
-      <c r="W8" s="2">
+      <c r="W8" s="9">
         <f>10^(V8/20)</f>
         <v>1.1431404696791313E-2</v>
       </c>
-      <c r="X8" s="2">
+      <c r="X8" s="9">
         <f t="shared" si="9"/>
         <v>1.3067701334182249E-4</v>
       </c>
@@ -5751,70 +5760,70 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="9">
         <v>-36.588999999999999</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="9">
         <f t="shared" si="0"/>
         <v>1.4809827498930051E-2</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="9">
         <f t="shared" si="1"/>
         <v>2.1933099054806474E-4</v>
       </c>
       <c r="F9" s="1">
         <v>7</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="9">
         <v>-25.92764</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="9">
         <f t="shared" si="2"/>
         <v>5.0537994056481295E-2</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="9">
         <f t="shared" si="3"/>
         <v>2.5540888432529388E-3</v>
       </c>
       <c r="K9" s="1">
         <v>7</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="9">
         <v>-32.496220000000001</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="9">
         <f t="shared" si="4"/>
         <v>2.3724059250121266E-2</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="9">
         <f t="shared" si="5"/>
         <v>5.6283098730326438E-4</v>
       </c>
       <c r="P9" s="1">
         <v>7</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="11">
         <v>-28.146439999999998</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="11">
         <f>10^(Q9/20)</f>
         <v>3.9145153463563898E-2</v>
       </c>
-      <c r="S9" s="2">
+      <c r="S9" s="11">
         <f t="shared" si="7"/>
         <v>1.5323430396859685E-3</v>
       </c>
       <c r="U9" s="1">
         <v>7</v>
       </c>
-      <c r="V9" s="2">
+      <c r="V9" s="9">
         <v>-36.419750000000001</v>
       </c>
-      <c r="W9" s="2">
+      <c r="W9" s="9">
         <f>10^(V9/20)</f>
         <v>1.5101236183902978E-2</v>
       </c>
-      <c r="X9" s="2">
+      <c r="X9" s="9">
         <f t="shared" si="9"/>
         <v>2.280473342820206E-4</v>
       </c>
@@ -5823,70 +5832,70 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="9">
         <v>-28.710799999999999</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="9">
         <f t="shared" si="0"/>
         <v>3.6682590697079062E-2</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="9">
         <f t="shared" si="1"/>
         <v>1.3456124602494314E-3</v>
       </c>
       <c r="F10" s="1">
         <v>8</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="9">
         <v>-38.089199999999998</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="9">
         <f t="shared" si="2"/>
         <v>1.2460629986291331E-2</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="9">
         <f t="shared" si="3"/>
         <v>1.5526729965526268E-4</v>
       </c>
       <c r="K10" s="1">
         <v>8</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="9">
         <v>-35.921900000000001</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="9">
         <f t="shared" si="4"/>
         <v>1.5992081706261624E-2</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="9">
         <f t="shared" si="5"/>
         <v>2.557466772997477E-4</v>
       </c>
       <c r="P10" s="1">
         <v>8</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="11">
         <v>-32.048209999999997</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="11">
         <f>10^(Q10/20)</f>
         <v>2.4979831238876763E-2</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="11">
         <f t="shared" si="7"/>
         <v>6.2399196872276342E-4</v>
       </c>
       <c r="U10" s="1">
         <v>8</v>
       </c>
-      <c r="V10" s="2">
+      <c r="V10" s="9">
         <v>-32.489280000000001</v>
       </c>
-      <c r="W10" s="2">
+      <c r="W10" s="9">
         <f t="shared" si="8"/>
         <v>2.3743022277629328E-2</v>
       </c>
-      <c r="X10" s="2">
+      <c r="X10" s="9">
         <f t="shared" si="9"/>
         <v>5.6373110687600256E-4</v>
       </c>
@@ -5895,226 +5904,226 @@
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="9">
         <f>SQRT(SUM(D4:D10)/D3)</f>
         <v>0.45270353589867951</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
       <c r="F11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="9">
         <f>SQRT(SUM(I4:I10)/I3)</f>
         <v>0.3166852054852487</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="K11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="9">
         <f>SQRT(SUM(N4:N10)/N3)</f>
         <v>0.19033646694474435</v>
       </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
       <c r="P11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="11">
         <f>SQRT(SUM(S4:S10)/S3)</f>
         <v>0.1274400276729003</v>
       </c>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
       <c r="U11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="V11" s="2">
+      <c r="V11" s="9">
         <f>SQRT(SUM(X4:X10)/X3)</f>
         <v>8.904797288767928E-2</v>
       </c>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="10">
         <f>B11*100</f>
         <v>45.270353589867952</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
       <c r="F12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="10">
         <f>G11*100</f>
         <v>31.668520548524871</v>
       </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="K12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="10">
         <f>L11*100</f>
         <v>19.033646694474434</v>
       </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="Q12" s="12">
         <f>Q11*100</f>
         <v>12.744002767290031</v>
       </c>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V12" s="4">
+      <c r="V12" s="10">
         <f>V11*100</f>
         <v>8.9047972887679272</v>
       </c>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="9">
         <v>14.321999999999999</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
       <c r="F13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="9">
         <v>14.577999999999999</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
       <c r="K13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="9">
         <v>11.843</v>
       </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
       <c r="P13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="Q13" s="1">
+      <c r="Q13" s="11">
         <v>9.5259999999999998</v>
       </c>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
       <c r="U13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="V13" s="1">
+      <c r="V13" s="9">
         <v>7.8639000000000001</v>
       </c>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="9">
         <v>116.68</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
       <c r="F14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="9">
         <v>113.01</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
       <c r="K14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="9">
         <v>109.43</v>
       </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
       <c r="P14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="Q14" s="11">
         <v>107.89</v>
       </c>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
       <c r="U14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="1">
+      <c r="V14" s="9">
         <v>107.12</v>
       </c>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="10">
         <f>(B13/B14)*100</f>
         <v>12.274597188892697</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
       <c r="F15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="10">
         <f>(G13/G14)*100</f>
         <v>12.899743385541102</v>
       </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
       <c r="K15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="10">
         <f>(L13/L14)*100</f>
         <v>10.822443571232752</v>
       </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
       <c r="P15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="12">
         <f>(Q13/Q14)*100</f>
         <v>8.829363240337381</v>
       </c>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
       <c r="U15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="V15" s="3">
+      <c r="V15" s="10">
         <f>(V13/V14)*100</f>
         <v>7.3412061239731141</v>
       </c>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6787,42 +6796,42 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="9">
         <v>-5.9874099999999997</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="9">
         <f>10^(B3/20)</f>
         <v>0.50191421990127816</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="9">
         <f>C3^2</f>
         <v>0.25191788413910859</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="9">
         <v>9.7491161999999996</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="9">
         <f>10^(G3/20)</f>
         <v>3.072244744665162</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="9">
         <f>H3^2</f>
         <v>9.4386877711227068</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="9">
         <v>13.1944</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="9">
         <f>10^(L3/20)</f>
         <v>4.5679358894666935</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="9">
         <f>M3^2</f>
         <v>20.866038290277871</v>
       </c>
@@ -6831,42 +6840,42 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="9">
         <v>-47.923389999999998</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="9">
         <f t="shared" ref="C4:C10" si="0">10^(B4/20)</f>
         <v>4.0163402724472308E-3</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="9">
         <f t="shared" ref="D4:D10" si="1">C4^2</f>
         <v>1.6130989184081495E-5</v>
       </c>
       <c r="F4" s="1">
         <v>2</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="9">
         <v>-25.243649999999999</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="9">
         <f t="shared" ref="H4:H10" si="2">10^(G4/20)</f>
         <v>5.4678614316365483E-2</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="9">
         <f t="shared" ref="I4:I10" si="3">H4^2</f>
         <v>2.9897508635578483E-3</v>
       </c>
       <c r="K4" s="1">
         <v>2</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="9">
         <v>4.1252880000000003</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="9">
         <f t="shared" ref="M4:M10" si="4">10^(L4/20)</f>
         <v>1.6079198623298983</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="9">
         <f t="shared" ref="N4:N10" si="5">M4^2</f>
         <v>2.5854062836749989</v>
       </c>
@@ -6875,42 +6884,42 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="9">
         <v>-59.354730000000004</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="9">
         <f t="shared" si="0"/>
         <v>1.0771185368062472E-3</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="9">
         <f t="shared" si="1"/>
         <v>1.1601843423316308E-6</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="9">
         <v>-40.991669999999999</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="9">
         <f t="shared" si="2"/>
         <v>8.9210608155914466E-3</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="9">
         <f t="shared" si="3"/>
         <v>7.9585326075481128E-5</v>
       </c>
       <c r="K5" s="1">
         <v>3</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="9">
         <v>-7.5076200000000002</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="9">
         <f t="shared" si="4"/>
         <v>0.42132671767257612</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="9">
         <f t="shared" si="5"/>
         <v>0.17751620302474666</v>
       </c>
@@ -6919,42 +6928,42 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="9">
         <v>-76.521500000000003</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="9">
         <f t="shared" si="0"/>
         <v>1.4925366353760677E-4</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="9">
         <f t="shared" si="1"/>
         <v>2.2276656079397127E-8</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="9">
         <v>-43.857667999999997</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="9">
         <f t="shared" si="2"/>
         <v>6.4138175255597308E-3</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="9">
         <f t="shared" si="3"/>
         <v>4.1137055251177144E-5</v>
       </c>
       <c r="K6" s="1">
         <v>4</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="9">
         <v>-3.687646</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="9">
         <f t="shared" si="4"/>
         <v>0.65406016562230995</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="9">
         <f t="shared" si="5"/>
         <v>0.42779470025388355</v>
       </c>
@@ -6963,42 +6972,42 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="9">
         <v>-92.178910000000002</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="9">
         <f t="shared" si="0"/>
         <v>2.4606763772357145E-5</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="9">
         <f t="shared" si="1"/>
         <v>6.054928233485881E-10</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="9">
         <v>-58.687959999999997</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="9">
         <f t="shared" si="2"/>
         <v>1.1630596794038942E-3</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="9">
         <f t="shared" si="3"/>
         <v>1.3527078178550891E-6</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="9">
         <v>-18.63626</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="9">
         <f t="shared" si="4"/>
         <v>0.11700030664878129</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="9">
         <f t="shared" si="5"/>
         <v>1.3689071755908855E-2</v>
       </c>
@@ -7007,42 +7016,42 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="9">
         <v>-90.704859999999996</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="9">
         <f t="shared" si="0"/>
         <v>2.9157950879776206E-5</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="9">
         <f t="shared" si="1"/>
         <v>8.50186099507442E-10</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="9">
         <v>-47.371000000000002</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="9">
         <f t="shared" si="2"/>
         <v>4.2800614072157203E-3</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="9">
         <f t="shared" si="3"/>
         <v>1.831892564953741E-5</v>
       </c>
       <c r="K8" s="1">
         <v>6</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="9">
         <v>-19.527329999999999</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="9">
         <f t="shared" si="4"/>
         <v>0.10559260398339658</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="9">
         <f t="shared" si="5"/>
         <v>1.114979801599442E-2</v>
       </c>
@@ -7051,42 +7060,42 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="9">
         <v>-98.370769999999993</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="9">
         <f t="shared" si="0"/>
         <v>1.2063171440136758E-5</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="9">
         <f t="shared" si="1"/>
         <v>1.4552010519413115E-10</v>
       </c>
       <c r="F9" s="1">
         <v>7</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="9">
         <v>-55.532060000000001</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="9">
         <f t="shared" si="2"/>
         <v>1.672618900577613E-3</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="9">
         <f t="shared" si="3"/>
         <v>2.7976539865694629E-6</v>
       </c>
       <c r="K9" s="1">
         <v>7</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="9">
         <v>-41.205199999999998</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="9">
         <f t="shared" si="4"/>
         <v>8.7044232438275235E-3</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="9">
         <f t="shared" si="5"/>
         <v>7.576698400768487E-5</v>
       </c>
@@ -7095,42 +7104,42 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="9">
         <v>-112.23600999999999</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="9">
         <f t="shared" si="0"/>
         <v>2.4445532387858817E-6</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="9">
         <f t="shared" si="1"/>
         <v>5.9758405372585441E-12</v>
       </c>
       <c r="F10" s="1">
         <v>8</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="9">
         <v>-54.980759999999997</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="9">
         <f t="shared" si="2"/>
         <v>1.7822228192771439E-3</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="9">
         <f t="shared" si="3"/>
         <v>3.1763181775521712E-6</v>
       </c>
       <c r="K10" s="1">
         <v>8</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="9">
         <v>-27.8599</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="9">
         <f t="shared" si="4"/>
         <v>4.0458054957634139E-2</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="9">
         <f t="shared" si="5"/>
         <v>1.6368542109549444E-3</v>
       </c>
@@ -7139,140 +7148,140 @@
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="9">
         <f>SQRT(SUM(D4:D10)/D3)</f>
         <v>8.2905332850849202E-3</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
       <c r="F11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="9">
         <f>SQRT(SUM(I4:I10)/I3)</f>
         <v>1.8228059874627934E-2</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="K11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="9">
         <f>SQRT(SUM(N4:N10)/N3)</f>
         <v>0.39266633186089883</v>
       </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="9">
         <f>B11*100</f>
         <v>0.829053328508492</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
       <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="9">
         <f>G11*100</f>
         <v>1.8228059874627933</v>
       </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="K12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="9">
         <f>L11*100</f>
         <v>39.266633186089884</v>
       </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="9">
         <v>2.5152000000000001</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
       <c r="F13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="9">
         <v>94.245999999999995</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
       <c r="K13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="9">
         <v>244.93</v>
       </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="9">
         <v>78.765000000000001</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
       <c r="F14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="9">
         <v>224.01</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
       <c r="K14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="9">
         <v>388.12</v>
       </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="9">
         <f>(B13/B14)*100</f>
         <v>3.1932965149495334</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
       <c r="F15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="9">
         <f>(G13/G14)*100</f>
         <v>42.072228918351854</v>
       </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
       <c r="K15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15" s="9">
         <f>(L13/L14)*100</f>
         <v>63.106771101721115</v>
       </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7365,42 +7374,42 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="9">
         <v>-25.274678000000002</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="9">
         <f>10^(B3/20)</f>
         <v>5.4483638159108443E-2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="9">
         <f>C3^2</f>
         <v>2.9684668270526576E-3</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="9">
         <v>8.9817060000000009</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="9">
         <f>10^(G3/20)</f>
         <v>2.8124531715117249</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="9">
         <f>H3^2</f>
         <v>7.9098928419463599</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="9">
         <v>19.416899999999998</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="9">
         <f>10^(L3/20)</f>
         <v>9.3507188678557984</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="9">
         <f>M3^2</f>
         <v>87.435943345674431</v>
       </c>
@@ -7409,42 +7418,42 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="9">
         <v>-118.995</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="9">
         <f t="shared" ref="C4:C10" si="0">10^(B4/20)</f>
         <v>1.1226645259802338E-6</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="9">
         <f t="shared" ref="D4:D10" si="1">C4^2</f>
         <v>1.260375637894423E-12</v>
       </c>
       <c r="F4" s="1">
         <v>2</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="9">
         <v>-31.732075999999999</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="9">
         <f t="shared" ref="H4:H10" si="2">10^(G4/20)</f>
         <v>2.5905751783015071E-2</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="9">
         <f t="shared" ref="I4:I10" si="3">H4^2</f>
         <v>6.7110797544318846E-4</v>
       </c>
       <c r="K4" s="1">
         <v>2</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="9">
         <v>-31.116399999999999</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="9">
         <f t="shared" ref="M4:M10" si="4">10^(L4/20)</f>
         <v>2.7808656012838967E-2</v>
       </c>
-      <c r="N4" s="2">
+      <c r="N4" s="9">
         <f t="shared" ref="N4:N10" si="5">M4^2</f>
         <v>7.7332134924040482E-4</v>
       </c>
@@ -7453,42 +7462,42 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="9">
         <v>-29.106104999999999</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="9">
         <f t="shared" si="0"/>
         <v>3.5050542967105115E-2</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="9">
         <f t="shared" si="1"/>
         <v>1.2285405622888819E-3</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="9">
         <v>-14.11999</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="9">
         <f t="shared" si="2"/>
         <v>0.19678885553209666</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="9">
         <f t="shared" si="3"/>
         <v>3.8725853661632406E-2</v>
       </c>
       <c r="K5" s="1">
         <v>3</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="9">
         <v>-5.471406</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="9">
         <f t="shared" si="4"/>
         <v>0.53263499879461385</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="9">
         <f t="shared" si="5"/>
         <v>0.28370004194093829</v>
       </c>
@@ -7497,42 +7506,42 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="9">
         <v>-116.8165</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="9">
         <f t="shared" si="0"/>
         <v>1.4426965724485703E-6</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="9">
         <f t="shared" si="1"/>
         <v>2.0813734001548528E-12</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="9">
         <v>-48.047980000000003</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="9">
         <f t="shared" si="2"/>
         <v>3.9591412835308631E-3</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="9">
         <f t="shared" si="3"/>
         <v>1.5674799702958411E-5</v>
       </c>
       <c r="K6" s="1">
         <v>4</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="9">
         <v>-24.66048</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="9">
         <f t="shared" si="4"/>
         <v>5.8475776834308088E-2</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="9">
         <f t="shared" si="5"/>
         <v>3.4194164763758023E-3</v>
       </c>
@@ -7541,42 +7550,42 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="9">
         <v>-38.732456999999997</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="9">
         <f t="shared" si="0"/>
         <v>1.1571166692173812E-2</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="9">
         <f t="shared" si="1"/>
         <v>1.3389189861807264E-4</v>
       </c>
       <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="9">
         <v>-19.348206999999999</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="9">
         <f t="shared" si="2"/>
         <v>0.10779277438543364</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="9">
         <f t="shared" si="3"/>
         <v>1.1619282209708998E-2</v>
       </c>
       <c r="K7" s="1">
         <v>5</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="9">
         <v>-6.723776</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="9">
         <f t="shared" si="4"/>
         <v>0.46111707044912315</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="9">
         <f t="shared" si="5"/>
         <v>0.21262895265958159</v>
       </c>
@@ -7585,42 +7594,42 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="9">
         <v>-114.1957</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="9">
         <f t="shared" si="0"/>
         <v>1.9508101206001143E-6</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="9">
         <f t="shared" si="1"/>
         <v>3.8056601266358327E-12</v>
       </c>
       <c r="F8" s="1">
         <v>6</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="9">
         <v>-60.111530000000002</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="9">
         <f t="shared" si="2"/>
         <v>9.8724172001270314E-4</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="9">
         <f t="shared" si="3"/>
         <v>9.7464621373364063E-7</v>
       </c>
       <c r="K8" s="1">
         <v>6</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="9">
         <v>-33.230699999999999</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="9">
         <f t="shared" si="4"/>
         <v>2.1800426994224943E-2</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="9">
         <f t="shared" si="5"/>
         <v>4.7525861713053157E-4</v>
       </c>
@@ -7629,42 +7638,42 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="9">
         <v>-57.957210000000003</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="9">
         <f t="shared" si="0"/>
         <v>1.2651426594704268E-3</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="9">
         <f t="shared" si="1"/>
         <v>1.6005859488119042E-6</v>
       </c>
       <c r="F9" s="1">
         <v>7</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="9">
         <v>-23.239789999999999</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="9">
         <f t="shared" si="2"/>
         <v>6.8866894619092206E-2</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="9">
         <f t="shared" si="3"/>
         <v>4.7426491744771513E-3</v>
       </c>
       <c r="K9" s="1">
         <v>7</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="9">
         <v>-24.285640000000001</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="9">
         <f t="shared" si="4"/>
         <v>6.1054545130109272E-2</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="9">
         <f t="shared" si="5"/>
         <v>3.7276574810445498E-3</v>
       </c>
@@ -7673,42 +7682,42 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="9">
         <v>-126.1932</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="9">
         <f t="shared" si="0"/>
         <v>4.9016240701903493E-7</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="9">
         <f t="shared" si="1"/>
         <v>2.4025918525469407E-13</v>
       </c>
       <c r="F10" s="1">
         <v>8</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="9">
         <v>-77.061824999999999</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="9">
         <f t="shared" si="2"/>
         <v>1.4025189890889075E-4</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="9">
         <f t="shared" si="3"/>
         <v>1.9670595147549709E-8</v>
       </c>
       <c r="K10" s="1">
         <v>8</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="9">
         <v>-33.091999999999999</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="9">
         <f t="shared" si="4"/>
         <v>2.2151339841371936E-2</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="9">
         <f t="shared" si="5"/>
         <v>4.906818567679517E-4</v>
       </c>
@@ -7717,140 +7726,140 @@
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="9">
         <f>SQRT(SUM(D4:D10)/D3)</f>
         <v>0.67786989575810741</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
       <c r="F11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="9">
         <f>SQRT(SUM(I4:I10)/I3)</f>
         <v>8.3972421687846785E-2</v>
       </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="K11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="9">
         <f>SQRT(SUM(N4:N10)/N3)</f>
         <v>7.6013942885339775E-2</v>
       </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="9">
         <f>B11*100</f>
         <v>67.786989575810736</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
       <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="9">
         <f>G11*100</f>
         <v>8.397242168784679</v>
       </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="K12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="9">
         <f>L11*100</f>
         <v>7.6013942885339771</v>
       </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="9">
         <v>4.3159999999999997E-2</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
       <c r="F13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="9">
         <v>82.626000000000005</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
       <c r="K13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="9">
         <v>890.77</v>
       </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="9">
         <v>2.4380999999999999</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
       <c r="F14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="9">
         <v>148.26</v>
       </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
       <c r="K14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="9">
         <v>251.94</v>
       </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="9">
         <f>(B13/B14)*100</f>
         <v>1.7702309175177393</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
       <c r="F15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="9">
         <f>(G13/G14)*100</f>
         <v>55.730473492513156</v>
       </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
       <c r="K15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L15" s="1">
+      <c r="L15" s="9">
         <f>(L13/L14)*100</f>
         <v>353.56434071604349</v>
       </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
